--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128959115</v>
       </c>
       <c r="B3" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128959115</v>
       </c>
       <c r="B3" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128959115</v>
       </c>
       <c r="B3" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -775,7 +775,7 @@
         <v>128959115</v>
       </c>
       <c r="B3" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -870,6 +870,1685 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129529701</v>
+      </c>
+      <c r="B4" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>638164</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6635000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På levande äldre gran</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129529667</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96970</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>53</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>638289</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6634966</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129529690</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92870</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>638521</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6634838</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129529673</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>638516</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6634868</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129529684</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92003</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>638462</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6634855</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129529697</v>
+      </c>
+      <c r="B9" t="n">
+        <v>90932</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gullgröppa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>638402</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6634635</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129529700</v>
+      </c>
+      <c r="B10" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>638165</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6634993</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På levande äldre gran</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129529691</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92870</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>638522</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6634845</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129529688</v>
+      </c>
+      <c r="B12" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>638173</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6634959</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På levande äldre gran</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129529698</v>
+      </c>
+      <c r="B13" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>638291</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6634662</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På levande äldre gran</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129529664</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91774</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1106</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vågticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Osteina undosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>638322</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6634962</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129529669</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91514</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>638445</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6634890</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129529682</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91323</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>638468</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6634921</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129529668</v>
+      </c>
+      <c r="B17" t="n">
+        <v>96970</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>53</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>638445</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6634888</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>1 kvm, längs hela stocken</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129529699</v>
+      </c>
+      <c r="B18" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>638353</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6634591</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På levande äldre gran</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129529689</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92824</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>638468</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6634921</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129529679</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>638353</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6634546</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -1659,7 +1659,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129529688</v>
+        <v>129529698</v>
       </c>
       <c r="B12" t="n">
         <v>4779</v>
@@ -1694,10 +1694,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>638173</v>
+        <v>638291</v>
       </c>
       <c r="R12" t="n">
-        <v>6634959</v>
+        <v>6634662</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1761,7 +1761,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129529698</v>
+        <v>129529688</v>
       </c>
       <c r="B13" t="n">
         <v>4779</v>
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>638291</v>
+        <v>638173</v>
       </c>
       <c r="R13" t="n">
-        <v>6634662</v>
+        <v>6634959</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1863,32 +1863,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129529664</v>
+        <v>129529669</v>
       </c>
       <c r="B14" t="n">
-        <v>91774</v>
+        <v>91514</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1106</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1898,10 +1898,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>638322</v>
+        <v>638445</v>
       </c>
       <c r="R14" t="n">
-        <v>6634962</v>
+        <v>6634890</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1960,32 +1960,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129529669</v>
+        <v>129529664</v>
       </c>
       <c r="B15" t="n">
-        <v>91514</v>
+        <v>91774</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>1106</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>638445</v>
+        <v>638322</v>
       </c>
       <c r="R15" t="n">
-        <v>6634890</v>
+        <v>6634962</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2256,32 +2256,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129529699</v>
+        <v>129529689</v>
       </c>
       <c r="B18" t="n">
-        <v>4779</v>
+        <v>92824</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102306</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2291,10 +2291,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>638353</v>
+        <v>638468</v>
       </c>
       <c r="R18" t="n">
-        <v>6634591</v>
+        <v>6634921</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2327,11 +2327,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2358,32 +2353,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129529689</v>
+        <v>129529699</v>
       </c>
       <c r="B19" t="n">
-        <v>92824</v>
+        <v>4779</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4361</v>
+        <v>102306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2393,10 +2388,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>638468</v>
+        <v>638353</v>
       </c>
       <c r="R19" t="n">
-        <v>6634921</v>
+        <v>6634591</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2429,6 +2424,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -1659,7 +1659,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129529698</v>
+        <v>129529688</v>
       </c>
       <c r="B12" t="n">
         <v>4779</v>
@@ -1694,10 +1694,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>638291</v>
+        <v>638173</v>
       </c>
       <c r="R12" t="n">
-        <v>6634662</v>
+        <v>6634959</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1761,7 +1761,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129529688</v>
+        <v>129529698</v>
       </c>
       <c r="B13" t="n">
         <v>4779</v>
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>638173</v>
+        <v>638291</v>
       </c>
       <c r="R13" t="n">
-        <v>6634959</v>
+        <v>6634662</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -978,7 +978,7 @@
         <v>129529667</v>
       </c>
       <c r="B5" t="n">
-        <v>96970</v>
+        <v>96973</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>129529690</v>
       </c>
       <c r="B6" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>129529684</v>
       </c>
       <c r="B8" t="n">
-        <v>92003</v>
+        <v>92006</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>129529697</v>
       </c>
       <c r="B9" t="n">
-        <v>90932</v>
+        <v>90935</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1460,32 +1460,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129529700</v>
+        <v>129529691</v>
       </c>
       <c r="B10" t="n">
-        <v>4779</v>
+        <v>92873</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102306</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>638165</v>
+        <v>638522</v>
       </c>
       <c r="R10" t="n">
-        <v>6634993</v>
+        <v>6634845</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1531,11 +1531,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1562,32 +1557,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129529691</v>
+        <v>129529700</v>
       </c>
       <c r="B11" t="n">
-        <v>92870</v>
+        <v>4779</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>102306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1597,10 +1592,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>638522</v>
+        <v>638165</v>
       </c>
       <c r="R11" t="n">
-        <v>6634845</v>
+        <v>6634993</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1633,6 +1628,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1863,32 +1863,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129529669</v>
+        <v>129529664</v>
       </c>
       <c r="B14" t="n">
-        <v>91514</v>
+        <v>91777</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>1106</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1898,10 +1898,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>638445</v>
+        <v>638322</v>
       </c>
       <c r="R14" t="n">
-        <v>6634890</v>
+        <v>6634962</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1960,32 +1960,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129529664</v>
+        <v>129529669</v>
       </c>
       <c r="B15" t="n">
-        <v>91774</v>
+        <v>91517</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1106</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>638322</v>
+        <v>638445</v>
       </c>
       <c r="R15" t="n">
-        <v>6634962</v>
+        <v>6634890</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2060,7 +2060,7 @@
         <v>129529682</v>
       </c>
       <c r="B16" t="n">
-        <v>91323</v>
+        <v>91326</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>129529668</v>
       </c>
       <c r="B17" t="n">
-        <v>96970</v>
+        <v>96973</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>129529689</v>
       </c>
       <c r="B18" t="n">
-        <v>92824</v>
+        <v>92827</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2550,6 +2550,894 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129587678</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>638458</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6634826</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129587673</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>638448</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6634809</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Blommande</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129587679</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>638451</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6634848</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129587676</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>638438</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6634803</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>10 buketter</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129587670</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>638333</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6634980</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129587685</v>
+      </c>
+      <c r="B26" t="n">
+        <v>100916</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>638463</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6634889</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129587677</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>638447</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6634803</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>10 buketter</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129587681</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>638468</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6634929</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129587667</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91553</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>638466</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6634835</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3438,6 +3438,4787 @@
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129597548</v>
+      </c>
+      <c r="B30" t="n">
+        <v>96973</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>53</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>638336</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6634702</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129598790</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>638333</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6634812</v>
+      </c>
+      <c r="S31" t="n">
+        <v>4</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129605451</v>
+      </c>
+      <c r="B32" t="n">
+        <v>92871</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>638325</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6634691</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129599980</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>638416</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6634840</v>
+      </c>
+      <c r="S33" t="n">
+        <v>13</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>2 vinterståndare</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129598966</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>638348</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6634797</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>3 vinterståndare</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129598714</v>
+      </c>
+      <c r="B35" t="n">
+        <v>91573</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>638323</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6634794</v>
+      </c>
+      <c r="S35" t="n">
+        <v>4</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Rikligt på undersidan av döda grenar på levande äldre gran.</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129599353</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>638395</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6634786</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129599884</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>638397</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6634819</v>
+      </c>
+      <c r="S37" t="n">
+        <v>4</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129599503</v>
+      </c>
+      <c r="B38" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>638325</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6634846</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Anders Broms</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Anders Broms</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129605441</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>638444</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6634897</v>
+      </c>
+      <c r="S39" t="n">
+        <v>15</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129605436</v>
+      </c>
+      <c r="B40" t="n">
+        <v>96973</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>53</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>638281</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6634960</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129597954</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>638325</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6634719</v>
+      </c>
+      <c r="S41" t="n">
+        <v>4</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>3 vinterståndare</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129599775</v>
+      </c>
+      <c r="B42" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>638435</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6634839</v>
+      </c>
+      <c r="S42" t="n">
+        <v>11</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129599955</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>638428</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6634839</v>
+      </c>
+      <c r="S43" t="n">
+        <v>14</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129599067</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>638355</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6634788</v>
+      </c>
+      <c r="S44" t="n">
+        <v>8</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129598225</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>638330</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6634715</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>2 vinterståndare</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129602955</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>638310</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6634749</v>
+      </c>
+      <c r="S46" t="n">
+        <v>24</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Hack av spillkråka</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129601221</v>
+      </c>
+      <c r="B47" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>638294</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6634962</v>
+      </c>
+      <c r="S47" t="n">
+        <v>12</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129602684</v>
+      </c>
+      <c r="B48" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>638332</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6634693</v>
+      </c>
+      <c r="S48" t="n">
+        <v>4</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129600150</v>
+      </c>
+      <c r="B49" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>638354</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6634767</v>
+      </c>
+      <c r="S49" t="n">
+        <v>4</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>129602225</v>
+      </c>
+      <c r="B50" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>638237</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6635004</v>
+      </c>
+      <c r="S50" t="n">
+        <v>7</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>129605439</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>638277</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6634933</v>
+      </c>
+      <c r="S51" t="n">
+        <v>15</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>129599969</v>
+      </c>
+      <c r="B52" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>638428</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6634835</v>
+      </c>
+      <c r="S52" t="n">
+        <v>12</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>129599511</v>
+      </c>
+      <c r="B53" t="n">
+        <v>91553</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>638406</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6634775</v>
+      </c>
+      <c r="S53" t="n">
+        <v>4</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>129599963</v>
+      </c>
+      <c r="B54" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>638420</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6634840</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>129599772</v>
+      </c>
+      <c r="B55" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>638399</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6634806</v>
+      </c>
+      <c r="S55" t="n">
+        <v>4</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>129602370</v>
+      </c>
+      <c r="B56" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>638275</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6634839</v>
+      </c>
+      <c r="S56" t="n">
+        <v>8</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>129596091</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Orreboda, Orreboda, Upl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>638323</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6634555</v>
+      </c>
+      <c r="S57" t="n">
+        <v>2</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>129602720</v>
+      </c>
+      <c r="B58" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>638301</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6634767</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>129605440</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>638309</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6634908</v>
+      </c>
+      <c r="S59" t="n">
+        <v>15</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>129600817</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>638230</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6634962</v>
+      </c>
+      <c r="S60" t="n">
+        <v>4</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>129601983</v>
+      </c>
+      <c r="B61" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>638209</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6635047</v>
+      </c>
+      <c r="S61" t="n">
+        <v>4</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>129602223</v>
+      </c>
+      <c r="B62" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>638236</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6634982</v>
+      </c>
+      <c r="S62" t="n">
+        <v>9</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>129600091</v>
+      </c>
+      <c r="B63" t="n">
+        <v>92873</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>638367</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6634820</v>
+      </c>
+      <c r="S63" t="n">
+        <v>4</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>129605450</v>
+      </c>
+      <c r="B64" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>638178</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6635025</v>
+      </c>
+      <c r="S64" t="n">
+        <v>15</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>129597436</v>
+      </c>
+      <c r="B65" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>638292</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6634699</v>
+      </c>
+      <c r="S65" t="n">
+        <v>11</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>129605452</v>
+      </c>
+      <c r="B66" t="n">
+        <v>92871</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>638324</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6634750</v>
+      </c>
+      <c r="S66" t="n">
+        <v>15</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>129601121</v>
+      </c>
+      <c r="B67" t="n">
+        <v>91777</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>1106</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Vågticka</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Osteina undosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>638329</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6634973</v>
+      </c>
+      <c r="S67" t="n">
+        <v>11</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>129605437</v>
+      </c>
+      <c r="B68" t="n">
+        <v>92271</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>638356</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6634677</v>
+      </c>
+      <c r="S68" t="n">
+        <v>15</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>129598997</v>
+      </c>
+      <c r="B69" t="n">
+        <v>92203</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>638351</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6634790</v>
+      </c>
+      <c r="S69" t="n">
+        <v>13</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>129605449</v>
+      </c>
+      <c r="B70" t="n">
+        <v>4779</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>638301</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6634752</v>
+      </c>
+      <c r="S70" t="n">
+        <v>15</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>129602574</v>
+      </c>
+      <c r="B71" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>638309</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6634813</v>
+      </c>
+      <c r="S71" t="n">
+        <v>17</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>129600760</v>
+      </c>
+      <c r="B72" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>638304</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6634890</v>
+      </c>
+      <c r="S72" t="n">
+        <v>14</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Hack av spillkråka</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AY72" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -1863,32 +1863,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129529664</v>
+        <v>129529669</v>
       </c>
       <c r="B14" t="n">
-        <v>91777</v>
+        <v>91517</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1106</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1898,10 +1898,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>638322</v>
+        <v>638445</v>
       </c>
       <c r="R14" t="n">
-        <v>6634962</v>
+        <v>6634890</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1960,32 +1960,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129529669</v>
+        <v>129529664</v>
       </c>
       <c r="B15" t="n">
-        <v>91517</v>
+        <v>91777</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>1106</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>638445</v>
+        <v>638322</v>
       </c>
       <c r="R15" t="n">
-        <v>6634890</v>
+        <v>6634962</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2256,32 +2256,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129529689</v>
+        <v>129529699</v>
       </c>
       <c r="B18" t="n">
-        <v>92827</v>
+        <v>4779</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4361</v>
+        <v>102306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2291,10 +2291,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>638468</v>
+        <v>638353</v>
       </c>
       <c r="R18" t="n">
-        <v>6634921</v>
+        <v>6634591</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2327,6 +2327,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2353,32 +2358,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129529699</v>
+        <v>129529689</v>
       </c>
       <c r="B19" t="n">
-        <v>4779</v>
+        <v>92827</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102306</v>
+        <v>4361</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2388,10 +2393,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>638353</v>
+        <v>638468</v>
       </c>
       <c r="R19" t="n">
-        <v>6634591</v>
+        <v>6634921</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2424,11 +2429,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2950,32 +2950,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129587670</v>
+        <v>129587685</v>
       </c>
       <c r="B25" t="n">
-        <v>57724</v>
+        <v>100916</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>638333</v>
+        <v>638463</v>
       </c>
       <c r="R25" t="n">
-        <v>6634980</v>
+        <v>6634889</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3047,32 +3047,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129587685</v>
+        <v>129587670</v>
       </c>
       <c r="B26" t="n">
-        <v>100916</v>
+        <v>57724</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3082,10 +3082,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>638463</v>
+        <v>638333</v>
       </c>
       <c r="R26" t="n">
-        <v>6634889</v>
+        <v>6634980</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3440,48 +3440,62 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129597548</v>
+        <v>129598790</v>
       </c>
       <c r="B30" t="n">
-        <v>96973</v>
+        <v>98727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>638336</v>
+        <v>638333</v>
       </c>
       <c r="R30" t="n">
-        <v>6634702</v>
+        <v>6634812</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3510,7 +3524,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3520,7 +3534,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3547,62 +3561,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129598790</v>
+        <v>129597548</v>
       </c>
       <c r="B31" t="n">
-        <v>98727</v>
+        <v>96973</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>638333</v>
+        <v>638336</v>
       </c>
       <c r="R31" t="n">
-        <v>6634812</v>
+        <v>6634702</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3891,62 +3891,44 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129598966</v>
+        <v>129598714</v>
       </c>
       <c r="B34" t="n">
-        <v>98727</v>
+        <v>91573</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>638348</v>
+        <v>638323</v>
       </c>
       <c r="R34" t="n">
-        <v>6634797</v>
+        <v>6634794</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3975,7 +3957,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -3985,12 +3967,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>3 vinterståndare</t>
+          <t>Rikligt på undersidan av döda grenar på levande äldre gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4017,44 +3999,62 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129598714</v>
+        <v>129598966</v>
       </c>
       <c r="B35" t="n">
-        <v>91573</v>
+        <v>98727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>638323</v>
+        <v>638348</v>
       </c>
       <c r="R35" t="n">
-        <v>6634794</v>
+        <v>6634797</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Rikligt på undersidan av döda grenar på levande äldre gran.</t>
+          <t>3 vinterståndare</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4659,7 +4659,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129597954</v>
+        <v>129599775</v>
       </c>
       <c r="B41" t="n">
         <v>98727</v>
@@ -4689,17 +4689,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4708,13 +4703,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>638325</v>
+        <v>638435</v>
       </c>
       <c r="R41" t="n">
-        <v>6634719</v>
+        <v>6634839</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4743,7 +4738,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4753,12 +4748,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>3 vinterståndare</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4773,19 +4763,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129599775</v>
+        <v>129599955</v>
       </c>
       <c r="B42" t="n">
         <v>98727</v>
@@ -4815,7 +4805,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4829,13 +4819,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>638435</v>
+        <v>638428</v>
       </c>
       <c r="R42" t="n">
         <v>6634839</v>
       </c>
       <c r="S42" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4864,7 +4854,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4874,7 +4864,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4887,11 +4877,21 @@
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Hannes Theelen</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Hannes Theelen</t>
+        </is>
+      </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129599955</v>
+        <v>129597954</v>
       </c>
       <c r="B43" t="n">
         <v>98727</v>
@@ -4921,12 +4921,17 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4935,13 +4940,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>638428</v>
+        <v>638325</v>
       </c>
       <c r="R43" t="n">
-        <v>6634839</v>
+        <v>6634719</v>
       </c>
       <c r="S43" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4970,7 +4975,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -4980,7 +4985,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>3 vinterståndare</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4993,11 +5003,21 @@
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129599067</v>
+        <v>129598225</v>
       </c>
       <c r="B44" t="n">
         <v>98727</v>
@@ -5027,7 +5047,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5046,13 +5066,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>638355</v>
+        <v>638330</v>
       </c>
       <c r="R44" t="n">
-        <v>6634788</v>
+        <v>6634715</v>
       </c>
       <c r="S44" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5081,7 +5101,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5091,12 +5111,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>En vinterståndare</t>
+          <t>2 vinterståndare</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5123,7 +5143,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129598225</v>
+        <v>129599067</v>
       </c>
       <c r="B45" t="n">
         <v>98727</v>
@@ -5153,7 +5173,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5172,13 +5192,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>638330</v>
+        <v>638355</v>
       </c>
       <c r="R45" t="n">
-        <v>6634715</v>
+        <v>6634788</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5207,7 +5227,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5217,12 +5237,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>2 vinterståndare</t>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5249,48 +5269,52 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129602955</v>
+        <v>129601221</v>
       </c>
       <c r="B46" t="n">
-        <v>57724</v>
+        <v>98727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>638310</v>
+        <v>638294</v>
       </c>
       <c r="R46" t="n">
-        <v>6634749</v>
+        <v>6634962</v>
       </c>
       <c r="S46" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5319,7 +5343,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5329,12 +5353,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Hack av spillkråka</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5347,56 +5366,62 @@
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Hannes Theelen</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Hannes Theelen</t>
+        </is>
+      </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129601221</v>
+        <v>129602955</v>
       </c>
       <c r="B47" t="n">
-        <v>98727</v>
+        <v>57724</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>638294</v>
+        <v>638310</v>
       </c>
       <c r="R47" t="n">
-        <v>6634962</v>
+        <v>6634749</v>
       </c>
       <c r="S47" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5425,7 +5450,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5435,7 +5460,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Hack av spillkråka</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5448,11 +5478,21 @@
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Hannes Theelen</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Hannes Theelen</t>
+        </is>
+      </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129602684</v>
+        <v>129600150</v>
       </c>
       <c r="B48" t="n">
         <v>98727</v>
@@ -5482,7 +5522,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5492,7 +5532,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5501,10 +5541,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>638332</v>
+        <v>638354</v>
       </c>
       <c r="R48" t="n">
-        <v>6634693</v>
+        <v>6634767</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -5536,7 +5576,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5546,7 +5586,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5573,7 +5613,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129600150</v>
+        <v>129602684</v>
       </c>
       <c r="B49" t="n">
         <v>98727</v>
@@ -5603,7 +5643,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5613,7 +5653,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5622,10 +5662,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>638354</v>
+        <v>638332</v>
       </c>
       <c r="R49" t="n">
-        <v>6634767</v>
+        <v>6634693</v>
       </c>
       <c r="S49" t="n">
         <v>4</v>
@@ -5657,7 +5697,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5667,7 +5707,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5917,57 +5957,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129599969</v>
+        <v>129599511</v>
       </c>
       <c r="B52" t="n">
-        <v>98727</v>
+        <v>91553</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>638428</v>
+        <v>638406</v>
       </c>
       <c r="R52" t="n">
-        <v>6634835</v>
+        <v>6634775</v>
       </c>
       <c r="S52" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5996,7 +6027,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6006,7 +6037,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6019,52 +6050,71 @@
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129599511</v>
+        <v>129599969</v>
       </c>
       <c r="B53" t="n">
-        <v>91553</v>
+        <v>98727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>638406</v>
+        <v>638428</v>
       </c>
       <c r="R53" t="n">
-        <v>6634775</v>
+        <v>6634835</v>
       </c>
       <c r="S53" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6093,7 +6143,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6103,7 +6153,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6118,12 +6168,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6498,57 +6548,57 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129596091</v>
+        <v>129602720</v>
       </c>
       <c r="B57" t="n">
-        <v>57724</v>
+        <v>98727</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Orreboda, Orreboda, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>638323</v>
+        <v>638301</v>
       </c>
       <c r="R57" t="n">
-        <v>6634555</v>
+        <v>6634767</v>
       </c>
       <c r="S57" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6577,7 +6627,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6587,7 +6637,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6602,69 +6652,69 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129602720</v>
+        <v>129596091</v>
       </c>
       <c r="B58" t="n">
-        <v>98727</v>
+        <v>57724</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Orreboda, Orreboda, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>638301</v>
+        <v>638323</v>
       </c>
       <c r="R58" t="n">
-        <v>6634767</v>
+        <v>6634555</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6693,7 +6743,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6703,7 +6753,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6716,11 +6766,21 @@
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129605440</v>
+        <v>129600817</v>
       </c>
       <c r="B59" t="n">
         <v>57724</v>
@@ -6749,19 +6809,24 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>638309</v>
+        <v>638230</v>
       </c>
       <c r="R59" t="n">
-        <v>6634908</v>
+        <v>6634962</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6788,9 +6853,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6805,19 +6880,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129600817</v>
+        <v>129605440</v>
       </c>
       <c r="B60" t="n">
         <v>57724</v>
@@ -6846,24 +6921,19 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>638230</v>
+        <v>638309</v>
       </c>
       <c r="R60" t="n">
-        <v>6634962</v>
+        <v>6634908</v>
       </c>
       <c r="S60" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6890,19 +6960,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6917,12 +6977,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7152,6 +7212,16 @@
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Hannes Theelen</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Hannes Theelen</t>
+        </is>
+      </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
@@ -7385,53 +7455,48 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129597436</v>
+        <v>129605452</v>
       </c>
       <c r="B65" t="n">
-        <v>57724</v>
+        <v>92871</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>638292</v>
+        <v>638324</v>
       </c>
       <c r="R65" t="n">
-        <v>6634699</v>
+        <v>6634750</v>
       </c>
       <c r="S65" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7458,19 +7523,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>10:38</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7485,60 +7540,65 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129605452</v>
+        <v>129597436</v>
       </c>
       <c r="B66" t="n">
-        <v>92871</v>
+        <v>57724</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>638324</v>
+        <v>638292</v>
       </c>
       <c r="R66" t="n">
-        <v>6634750</v>
+        <v>6634699</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7565,9 +7625,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7582,12 +7652,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7798,10 +7868,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129598997</v>
+        <v>129605449</v>
       </c>
       <c r="B69" t="n">
-        <v>92203</v>
+        <v>4779</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7809,37 +7879,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1339</v>
+        <v>102306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>638351</v>
+        <v>638301</v>
       </c>
       <c r="R69" t="n">
-        <v>6634790</v>
+        <v>6634752</v>
       </c>
       <c r="S69" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7866,19 +7941,14 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>11:45</t>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7887,71 +7957,67 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129605449</v>
+        <v>129600760</v>
       </c>
       <c r="B70" t="n">
-        <v>4779</v>
+        <v>57724</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>638301</v>
+        <v>638304</v>
       </c>
       <c r="R70" t="n">
-        <v>6634752</v>
+        <v>6634890</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7978,14 +8044,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På äldre levande gran</t>
+          <t>Hack av spillkråka</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7994,19 +8070,18 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8115,36 +8190,46 @@
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Hannes Theelen</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Hannes Theelen</t>
+        </is>
+      </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129600760</v>
+        <v>129598997</v>
       </c>
       <c r="B72" t="n">
-        <v>57724</v>
+        <v>92203</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8154,13 +8239,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>638304</v>
+        <v>638351</v>
       </c>
       <c r="R72" t="n">
-        <v>6634890</v>
+        <v>6634790</v>
       </c>
       <c r="S72" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8189,7 +8274,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8199,12 +8284,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:04</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Hack av spillkråka</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8217,6 +8297,16 @@
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
       <c r="AY72" t="inlineStr"/>
     </row>
   </sheetData>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -1460,32 +1460,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129529691</v>
+        <v>129529700</v>
       </c>
       <c r="B10" t="n">
-        <v>92873</v>
+        <v>4779</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>102306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>638522</v>
+        <v>638165</v>
       </c>
       <c r="R10" t="n">
-        <v>6634845</v>
+        <v>6634993</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1531,6 +1531,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1557,32 +1562,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129529700</v>
+        <v>129529691</v>
       </c>
       <c r="B11" t="n">
-        <v>4779</v>
+        <v>92873</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102306</v>
+        <v>5966</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1592,10 +1597,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>638165</v>
+        <v>638522</v>
       </c>
       <c r="R11" t="n">
-        <v>6634993</v>
+        <v>6634845</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1628,11 +1633,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1863,32 +1863,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129529669</v>
+        <v>129529664</v>
       </c>
       <c r="B14" t="n">
-        <v>91517</v>
+        <v>91777</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>1106</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1898,10 +1898,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>638445</v>
+        <v>638322</v>
       </c>
       <c r="R14" t="n">
-        <v>6634890</v>
+        <v>6634962</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1960,32 +1960,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129529664</v>
+        <v>129529669</v>
       </c>
       <c r="B15" t="n">
-        <v>91777</v>
+        <v>91517</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1106</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>638322</v>
+        <v>638445</v>
       </c>
       <c r="R15" t="n">
-        <v>6634962</v>
+        <v>6634890</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2256,32 +2256,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129529699</v>
+        <v>129529689</v>
       </c>
       <c r="B18" t="n">
-        <v>4779</v>
+        <v>92827</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102306</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2291,10 +2291,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>638353</v>
+        <v>638468</v>
       </c>
       <c r="R18" t="n">
-        <v>6634591</v>
+        <v>6634921</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2327,11 +2327,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2358,32 +2353,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129529689</v>
+        <v>129529699</v>
       </c>
       <c r="B19" t="n">
-        <v>92827</v>
+        <v>4779</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4361</v>
+        <v>102306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2393,10 +2388,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>638468</v>
+        <v>638353</v>
       </c>
       <c r="R19" t="n">
-        <v>6634921</v>
+        <v>6634591</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2429,6 +2424,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3440,62 +3440,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129598790</v>
+        <v>129597548</v>
       </c>
       <c r="B30" t="n">
-        <v>98727</v>
+        <v>96973</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>638333</v>
+        <v>638336</v>
       </c>
       <c r="R30" t="n">
-        <v>6634812</v>
+        <v>6634702</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3524,7 +3510,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3534,7 +3520,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3561,48 +3547,62 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129597548</v>
+        <v>129598790</v>
       </c>
       <c r="B31" t="n">
-        <v>96973</v>
+        <v>98727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>638336</v>
+        <v>638333</v>
       </c>
       <c r="R31" t="n">
-        <v>6634702</v>
+        <v>6634812</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4465,32 +4465,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129605441</v>
+        <v>129605436</v>
       </c>
       <c r="B39" t="n">
-        <v>91326</v>
+        <v>96973</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3215</v>
+        <v>53</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4500,10 +4500,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>638444</v>
+        <v>638281</v>
       </c>
       <c r="R39" t="n">
-        <v>6634897</v>
+        <v>6634960</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4562,32 +4562,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129605436</v>
+        <v>129605441</v>
       </c>
       <c r="B40" t="n">
-        <v>96973</v>
+        <v>91326</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>53</v>
+        <v>3215</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4597,10 +4597,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>638281</v>
+        <v>638444</v>
       </c>
       <c r="R40" t="n">
-        <v>6634960</v>
+        <v>6634897</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5017,62 +5017,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129598225</v>
+        <v>129602955</v>
       </c>
       <c r="B44" t="n">
-        <v>98727</v>
+        <v>57724</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>638330</v>
+        <v>638310</v>
       </c>
       <c r="R44" t="n">
-        <v>6634715</v>
+        <v>6634749</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5101,7 +5087,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5111,12 +5097,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>2 vinterståndare</t>
+          <t>Hack av spillkråka</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5131,19 +5117,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129599067</v>
+        <v>129601221</v>
       </c>
       <c r="B45" t="n">
         <v>98727</v>
@@ -5173,17 +5159,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5192,13 +5168,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>638355</v>
+        <v>638294</v>
       </c>
       <c r="R45" t="n">
-        <v>6634788</v>
+        <v>6634962</v>
       </c>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5227,7 +5203,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5237,12 +5213,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>En vinterståndare</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5257,19 +5228,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129601221</v>
+        <v>129598225</v>
       </c>
       <c r="B46" t="n">
         <v>98727</v>
@@ -5299,7 +5270,17 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5308,13 +5289,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>638294</v>
+        <v>638330</v>
       </c>
       <c r="R46" t="n">
-        <v>6634962</v>
+        <v>6634715</v>
       </c>
       <c r="S46" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5343,7 +5324,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5353,7 +5334,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>2 vinterståndare</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5368,60 +5354,74 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129602955</v>
+        <v>129599067</v>
       </c>
       <c r="B47" t="n">
-        <v>57724</v>
+        <v>98727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>638310</v>
+        <v>638355</v>
       </c>
       <c r="R47" t="n">
-        <v>6634749</v>
+        <v>6634788</v>
       </c>
       <c r="S47" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Hack av spillkråka</t>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5480,12 +5480,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5957,48 +5957,62 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129599511</v>
+        <v>129599963</v>
       </c>
       <c r="B52" t="n">
-        <v>91553</v>
+        <v>98727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>638406</v>
+        <v>638420</v>
       </c>
       <c r="R52" t="n">
-        <v>6634775</v>
+        <v>6634840</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6027,7 +6041,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6037,7 +6051,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6064,7 +6078,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129599969</v>
+        <v>129599772</v>
       </c>
       <c r="B53" t="n">
         <v>98727</v>
@@ -6094,12 +6108,17 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6108,13 +6127,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>638428</v>
+        <v>638399</v>
       </c>
       <c r="R53" t="n">
-        <v>6634835</v>
+        <v>6634806</v>
       </c>
       <c r="S53" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6143,7 +6162,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6153,7 +6172,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6168,19 +6192,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129599963</v>
+        <v>129599969</v>
       </c>
       <c r="B54" t="n">
         <v>98727</v>
@@ -6215,12 +6239,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6229,13 +6248,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>638420</v>
+        <v>638428</v>
       </c>
       <c r="R54" t="n">
-        <v>6634840</v>
+        <v>6634835</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6289,71 +6308,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129599772</v>
+        <v>129599511</v>
       </c>
       <c r="B55" t="n">
-        <v>98727</v>
+        <v>91553</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>638399</v>
+        <v>638406</v>
       </c>
       <c r="R55" t="n">
-        <v>6634806</v>
+        <v>6634775</v>
       </c>
       <c r="S55" t="n">
         <v>4</v>
@@ -6385,7 +6390,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6395,12 +6400,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>En vinterståndare</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7455,48 +7455,53 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129605452</v>
+        <v>129597436</v>
       </c>
       <c r="B65" t="n">
-        <v>92871</v>
+        <v>57724</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>638324</v>
+        <v>638292</v>
       </c>
       <c r="R65" t="n">
-        <v>6634750</v>
+        <v>6634699</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7523,9 +7528,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7540,65 +7555,60 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129597436</v>
+        <v>129605452</v>
       </c>
       <c r="B66" t="n">
-        <v>57724</v>
+        <v>92871</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>638292</v>
+        <v>638324</v>
       </c>
       <c r="R66" t="n">
-        <v>6634699</v>
+        <v>6634750</v>
       </c>
       <c r="S66" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7625,19 +7635,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>10:38</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7652,60 +7652,60 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129601121</v>
+        <v>129605437</v>
       </c>
       <c r="B67" t="n">
-        <v>91777</v>
+        <v>92271</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1106</v>
+        <v>3298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>638329</v>
+        <v>638356</v>
       </c>
       <c r="R67" t="n">
-        <v>6634973</v>
+        <v>6634677</v>
       </c>
       <c r="S67" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7732,19 +7732,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7759,60 +7749,60 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129605437</v>
+        <v>129601121</v>
       </c>
       <c r="B68" t="n">
-        <v>92271</v>
+        <v>91777</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3298</v>
+        <v>1106</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>638356</v>
+        <v>638329</v>
       </c>
       <c r="R68" t="n">
-        <v>6634677</v>
+        <v>6634973</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7839,9 +7829,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7856,65 +7856,60 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129605449</v>
+        <v>129600760</v>
       </c>
       <c r="B69" t="n">
-        <v>4779</v>
+        <v>57724</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>638301</v>
+        <v>638304</v>
       </c>
       <c r="R69" t="n">
-        <v>6634752</v>
+        <v>6634890</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7941,14 +7936,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På äldre levande gran</t>
+          <t>Hack av spillkråka</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7957,67 +7962,71 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129600760</v>
+        <v>129605449</v>
       </c>
       <c r="B70" t="n">
-        <v>57724</v>
+        <v>4779</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>638304</v>
+        <v>638301</v>
       </c>
       <c r="R70" t="n">
-        <v>6634890</v>
+        <v>6634752</v>
       </c>
       <c r="S70" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8044,24 +8053,14 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Hack av spillkråka</t>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8070,75 +8069,67 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129602574</v>
+        <v>129598997</v>
       </c>
       <c r="B71" t="n">
-        <v>98727</v>
+        <v>92203</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>638309</v>
+        <v>638351</v>
       </c>
       <c r="R71" t="n">
-        <v>6634813</v>
+        <v>6634790</v>
       </c>
       <c r="S71" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8167,7 +8158,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8177,7 +8168,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8192,60 +8183,69 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129598997</v>
+        <v>129602574</v>
       </c>
       <c r="B72" t="n">
-        <v>92203</v>
+        <v>98727</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>638351</v>
+        <v>638309</v>
       </c>
       <c r="R72" t="n">
-        <v>6634790</v>
+        <v>6634813</v>
       </c>
       <c r="S72" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8284,7 +8284,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8299,12 +8299,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -1460,32 +1460,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129529700</v>
+        <v>129529691</v>
       </c>
       <c r="B10" t="n">
-        <v>4779</v>
+        <v>92873</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102306</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>638165</v>
+        <v>638522</v>
       </c>
       <c r="R10" t="n">
-        <v>6634993</v>
+        <v>6634845</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1531,11 +1531,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1562,32 +1557,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129529691</v>
+        <v>129529700</v>
       </c>
       <c r="B11" t="n">
-        <v>92873</v>
+        <v>4779</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>102306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1597,10 +1592,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>638522</v>
+        <v>638165</v>
       </c>
       <c r="R11" t="n">
-        <v>6634845</v>
+        <v>6634993</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1633,6 +1628,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1863,32 +1863,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129529664</v>
+        <v>129529669</v>
       </c>
       <c r="B14" t="n">
-        <v>91777</v>
+        <v>91517</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1106</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1898,10 +1898,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>638322</v>
+        <v>638445</v>
       </c>
       <c r="R14" t="n">
-        <v>6634962</v>
+        <v>6634890</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1960,32 +1960,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129529669</v>
+        <v>129529664</v>
       </c>
       <c r="B15" t="n">
-        <v>91517</v>
+        <v>91777</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>1106</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>638445</v>
+        <v>638322</v>
       </c>
       <c r="R15" t="n">
-        <v>6634890</v>
+        <v>6634962</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2256,32 +2256,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129529689</v>
+        <v>129529699</v>
       </c>
       <c r="B18" t="n">
-        <v>92827</v>
+        <v>4779</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4361</v>
+        <v>102306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2291,10 +2291,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>638468</v>
+        <v>638353</v>
       </c>
       <c r="R18" t="n">
-        <v>6634921</v>
+        <v>6634591</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2327,6 +2327,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2353,32 +2358,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129529699</v>
+        <v>129529689</v>
       </c>
       <c r="B19" t="n">
-        <v>4779</v>
+        <v>92827</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102306</v>
+        <v>4361</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2388,10 +2393,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>638353</v>
+        <v>638468</v>
       </c>
       <c r="R19" t="n">
-        <v>6634591</v>
+        <v>6634921</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2424,11 +2429,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2950,32 +2950,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129587685</v>
+        <v>129587670</v>
       </c>
       <c r="B25" t="n">
-        <v>100916</v>
+        <v>57724</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>638463</v>
+        <v>638333</v>
       </c>
       <c r="R25" t="n">
-        <v>6634889</v>
+        <v>6634980</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3047,32 +3047,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129587670</v>
+        <v>129587685</v>
       </c>
       <c r="B26" t="n">
-        <v>57724</v>
+        <v>100916</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3082,10 +3082,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>638333</v>
+        <v>638463</v>
       </c>
       <c r="R26" t="n">
-        <v>6634980</v>
+        <v>6634889</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3891,44 +3891,62 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129598714</v>
+        <v>129598966</v>
       </c>
       <c r="B34" t="n">
-        <v>91573</v>
+        <v>98727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>638323</v>
+        <v>638348</v>
       </c>
       <c r="R34" t="n">
-        <v>6634794</v>
+        <v>6634797</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3957,7 +3975,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -3967,12 +3985,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Rikligt på undersidan av döda grenar på levande äldre gran.</t>
+          <t>3 vinterståndare</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3999,7 +4017,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129598966</v>
+        <v>129599353</v>
       </c>
       <c r="B35" t="n">
         <v>98727</v>
@@ -4029,7 +4047,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4039,7 +4057,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4048,13 +4066,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>638348</v>
+        <v>638395</v>
       </c>
       <c r="R35" t="n">
-        <v>6634797</v>
+        <v>6634786</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4083,7 +4101,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4093,12 +4111,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>3 vinterståndare</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4125,62 +4138,44 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129599353</v>
+        <v>129598714</v>
       </c>
       <c r="B36" t="n">
-        <v>98727</v>
+        <v>91573</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>638395</v>
+        <v>638323</v>
       </c>
       <c r="R36" t="n">
-        <v>6634786</v>
+        <v>6634794</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4209,7 +4204,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4219,7 +4214,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Rikligt på undersidan av döda grenar på levande äldre gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4465,32 +4465,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129605436</v>
+        <v>129605441</v>
       </c>
       <c r="B39" t="n">
-        <v>96973</v>
+        <v>91326</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>53</v>
+        <v>3215</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4500,10 +4500,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>638281</v>
+        <v>638444</v>
       </c>
       <c r="R39" t="n">
-        <v>6634960</v>
+        <v>6634897</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4562,32 +4562,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129605441</v>
+        <v>129605436</v>
       </c>
       <c r="B40" t="n">
-        <v>91326</v>
+        <v>96973</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3215</v>
+        <v>53</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4597,10 +4597,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>638444</v>
+        <v>638281</v>
       </c>
       <c r="R40" t="n">
-        <v>6634897</v>
+        <v>6634960</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4659,7 +4659,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129599775</v>
+        <v>129599955</v>
       </c>
       <c r="B41" t="n">
         <v>98727</v>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4703,13 +4703,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>638435</v>
+        <v>638428</v>
       </c>
       <c r="R41" t="n">
         <v>6634839</v>
       </c>
       <c r="S41" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4775,7 +4775,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129599955</v>
+        <v>129599775</v>
       </c>
       <c r="B42" t="n">
         <v>98727</v>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4819,13 +4819,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>638428</v>
+        <v>638435</v>
       </c>
       <c r="R42" t="n">
         <v>6634839</v>
       </c>
       <c r="S42" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5017,48 +5017,62 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129602955</v>
+        <v>129598225</v>
       </c>
       <c r="B44" t="n">
-        <v>57724</v>
+        <v>98727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>638310</v>
+        <v>638330</v>
       </c>
       <c r="R44" t="n">
-        <v>6634749</v>
+        <v>6634715</v>
       </c>
       <c r="S44" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5087,7 +5101,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5097,12 +5111,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Hack av spillkråka</t>
+          <t>2 vinterståndare</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5117,19 +5131,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129601221</v>
+        <v>129599067</v>
       </c>
       <c r="B45" t="n">
         <v>98727</v>
@@ -5159,7 +5173,17 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5168,13 +5192,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>638294</v>
+        <v>638355</v>
       </c>
       <c r="R45" t="n">
-        <v>6634962</v>
+        <v>6634788</v>
       </c>
       <c r="S45" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5203,7 +5227,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5213,7 +5237,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5228,19 +5257,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129598225</v>
+        <v>129601221</v>
       </c>
       <c r="B46" t="n">
         <v>98727</v>
@@ -5270,17 +5299,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5289,13 +5308,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>638330</v>
+        <v>638294</v>
       </c>
       <c r="R46" t="n">
-        <v>6634715</v>
+        <v>6634962</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5324,7 +5343,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5334,12 +5353,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>2 vinterståndare</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5354,74 +5368,60 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129599067</v>
+        <v>129602955</v>
       </c>
       <c r="B47" t="n">
-        <v>98727</v>
+        <v>57724</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>638355</v>
+        <v>638310</v>
       </c>
       <c r="R47" t="n">
-        <v>6634788</v>
+        <v>6634749</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>En vinterståndare</t>
+          <t>Hack av spillkråka</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5480,12 +5480,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5860,48 +5860,57 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129605439</v>
+        <v>129599969</v>
       </c>
       <c r="B51" t="n">
-        <v>57724</v>
+        <v>98727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>638277</v>
+        <v>638428</v>
       </c>
       <c r="R51" t="n">
-        <v>6634933</v>
+        <v>6634835</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5928,9 +5937,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5945,12 +5964,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6204,57 +6223,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129599969</v>
+        <v>129605439</v>
       </c>
       <c r="B54" t="n">
-        <v>98727</v>
+        <v>57724</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>638428</v>
+        <v>638277</v>
       </c>
       <c r="R54" t="n">
-        <v>6634835</v>
+        <v>6634933</v>
       </c>
       <c r="S54" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6281,19 +6291,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>12:24</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6308,12 +6308,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6548,57 +6548,57 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129602720</v>
+        <v>129596091</v>
       </c>
       <c r="B57" t="n">
-        <v>98727</v>
+        <v>57724</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Orreboda, Orreboda, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>638301</v>
+        <v>638323</v>
       </c>
       <c r="R57" t="n">
-        <v>6634767</v>
+        <v>6634555</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6652,69 +6652,69 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129596091</v>
+        <v>129602720</v>
       </c>
       <c r="B58" t="n">
-        <v>57724</v>
+        <v>98727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Orreboda, Orreboda, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>638323</v>
+        <v>638301</v>
       </c>
       <c r="R58" t="n">
-        <v>6634555</v>
+        <v>6634767</v>
       </c>
       <c r="S58" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6753,7 +6753,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6768,12 +6768,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7868,48 +7868,57 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129600760</v>
+        <v>129602574</v>
       </c>
       <c r="B69" t="n">
-        <v>57724</v>
+        <v>98727</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>638304</v>
+        <v>638309</v>
       </c>
       <c r="R69" t="n">
-        <v>6634890</v>
+        <v>6634813</v>
       </c>
       <c r="S69" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7938,7 +7947,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7948,12 +7957,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:04</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Hack av spillkråka</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7980,53 +7984,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129605449</v>
+        <v>129600760</v>
       </c>
       <c r="B70" t="n">
-        <v>4779</v>
+        <v>57724</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>638301</v>
+        <v>638304</v>
       </c>
       <c r="R70" t="n">
-        <v>6634752</v>
+        <v>6634890</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8053,14 +8052,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På äldre levande gran</t>
+          <t>Hack av spillkråka</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8069,29 +8078,28 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129598997</v>
+        <v>129605449</v>
       </c>
       <c r="B71" t="n">
-        <v>92203</v>
+        <v>4779</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8099,37 +8107,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1339</v>
+        <v>102306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>638351</v>
+        <v>638301</v>
       </c>
       <c r="R71" t="n">
-        <v>6634790</v>
+        <v>6634752</v>
       </c>
       <c r="S71" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8156,19 +8169,14 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>11:45</t>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8177,75 +8185,67 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129602574</v>
+        <v>129598997</v>
       </c>
       <c r="B72" t="n">
-        <v>98727</v>
+        <v>92203</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>638309</v>
+        <v>638351</v>
       </c>
       <c r="R72" t="n">
-        <v>6634813</v>
+        <v>6634790</v>
       </c>
       <c r="S72" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8284,7 +8284,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8299,12 +8299,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -1460,32 +1460,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129529691</v>
+        <v>129529700</v>
       </c>
       <c r="B10" t="n">
-        <v>92873</v>
+        <v>4779</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>102306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>638522</v>
+        <v>638165</v>
       </c>
       <c r="R10" t="n">
-        <v>6634845</v>
+        <v>6634993</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1531,6 +1531,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1557,32 +1562,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129529700</v>
+        <v>129529691</v>
       </c>
       <c r="B11" t="n">
-        <v>4779</v>
+        <v>92873</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102306</v>
+        <v>5966</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1592,10 +1597,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>638165</v>
+        <v>638522</v>
       </c>
       <c r="R11" t="n">
-        <v>6634993</v>
+        <v>6634845</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1628,11 +1633,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1863,32 +1863,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129529669</v>
+        <v>129529664</v>
       </c>
       <c r="B14" t="n">
-        <v>91517</v>
+        <v>91777</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>1106</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1898,10 +1898,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>638445</v>
+        <v>638322</v>
       </c>
       <c r="R14" t="n">
-        <v>6634890</v>
+        <v>6634962</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1960,32 +1960,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129529664</v>
+        <v>129529669</v>
       </c>
       <c r="B15" t="n">
-        <v>91777</v>
+        <v>91517</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1106</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>638322</v>
+        <v>638445</v>
       </c>
       <c r="R15" t="n">
-        <v>6634962</v>
+        <v>6634890</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2256,32 +2256,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129529699</v>
+        <v>129529689</v>
       </c>
       <c r="B18" t="n">
-        <v>4779</v>
+        <v>92827</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102306</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2291,10 +2291,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>638353</v>
+        <v>638468</v>
       </c>
       <c r="R18" t="n">
-        <v>6634591</v>
+        <v>6634921</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2327,11 +2327,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2358,32 +2353,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129529689</v>
+        <v>129529699</v>
       </c>
       <c r="B19" t="n">
-        <v>92827</v>
+        <v>4779</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4361</v>
+        <v>102306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2393,10 +2388,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>638468</v>
+        <v>638353</v>
       </c>
       <c r="R19" t="n">
-        <v>6634921</v>
+        <v>6634591</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2429,6 +2424,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2950,32 +2950,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129587670</v>
+        <v>129587685</v>
       </c>
       <c r="B25" t="n">
-        <v>57724</v>
+        <v>100916</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>638333</v>
+        <v>638463</v>
       </c>
       <c r="R25" t="n">
-        <v>6634980</v>
+        <v>6634889</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3047,32 +3047,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129587685</v>
+        <v>129587670</v>
       </c>
       <c r="B26" t="n">
-        <v>100916</v>
+        <v>57724</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3082,10 +3082,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>638463</v>
+        <v>638333</v>
       </c>
       <c r="R26" t="n">
-        <v>6634889</v>
+        <v>6634980</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3668,48 +3668,62 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129605451</v>
+        <v>129599980</v>
       </c>
       <c r="B32" t="n">
-        <v>92871</v>
+        <v>98727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>638325</v>
+        <v>638416</v>
       </c>
       <c r="R32" t="n">
-        <v>6634691</v>
+        <v>6634840</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3736,9 +3750,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>2 vinterståndare</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3753,74 +3782,60 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129599980</v>
+        <v>129605451</v>
       </c>
       <c r="B33" t="n">
-        <v>98727</v>
+        <v>92871</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>638416</v>
+        <v>638325</v>
       </c>
       <c r="R33" t="n">
-        <v>6634840</v>
+        <v>6634691</v>
       </c>
       <c r="S33" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3847,24 +3862,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>2 vinterståndare</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3879,74 +3879,56 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129598966</v>
+        <v>129598714</v>
       </c>
       <c r="B34" t="n">
-        <v>98727</v>
+        <v>91573</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>638348</v>
+        <v>638323</v>
       </c>
       <c r="R34" t="n">
-        <v>6634797</v>
+        <v>6634794</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3975,7 +3957,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -3985,12 +3967,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>3 vinterståndare</t>
+          <t>Rikligt på undersidan av döda grenar på levande äldre gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4017,7 +3999,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129599353</v>
+        <v>129598966</v>
       </c>
       <c r="B35" t="n">
         <v>98727</v>
@@ -4047,7 +4029,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4057,7 +4039,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4066,13 +4048,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>638395</v>
+        <v>638348</v>
       </c>
       <c r="R35" t="n">
-        <v>6634786</v>
+        <v>6634797</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4101,7 +4083,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4111,7 +4093,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>3 vinterståndare</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4138,44 +4125,62 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129598714</v>
+        <v>129599353</v>
       </c>
       <c r="B36" t="n">
-        <v>91573</v>
+        <v>98727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>638323</v>
+        <v>638395</v>
       </c>
       <c r="R36" t="n">
-        <v>6634794</v>
+        <v>6634786</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4204,7 +4209,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4214,12 +4219,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:29</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Rikligt på undersidan av döda grenar på levande äldre gran.</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4659,7 +4659,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129599955</v>
+        <v>129599775</v>
       </c>
       <c r="B41" t="n">
         <v>98727</v>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4703,13 +4703,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>638428</v>
+        <v>638435</v>
       </c>
       <c r="R41" t="n">
         <v>6634839</v>
       </c>
       <c r="S41" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4775,7 +4775,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129599775</v>
+        <v>129599955</v>
       </c>
       <c r="B42" t="n">
         <v>98727</v>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4819,13 +4819,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>638435</v>
+        <v>638428</v>
       </c>
       <c r="R42" t="n">
         <v>6634839</v>
       </c>
       <c r="S42" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5017,62 +5017,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129598225</v>
+        <v>129602955</v>
       </c>
       <c r="B44" t="n">
-        <v>98727</v>
+        <v>57724</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>638330</v>
+        <v>638310</v>
       </c>
       <c r="R44" t="n">
-        <v>6634715</v>
+        <v>6634749</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5101,7 +5087,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5111,12 +5097,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>2 vinterståndare</t>
+          <t>Hack av spillkråka</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5131,19 +5117,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129599067</v>
+        <v>129598225</v>
       </c>
       <c r="B45" t="n">
         <v>98727</v>
@@ -5173,7 +5159,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5192,13 +5178,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>638355</v>
+        <v>638330</v>
       </c>
       <c r="R45" t="n">
-        <v>6634788</v>
+        <v>6634715</v>
       </c>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5227,7 +5213,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5237,12 +5223,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>En vinterståndare</t>
+          <t>2 vinterståndare</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5269,7 +5255,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129601221</v>
+        <v>129599067</v>
       </c>
       <c r="B46" t="n">
         <v>98727</v>
@@ -5299,7 +5285,17 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5308,13 +5304,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>638294</v>
+        <v>638355</v>
       </c>
       <c r="R46" t="n">
-        <v>6634962</v>
+        <v>6634788</v>
       </c>
       <c r="S46" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5343,7 +5339,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5353,7 +5349,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5368,60 +5369,64 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129602955</v>
+        <v>129601221</v>
       </c>
       <c r="B47" t="n">
-        <v>57724</v>
+        <v>98727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>638310</v>
+        <v>638294</v>
       </c>
       <c r="R47" t="n">
-        <v>6634749</v>
+        <v>6634962</v>
       </c>
       <c r="S47" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5450,7 +5455,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5460,12 +5465,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Hack av spillkråka</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6223,10 +6223,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129605439</v>
+        <v>129599511</v>
       </c>
       <c r="B54" t="n">
-        <v>57724</v>
+        <v>91553</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6234,37 +6234,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>638277</v>
+        <v>638406</v>
       </c>
       <c r="R54" t="n">
-        <v>6634933</v>
+        <v>6634775</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6291,9 +6291,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6308,22 +6318,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129599511</v>
+        <v>129605439</v>
       </c>
       <c r="B55" t="n">
-        <v>91553</v>
+        <v>57724</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6331,37 +6341,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>638406</v>
+        <v>638277</v>
       </c>
       <c r="R55" t="n">
-        <v>6634775</v>
+        <v>6634933</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6388,19 +6398,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>12:05</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6415,12 +6415,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6548,57 +6548,57 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129596091</v>
+        <v>129602720</v>
       </c>
       <c r="B57" t="n">
-        <v>57724</v>
+        <v>98727</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Orreboda, Orreboda, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>638323</v>
+        <v>638301</v>
       </c>
       <c r="R57" t="n">
-        <v>6634555</v>
+        <v>6634767</v>
       </c>
       <c r="S57" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6652,69 +6652,69 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129602720</v>
+        <v>129596091</v>
       </c>
       <c r="B58" t="n">
-        <v>98727</v>
+        <v>57724</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Orreboda, Orreboda, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>638301</v>
+        <v>638323</v>
       </c>
       <c r="R58" t="n">
-        <v>6634767</v>
+        <v>6634555</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6753,7 +6753,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6768,12 +6768,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6989,7 +6989,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129601983</v>
+        <v>129602223</v>
       </c>
       <c r="B61" t="n">
         <v>98727</v>
@@ -7019,17 +7019,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7038,13 +7033,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>638209</v>
+        <v>638236</v>
       </c>
       <c r="R61" t="n">
-        <v>6635047</v>
+        <v>6634982</v>
       </c>
       <c r="S61" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7073,7 +7068,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7083,7 +7078,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7098,19 +7093,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129602223</v>
+        <v>129601983</v>
       </c>
       <c r="B62" t="n">
         <v>98727</v>
@@ -7140,12 +7135,17 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7154,13 +7154,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>638236</v>
+        <v>638209</v>
       </c>
       <c r="R62" t="n">
-        <v>6634982</v>
+        <v>6635047</v>
       </c>
       <c r="S62" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7214,12 +7214,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7664,48 +7664,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129605437</v>
+        <v>129601121</v>
       </c>
       <c r="B67" t="n">
-        <v>92271</v>
+        <v>91777</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3298</v>
+        <v>1106</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>638356</v>
+        <v>638329</v>
       </c>
       <c r="R67" t="n">
-        <v>6634677</v>
+        <v>6634973</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7732,9 +7732,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7749,60 +7759,60 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129601121</v>
+        <v>129605437</v>
       </c>
       <c r="B68" t="n">
-        <v>91777</v>
+        <v>92271</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1106</v>
+        <v>3298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>638329</v>
+        <v>638356</v>
       </c>
       <c r="R68" t="n">
-        <v>6634973</v>
+        <v>6634677</v>
       </c>
       <c r="S68" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7829,19 +7839,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7856,69 +7856,60 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129602574</v>
+        <v>129598997</v>
       </c>
       <c r="B69" t="n">
-        <v>98727</v>
+        <v>92203</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>638309</v>
+        <v>638351</v>
       </c>
       <c r="R69" t="n">
-        <v>6634813</v>
+        <v>6634790</v>
       </c>
       <c r="S69" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7947,7 +7938,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7957,7 +7948,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7972,12 +7963,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -8204,48 +8195,57 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129598997</v>
+        <v>129602574</v>
       </c>
       <c r="B72" t="n">
-        <v>92203</v>
+        <v>98727</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>638351</v>
+        <v>638309</v>
       </c>
       <c r="R72" t="n">
-        <v>6634790</v>
+        <v>6634813</v>
       </c>
       <c r="S72" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8284,7 +8284,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8299,12 +8299,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -978,7 +978,7 @@
         <v>129529667</v>
       </c>
       <c r="B5" t="n">
-        <v>96973</v>
+        <v>97002</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>129529690</v>
       </c>
       <c r="B6" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>129529673</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>129529684</v>
       </c>
       <c r="B8" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>129529697</v>
       </c>
       <c r="B9" t="n">
-        <v>90935</v>
+        <v>90963</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1460,32 +1460,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129529700</v>
+        <v>129529691</v>
       </c>
       <c r="B10" t="n">
-        <v>4779</v>
+        <v>92901</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102306</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>638165</v>
+        <v>638522</v>
       </c>
       <c r="R10" t="n">
-        <v>6634993</v>
+        <v>6634845</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1531,11 +1531,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1562,32 +1557,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129529691</v>
+        <v>129529700</v>
       </c>
       <c r="B11" t="n">
-        <v>92873</v>
+        <v>4779</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>102306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1597,10 +1592,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>638522</v>
+        <v>638165</v>
       </c>
       <c r="R11" t="n">
-        <v>6634845</v>
+        <v>6634993</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1633,6 +1628,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1866,7 +1866,7 @@
         <v>129529664</v>
       </c>
       <c r="B14" t="n">
-        <v>91777</v>
+        <v>91805</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>129529669</v>
       </c>
       <c r="B15" t="n">
-        <v>91517</v>
+        <v>91545</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>129529682</v>
       </c>
       <c r="B16" t="n">
-        <v>91326</v>
+        <v>91354</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>129529668</v>
       </c>
       <c r="B17" t="n">
-        <v>96973</v>
+        <v>97002</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>129529689</v>
       </c>
       <c r="B18" t="n">
-        <v>92827</v>
+        <v>92855</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>129529679</v>
       </c>
       <c r="B20" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>129587678</v>
       </c>
       <c r="B21" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>129587673</v>
       </c>
       <c r="B22" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>129587679</v>
       </c>
       <c r="B23" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>129587676</v>
       </c>
       <c r="B24" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2950,32 +2950,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129587685</v>
+        <v>129587670</v>
       </c>
       <c r="B25" t="n">
-        <v>100916</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>638463</v>
+        <v>638333</v>
       </c>
       <c r="R25" t="n">
-        <v>6634889</v>
+        <v>6634980</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3047,32 +3047,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129587670</v>
+        <v>129587685</v>
       </c>
       <c r="B26" t="n">
-        <v>57724</v>
+        <v>100945</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3082,10 +3082,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>638333</v>
+        <v>638463</v>
       </c>
       <c r="R26" t="n">
-        <v>6634980</v>
+        <v>6634889</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3147,7 +3147,7 @@
         <v>129587677</v>
       </c>
       <c r="B27" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>129587681</v>
       </c>
       <c r="B28" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>129587667</v>
       </c>
       <c r="B29" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>129597548</v>
       </c>
       <c r="B30" t="n">
-        <v>96973</v>
+        <v>97002</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>129598790</v>
       </c>
       <c r="B31" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>129599980</v>
       </c>
       <c r="B32" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>129605451</v>
       </c>
       <c r="B33" t="n">
-        <v>92871</v>
+        <v>92899</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>129598714</v>
       </c>
       <c r="B34" t="n">
-        <v>91573</v>
+        <v>91601</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>129598966</v>
       </c>
       <c r="B35" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>129599353</v>
       </c>
       <c r="B36" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4246,53 +4246,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129599884</v>
+        <v>129599503</v>
       </c>
       <c r="B37" t="n">
-        <v>57724</v>
+        <v>98756</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>638397</v>
+        <v>638325</v>
       </c>
       <c r="R37" t="n">
-        <v>6634819</v>
+        <v>6634846</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4321,7 +4316,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4331,7 +4326,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4346,60 +4341,65 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Broms</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Broms</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129599503</v>
+        <v>129599884</v>
       </c>
       <c r="B38" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>638325</v>
+        <v>638397</v>
       </c>
       <c r="R38" t="n">
-        <v>6634846</v>
+        <v>6634819</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4453,12 +4453,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anders Broms</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anders Broms</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4468,7 +4468,7 @@
         <v>129605441</v>
       </c>
       <c r="B39" t="n">
-        <v>91326</v>
+        <v>91354</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
         <v>129605436</v>
       </c>
       <c r="B40" t="n">
-        <v>96973</v>
+        <v>97002</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>129599775</v>
       </c>
       <c r="B41" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>129599955</v>
       </c>
       <c r="B42" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>129597954</v>
       </c>
       <c r="B43" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5017,48 +5017,52 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129602955</v>
+        <v>129601221</v>
       </c>
       <c r="B44" t="n">
-        <v>57724</v>
+        <v>98756</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>638310</v>
+        <v>638294</v>
       </c>
       <c r="R44" t="n">
-        <v>6634749</v>
+        <v>6634962</v>
       </c>
       <c r="S44" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5087,7 +5091,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5097,12 +5101,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Hack av spillkråka</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5129,62 +5128,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129598225</v>
+        <v>129602955</v>
       </c>
       <c r="B45" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>638330</v>
+        <v>638310</v>
       </c>
       <c r="R45" t="n">
-        <v>6634715</v>
+        <v>6634749</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5213,7 +5198,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5223,12 +5208,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>2 vinterståndare</t>
+          <t>Hack av spillkråka</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5243,22 +5228,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129599067</v>
+        <v>129598225</v>
       </c>
       <c r="B46" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5285,7 +5270,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5304,13 +5289,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>638355</v>
+        <v>638330</v>
       </c>
       <c r="R46" t="n">
-        <v>6634788</v>
+        <v>6634715</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5339,7 +5324,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5349,12 +5334,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>En vinterståndare</t>
+          <t>2 vinterståndare</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5381,10 +5366,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129601221</v>
+        <v>129599067</v>
       </c>
       <c r="B47" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5411,7 +5396,17 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5420,13 +5415,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>638294</v>
+        <v>638355</v>
       </c>
       <c r="R47" t="n">
-        <v>6634962</v>
+        <v>6634788</v>
       </c>
       <c r="S47" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5455,7 +5450,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5465,7 +5460,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5480,12 +5480,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5495,7 +5495,7 @@
         <v>129600150</v>
       </c>
       <c r="B48" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>129602684</v>
       </c>
       <c r="B49" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>129602225</v>
       </c>
       <c r="B50" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5860,57 +5860,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129599969</v>
+        <v>129599511</v>
       </c>
       <c r="B51" t="n">
-        <v>98727</v>
+        <v>91581</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>638428</v>
+        <v>638406</v>
       </c>
       <c r="R51" t="n">
-        <v>6634835</v>
+        <v>6634775</v>
       </c>
       <c r="S51" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5939,7 +5930,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5949,7 +5940,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5964,22 +5955,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129599963</v>
+        <v>129599969</v>
       </c>
       <c r="B52" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6011,12 +6002,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6025,13 +6011,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>638420</v>
+        <v>638428</v>
       </c>
       <c r="R52" t="n">
-        <v>6634840</v>
+        <v>6634835</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6085,22 +6071,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129599772</v>
+        <v>129599963</v>
       </c>
       <c r="B53" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6127,7 +6113,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6137,7 +6123,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6146,13 +6132,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>638399</v>
+        <v>638420</v>
       </c>
       <c r="R53" t="n">
-        <v>6634806</v>
+        <v>6634840</v>
       </c>
       <c r="S53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6181,7 +6167,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6191,12 +6177,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>En vinterståndare</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6223,45 +6204,59 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129599511</v>
+        <v>129599772</v>
       </c>
       <c r="B54" t="n">
-        <v>91553</v>
+        <v>98756</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>638406</v>
+        <v>638399</v>
       </c>
       <c r="R54" t="n">
-        <v>6634775</v>
+        <v>6634806</v>
       </c>
       <c r="S54" t="n">
         <v>4</v>
@@ -6293,7 +6288,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6303,7 +6298,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6333,7 +6333,7 @@
         <v>129605439</v>
       </c>
       <c r="B55" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         <v>129602370</v>
       </c>
       <c r="B56" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6548,57 +6548,57 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129602720</v>
+        <v>129596091</v>
       </c>
       <c r="B57" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Orreboda, Orreboda, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>638301</v>
+        <v>638323</v>
       </c>
       <c r="R57" t="n">
-        <v>6634767</v>
+        <v>6634555</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6652,69 +6652,69 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129596091</v>
+        <v>129602720</v>
       </c>
       <c r="B58" t="n">
-        <v>57724</v>
+        <v>98756</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Orreboda, Orreboda, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>638323</v>
+        <v>638301</v>
       </c>
       <c r="R58" t="n">
-        <v>6634555</v>
+        <v>6634767</v>
       </c>
       <c r="S58" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6753,7 +6753,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6768,12 +6768,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6783,7 +6783,7 @@
         <v>129600817</v>
       </c>
       <c r="B59" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         <v>129605440</v>
       </c>
       <c r="B60" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6989,10 +6989,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129602223</v>
+        <v>129601983</v>
       </c>
       <c r="B61" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7019,12 +7019,17 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7033,13 +7038,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>638236</v>
+        <v>638209</v>
       </c>
       <c r="R61" t="n">
-        <v>6634982</v>
+        <v>6635047</v>
       </c>
       <c r="S61" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7068,7 +7073,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7078,7 +7083,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7093,22 +7098,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129601983</v>
+        <v>129602223</v>
       </c>
       <c r="B62" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7135,17 +7140,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7154,13 +7154,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>638209</v>
+        <v>638236</v>
       </c>
       <c r="R62" t="n">
-        <v>6635047</v>
+        <v>6634982</v>
       </c>
       <c r="S62" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7214,12 +7214,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7229,7 +7229,7 @@
         <v>129600091</v>
       </c>
       <c r="B63" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>129597436</v>
       </c>
       <c r="B65" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>129605452</v>
       </c>
       <c r="B66" t="n">
-        <v>92871</v>
+        <v>92899</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7667,7 +7667,7 @@
         <v>129601121</v>
       </c>
       <c r="B67" t="n">
-        <v>91777</v>
+        <v>91805</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         <v>129605437</v>
       </c>
       <c r="B68" t="n">
-        <v>92271</v>
+        <v>92299</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
         <v>129598997</v>
       </c>
       <c r="B69" t="n">
-        <v>92203</v>
+        <v>92231</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7975,48 +7975,53 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129600760</v>
+        <v>129605449</v>
       </c>
       <c r="B70" t="n">
-        <v>57724</v>
+        <v>4779</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>638304</v>
+        <v>638301</v>
       </c>
       <c r="R70" t="n">
-        <v>6634890</v>
+        <v>6634752</v>
       </c>
       <c r="S70" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8043,24 +8048,14 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Hack av spillkråka</t>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8069,71 +8064,67 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129605449</v>
+        <v>129600760</v>
       </c>
       <c r="B71" t="n">
-        <v>4779</v>
+        <v>57727</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>638301</v>
+        <v>638304</v>
       </c>
       <c r="R71" t="n">
-        <v>6634752</v>
+        <v>6634890</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8160,14 +8151,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På äldre levande gran</t>
+          <t>Hack av spillkråka</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8176,19 +8177,18 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -8198,7 +8198,7 @@
         <v>129602574</v>
       </c>
       <c r="B72" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -3440,48 +3440,62 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129597548</v>
+        <v>129598790</v>
       </c>
       <c r="B30" t="n">
-        <v>97002</v>
+        <v>98756</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>638336</v>
+        <v>638333</v>
       </c>
       <c r="R30" t="n">
-        <v>6634702</v>
+        <v>6634812</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3510,7 +3524,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3520,7 +3534,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3547,62 +3561,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129598790</v>
+        <v>129597548</v>
       </c>
       <c r="B31" t="n">
-        <v>98756</v>
+        <v>97002</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>638333</v>
+        <v>638336</v>
       </c>
       <c r="R31" t="n">
-        <v>6634812</v>
+        <v>6634702</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4465,32 +4465,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129605441</v>
+        <v>129605436</v>
       </c>
       <c r="B39" t="n">
-        <v>91354</v>
+        <v>97002</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3215</v>
+        <v>53</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4500,10 +4500,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>638444</v>
+        <v>638281</v>
       </c>
       <c r="R39" t="n">
-        <v>6634897</v>
+        <v>6634960</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4562,32 +4562,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129605436</v>
+        <v>129605441</v>
       </c>
       <c r="B40" t="n">
-        <v>97002</v>
+        <v>91354</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>53</v>
+        <v>3215</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4597,10 +4597,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>638281</v>
+        <v>638444</v>
       </c>
       <c r="R40" t="n">
-        <v>6634960</v>
+        <v>6634897</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -6780,38 +6780,47 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129600817</v>
+        <v>129601983</v>
       </c>
       <c r="B59" t="n">
-        <v>57727</v>
+        <v>98756</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6820,10 +6829,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>638230</v>
+        <v>638209</v>
       </c>
       <c r="R59" t="n">
-        <v>6634962</v>
+        <v>6635047</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -6855,7 +6864,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6865,7 +6874,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6892,48 +6901,57 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129605440</v>
+        <v>129602223</v>
       </c>
       <c r="B60" t="n">
-        <v>57727</v>
+        <v>98756</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>638309</v>
+        <v>638236</v>
       </c>
       <c r="R60" t="n">
-        <v>6634908</v>
+        <v>6634982</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6960,9 +6978,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6977,59 +7005,50 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129601983</v>
+        <v>129600817</v>
       </c>
       <c r="B61" t="n">
-        <v>98756</v>
+        <v>57727</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7038,10 +7057,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>638209</v>
+        <v>638230</v>
       </c>
       <c r="R61" t="n">
-        <v>6635047</v>
+        <v>6634962</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
@@ -7073,7 +7092,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7083,7 +7102,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7110,57 +7129,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129602223</v>
+        <v>129605440</v>
       </c>
       <c r="B62" t="n">
-        <v>98756</v>
+        <v>57727</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>638236</v>
+        <v>638309</v>
       </c>
       <c r="R62" t="n">
-        <v>6634982</v>
+        <v>6634908</v>
       </c>
       <c r="S62" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7187,19 +7197,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>14:09</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7214,12 +7214,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -978,7 +978,7 @@
         <v>129529667</v>
       </c>
       <c r="B5" t="n">
-        <v>97002</v>
+        <v>97014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>129529690</v>
       </c>
       <c r="B6" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>129529673</v>
       </c>
       <c r="B7" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>129529684</v>
       </c>
       <c r="B8" t="n">
-        <v>92034</v>
+        <v>92040</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>129529697</v>
       </c>
       <c r="B9" t="n">
-        <v>90963</v>
+        <v>90969</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1460,32 +1460,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129529691</v>
+        <v>129529700</v>
       </c>
       <c r="B10" t="n">
-        <v>92901</v>
+        <v>4779</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>102306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>638522</v>
+        <v>638165</v>
       </c>
       <c r="R10" t="n">
-        <v>6634845</v>
+        <v>6634993</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1531,6 +1531,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1557,32 +1562,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129529700</v>
+        <v>129529691</v>
       </c>
       <c r="B11" t="n">
-        <v>4779</v>
+        <v>92907</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102306</v>
+        <v>5966</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1592,10 +1597,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>638165</v>
+        <v>638522</v>
       </c>
       <c r="R11" t="n">
-        <v>6634993</v>
+        <v>6634845</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1628,11 +1633,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1866,7 +1866,7 @@
         <v>129529664</v>
       </c>
       <c r="B14" t="n">
-        <v>91805</v>
+        <v>91811</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>129529669</v>
       </c>
       <c r="B15" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>129529682</v>
       </c>
       <c r="B16" t="n">
-        <v>91354</v>
+        <v>91360</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>129529668</v>
       </c>
       <c r="B17" t="n">
-        <v>97002</v>
+        <v>97014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>129529689</v>
       </c>
       <c r="B18" t="n">
-        <v>92855</v>
+        <v>92861</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>129529679</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>129587678</v>
       </c>
       <c r="B21" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>129587673</v>
       </c>
       <c r="B22" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>129587679</v>
       </c>
       <c r="B23" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>129587676</v>
       </c>
       <c r="B24" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>129587670</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>129587685</v>
       </c>
       <c r="B26" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>129587677</v>
       </c>
       <c r="B27" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>129587681</v>
       </c>
       <c r="B28" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>129587667</v>
       </c>
       <c r="B29" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3440,62 +3440,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129598790</v>
+        <v>129597548</v>
       </c>
       <c r="B30" t="n">
-        <v>98756</v>
+        <v>97014</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>638333</v>
+        <v>638336</v>
       </c>
       <c r="R30" t="n">
-        <v>6634812</v>
+        <v>6634702</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3524,7 +3510,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3534,7 +3520,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3561,48 +3547,62 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129597548</v>
+        <v>129598790</v>
       </c>
       <c r="B31" t="n">
-        <v>97002</v>
+        <v>98768</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>638336</v>
+        <v>638333</v>
       </c>
       <c r="R31" t="n">
-        <v>6634702</v>
+        <v>6634812</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3671,7 +3671,7 @@
         <v>129599980</v>
       </c>
       <c r="B32" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>129605451</v>
       </c>
       <c r="B33" t="n">
-        <v>92899</v>
+        <v>92905</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>129598714</v>
       </c>
       <c r="B34" t="n">
-        <v>91601</v>
+        <v>91607</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>129598966</v>
       </c>
       <c r="B35" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>129599353</v>
       </c>
       <c r="B36" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4246,48 +4246,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129599503</v>
+        <v>129599884</v>
       </c>
       <c r="B37" t="n">
-        <v>98756</v>
+        <v>57732</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>638325</v>
+        <v>638397</v>
       </c>
       <c r="R37" t="n">
-        <v>6634846</v>
+        <v>6634819</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4316,7 +4321,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4326,7 +4331,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4341,65 +4346,60 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anders Broms</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anders Broms</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129599884</v>
+        <v>129599503</v>
       </c>
       <c r="B38" t="n">
-        <v>57727</v>
+        <v>98768</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>638397</v>
+        <v>638325</v>
       </c>
       <c r="R38" t="n">
-        <v>6634819</v>
+        <v>6634846</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4453,12 +4453,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Broms</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Broms</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4468,7 +4468,7 @@
         <v>129605436</v>
       </c>
       <c r="B39" t="n">
-        <v>97002</v>
+        <v>97014</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
         <v>129605441</v>
       </c>
       <c r="B40" t="n">
-        <v>91354</v>
+        <v>91360</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>129599775</v>
       </c>
       <c r="B41" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4775,10 +4775,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129599955</v>
+        <v>129597954</v>
       </c>
       <c r="B42" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4805,12 +4805,17 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4819,13 +4824,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>638428</v>
+        <v>638325</v>
       </c>
       <c r="R42" t="n">
-        <v>6634839</v>
+        <v>6634719</v>
       </c>
       <c r="S42" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4854,7 +4859,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4864,7 +4869,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>3 vinterståndare</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4879,22 +4889,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129597954</v>
+        <v>129599955</v>
       </c>
       <c r="B43" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4921,17 +4931,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4940,13 +4945,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>638325</v>
+        <v>638428</v>
       </c>
       <c r="R43" t="n">
-        <v>6634719</v>
+        <v>6634839</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4975,7 +4980,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -4985,12 +4990,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>3 vinterståndare</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5005,64 +5005,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129601221</v>
+        <v>129602955</v>
       </c>
       <c r="B44" t="n">
-        <v>98756</v>
+        <v>57732</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>638294</v>
+        <v>638310</v>
       </c>
       <c r="R44" t="n">
-        <v>6634962</v>
+        <v>6634749</v>
       </c>
       <c r="S44" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5091,7 +5087,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5101,7 +5097,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Hack av spillkråka</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5128,48 +5129,62 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129602955</v>
+        <v>129598225</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>98768</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>638310</v>
+        <v>638330</v>
       </c>
       <c r="R45" t="n">
-        <v>6634749</v>
+        <v>6634715</v>
       </c>
       <c r="S45" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5198,7 +5213,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5208,12 +5223,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Hack av spillkråka</t>
+          <t>2 vinterståndare</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5228,22 +5243,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129598225</v>
+        <v>129599067</v>
       </c>
       <c r="B46" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5270,7 +5285,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5289,13 +5304,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>638330</v>
+        <v>638355</v>
       </c>
       <c r="R46" t="n">
-        <v>6634715</v>
+        <v>6634788</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5324,7 +5339,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5334,12 +5349,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>2 vinterståndare</t>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5366,10 +5381,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129599067</v>
+        <v>129601221</v>
       </c>
       <c r="B47" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5396,17 +5411,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5415,13 +5420,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>638355</v>
+        <v>638294</v>
       </c>
       <c r="R47" t="n">
-        <v>6634788</v>
+        <v>6634962</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5450,7 +5455,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5460,12 +5465,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>En vinterståndare</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5480,12 +5480,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5495,7 +5495,7 @@
         <v>129600150</v>
       </c>
       <c r="B48" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>129602684</v>
       </c>
       <c r="B49" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>129602225</v>
       </c>
       <c r="B50" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5860,10 +5860,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129599511</v>
+        <v>129605439</v>
       </c>
       <c r="B51" t="n">
-        <v>91581</v>
+        <v>57732</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5871,37 +5871,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>638406</v>
+        <v>638277</v>
       </c>
       <c r="R51" t="n">
-        <v>6634775</v>
+        <v>6634933</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5928,19 +5928,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>12:05</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5955,12 +5945,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5970,7 +5960,7 @@
         <v>129599969</v>
       </c>
       <c r="B52" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6086,7 +6076,7 @@
         <v>129599963</v>
       </c>
       <c r="B53" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6207,7 +6197,7 @@
         <v>129599772</v>
       </c>
       <c r="B54" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6330,10 +6320,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129605439</v>
+        <v>129599511</v>
       </c>
       <c r="B55" t="n">
-        <v>57727</v>
+        <v>91587</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6341,37 +6331,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>638277</v>
+        <v>638406</v>
       </c>
       <c r="R55" t="n">
-        <v>6634933</v>
+        <v>6634775</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6398,9 +6388,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6415,12 +6415,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6430,7 +6430,7 @@
         <v>129602370</v>
       </c>
       <c r="B56" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6551,7 +6551,7 @@
         <v>129596091</v>
       </c>
       <c r="B57" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>129602720</v>
       </c>
       <c r="B58" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6780,62 +6780,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129601983</v>
+        <v>129605440</v>
       </c>
       <c r="B59" t="n">
-        <v>98756</v>
+        <v>57732</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>638209</v>
+        <v>638309</v>
       </c>
       <c r="R59" t="n">
-        <v>6635047</v>
+        <v>6634908</v>
       </c>
       <c r="S59" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6862,19 +6848,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>13:56</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6889,54 +6865,50 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129602223</v>
+        <v>129600817</v>
       </c>
       <c r="B60" t="n">
-        <v>98756</v>
+        <v>57732</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6945,13 +6917,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>638236</v>
+        <v>638230</v>
       </c>
       <c r="R60" t="n">
-        <v>6634982</v>
+        <v>6634962</v>
       </c>
       <c r="S60" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6980,7 +6952,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6990,7 +6962,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7005,50 +6977,59 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129600817</v>
+        <v>129601983</v>
       </c>
       <c r="B61" t="n">
-        <v>57727</v>
+        <v>98768</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7057,10 +7038,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>638230</v>
+        <v>638209</v>
       </c>
       <c r="R61" t="n">
-        <v>6634962</v>
+        <v>6635047</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
@@ -7092,7 +7073,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7102,7 +7083,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7129,48 +7110,57 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129605440</v>
+        <v>129602223</v>
       </c>
       <c r="B62" t="n">
-        <v>57727</v>
+        <v>98768</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>638309</v>
+        <v>638236</v>
       </c>
       <c r="R62" t="n">
-        <v>6634908</v>
+        <v>6634982</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7197,9 +7187,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7214,12 +7214,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7229,7 +7229,7 @@
         <v>129600091</v>
       </c>
       <c r="B63" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>129597436</v>
       </c>
       <c r="B65" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>129605452</v>
       </c>
       <c r="B66" t="n">
-        <v>92899</v>
+        <v>92905</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7667,7 +7667,7 @@
         <v>129601121</v>
       </c>
       <c r="B67" t="n">
-        <v>91805</v>
+        <v>91811</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         <v>129605437</v>
       </c>
       <c r="B68" t="n">
-        <v>92299</v>
+        <v>92305</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7868,32 +7868,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129598997</v>
+        <v>129600760</v>
       </c>
       <c r="B69" t="n">
-        <v>92231</v>
+        <v>57732</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7903,13 +7903,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>638351</v>
+        <v>638304</v>
       </c>
       <c r="R69" t="n">
-        <v>6634790</v>
+        <v>6634890</v>
       </c>
       <c r="S69" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7948,7 +7948,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Hack av spillkråka</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7963,12 +7968,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -8083,32 +8088,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129600760</v>
+        <v>129598997</v>
       </c>
       <c r="B71" t="n">
-        <v>57727</v>
+        <v>92237</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8118,13 +8123,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>638304</v>
+        <v>638351</v>
       </c>
       <c r="R71" t="n">
-        <v>6634890</v>
+        <v>6634790</v>
       </c>
       <c r="S71" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8153,7 +8158,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8163,12 +8168,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:04</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Hack av spillkråka</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8183,12 +8183,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -8198,7 +8198,7 @@
         <v>129602574</v>
       </c>
       <c r="B72" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -978,7 +978,7 @@
         <v>129529667</v>
       </c>
       <c r="B5" t="n">
-        <v>97014</v>
+        <v>97015</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>129529690</v>
       </c>
       <c r="B6" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>129529673</v>
       </c>
       <c r="B7" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>129529684</v>
       </c>
       <c r="B8" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>129529697</v>
       </c>
       <c r="B9" t="n">
-        <v>90969</v>
+        <v>90970</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1460,32 +1460,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129529700</v>
+        <v>129529691</v>
       </c>
       <c r="B10" t="n">
-        <v>4779</v>
+        <v>92908</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102306</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>638165</v>
+        <v>638522</v>
       </c>
       <c r="R10" t="n">
-        <v>6634993</v>
+        <v>6634845</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1531,11 +1531,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1562,32 +1557,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129529691</v>
+        <v>129529700</v>
       </c>
       <c r="B11" t="n">
-        <v>92907</v>
+        <v>4779</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>102306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1597,10 +1592,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>638522</v>
+        <v>638165</v>
       </c>
       <c r="R11" t="n">
-        <v>6634845</v>
+        <v>6634993</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1633,6 +1628,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1863,32 +1863,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129529664</v>
+        <v>129529669</v>
       </c>
       <c r="B14" t="n">
-        <v>91811</v>
+        <v>91552</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1106</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1898,10 +1898,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>638322</v>
+        <v>638445</v>
       </c>
       <c r="R14" t="n">
-        <v>6634962</v>
+        <v>6634890</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1960,32 +1960,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129529669</v>
+        <v>129529664</v>
       </c>
       <c r="B15" t="n">
-        <v>91551</v>
+        <v>91812</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>1106</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>638445</v>
+        <v>638322</v>
       </c>
       <c r="R15" t="n">
-        <v>6634890</v>
+        <v>6634962</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2060,7 +2060,7 @@
         <v>129529682</v>
       </c>
       <c r="B16" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>129529668</v>
       </c>
       <c r="B17" t="n">
-        <v>97014</v>
+        <v>97015</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2256,32 +2256,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129529689</v>
+        <v>129529699</v>
       </c>
       <c r="B18" t="n">
-        <v>92861</v>
+        <v>4779</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4361</v>
+        <v>102306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2291,10 +2291,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>638468</v>
+        <v>638353</v>
       </c>
       <c r="R18" t="n">
-        <v>6634921</v>
+        <v>6634591</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2327,6 +2327,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2353,32 +2358,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129529699</v>
+        <v>129529689</v>
       </c>
       <c r="B19" t="n">
-        <v>4779</v>
+        <v>92862</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102306</v>
+        <v>4361</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2388,10 +2393,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>638353</v>
+        <v>638468</v>
       </c>
       <c r="R19" t="n">
-        <v>6634591</v>
+        <v>6634921</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2424,11 +2429,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2458,7 +2458,7 @@
         <v>129529679</v>
       </c>
       <c r="B20" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>129587678</v>
       </c>
       <c r="B21" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>129587673</v>
       </c>
       <c r="B22" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>129587679</v>
       </c>
       <c r="B23" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>129587676</v>
       </c>
       <c r="B24" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>129587670</v>
       </c>
       <c r="B25" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>129587685</v>
       </c>
       <c r="B26" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3144,10 +3144,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129587677</v>
+        <v>129587681</v>
       </c>
       <c r="B27" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>638447</v>
+        <v>638468</v>
       </c>
       <c r="R27" t="n">
-        <v>6634803</v>
+        <v>6634929</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3215,11 +3215,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3246,10 +3241,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129587681</v>
+        <v>129587677</v>
       </c>
       <c r="B28" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3281,10 +3276,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>638468</v>
+        <v>638447</v>
       </c>
       <c r="R28" t="n">
-        <v>6634929</v>
+        <v>6634803</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3317,6 +3312,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3346,7 +3346,7 @@
         <v>129587667</v>
       </c>
       <c r="B29" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3440,48 +3440,62 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129597548</v>
+        <v>129598790</v>
       </c>
       <c r="B30" t="n">
-        <v>97014</v>
+        <v>98769</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>638336</v>
+        <v>638333</v>
       </c>
       <c r="R30" t="n">
-        <v>6634702</v>
+        <v>6634812</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3510,7 +3524,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3520,7 +3534,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3547,62 +3561,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129598790</v>
+        <v>129597548</v>
       </c>
       <c r="B31" t="n">
-        <v>98768</v>
+        <v>97015</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>638333</v>
+        <v>638336</v>
       </c>
       <c r="R31" t="n">
-        <v>6634812</v>
+        <v>6634702</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3668,62 +3668,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129599980</v>
+        <v>129605451</v>
       </c>
       <c r="B32" t="n">
-        <v>98768</v>
+        <v>92906</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>638416</v>
+        <v>638325</v>
       </c>
       <c r="R32" t="n">
-        <v>6634840</v>
+        <v>6634691</v>
       </c>
       <c r="S32" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3750,24 +3736,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>2 vinterståndare</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3782,60 +3753,74 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129605451</v>
+        <v>129599980</v>
       </c>
       <c r="B33" t="n">
-        <v>92905</v>
+        <v>98769</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>638325</v>
+        <v>638416</v>
       </c>
       <c r="R33" t="n">
-        <v>6634691</v>
+        <v>6634840</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3862,9 +3847,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>2 vinterståndare</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3879,12 +3879,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -3894,7 +3894,7 @@
         <v>129598714</v>
       </c>
       <c r="B34" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>129598966</v>
       </c>
       <c r="B35" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>129599353</v>
       </c>
       <c r="B36" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>129599884</v>
       </c>
       <c r="B37" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
         <v>129599503</v>
       </c>
       <c r="B38" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4465,32 +4465,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129605436</v>
+        <v>129605441</v>
       </c>
       <c r="B39" t="n">
-        <v>97014</v>
+        <v>91361</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>53</v>
+        <v>3215</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4500,10 +4500,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>638281</v>
+        <v>638444</v>
       </c>
       <c r="R39" t="n">
-        <v>6634960</v>
+        <v>6634897</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4562,32 +4562,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129605441</v>
+        <v>129605436</v>
       </c>
       <c r="B40" t="n">
-        <v>91360</v>
+        <v>97015</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3215</v>
+        <v>53</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4597,10 +4597,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>638444</v>
+        <v>638281</v>
       </c>
       <c r="R40" t="n">
-        <v>6634897</v>
+        <v>6634960</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4662,7 +4662,7 @@
         <v>129599775</v>
       </c>
       <c r="B41" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4775,10 +4775,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129597954</v>
+        <v>129599955</v>
       </c>
       <c r="B42" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4805,17 +4805,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4824,13 +4819,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>638325</v>
+        <v>638428</v>
       </c>
       <c r="R42" t="n">
-        <v>6634719</v>
+        <v>6634839</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4859,7 +4854,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4869,12 +4864,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>3 vinterståndare</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4889,22 +4879,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129599955</v>
+        <v>129597954</v>
       </c>
       <c r="B43" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4931,12 +4921,17 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4945,13 +4940,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>638428</v>
+        <v>638325</v>
       </c>
       <c r="R43" t="n">
-        <v>6634839</v>
+        <v>6634719</v>
       </c>
       <c r="S43" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4980,7 +4975,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -4990,7 +4985,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>3 vinterståndare</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5005,60 +5005,64 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129602955</v>
+        <v>129601221</v>
       </c>
       <c r="B44" t="n">
-        <v>57732</v>
+        <v>98769</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>638310</v>
+        <v>638294</v>
       </c>
       <c r="R44" t="n">
-        <v>6634749</v>
+        <v>6634962</v>
       </c>
       <c r="S44" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5087,7 +5091,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5097,12 +5101,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Hack av spillkråka</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5132,7 +5131,7 @@
         <v>129598225</v>
       </c>
       <c r="B45" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5258,7 +5257,7 @@
         <v>129599067</v>
       </c>
       <c r="B46" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5381,52 +5380,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129601221</v>
+        <v>129602955</v>
       </c>
       <c r="B47" t="n">
-        <v>98768</v>
+        <v>57733</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>638294</v>
+        <v>638310</v>
       </c>
       <c r="R47" t="n">
-        <v>6634962</v>
+        <v>6634749</v>
       </c>
       <c r="S47" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5455,7 +5450,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5465,7 +5460,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Hack av spillkråka</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5495,7 +5495,7 @@
         <v>129600150</v>
       </c>
       <c r="B48" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>129602684</v>
       </c>
       <c r="B49" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>129602225</v>
       </c>
       <c r="B50" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5860,10 +5860,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129605439</v>
+        <v>129599511</v>
       </c>
       <c r="B51" t="n">
-        <v>57732</v>
+        <v>91588</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5871,37 +5871,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>638277</v>
+        <v>638406</v>
       </c>
       <c r="R51" t="n">
-        <v>6634933</v>
+        <v>6634775</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5928,9 +5928,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5945,69 +5955,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129599969</v>
+        <v>129605439</v>
       </c>
       <c r="B52" t="n">
-        <v>98768</v>
+        <v>57733</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>638428</v>
+        <v>638277</v>
       </c>
       <c r="R52" t="n">
-        <v>6634835</v>
+        <v>6634933</v>
       </c>
       <c r="S52" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6034,19 +6035,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>12:24</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6061,22 +6052,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129599963</v>
+        <v>129599969</v>
       </c>
       <c r="B53" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6108,12 +6099,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6122,13 +6108,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>638420</v>
+        <v>638428</v>
       </c>
       <c r="R53" t="n">
-        <v>6634840</v>
+        <v>6634835</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6182,22 +6168,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129599772</v>
+        <v>129599963</v>
       </c>
       <c r="B54" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6224,7 +6210,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6234,7 +6220,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6243,13 +6229,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>638399</v>
+        <v>638420</v>
       </c>
       <c r="R54" t="n">
-        <v>6634806</v>
+        <v>6634840</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6278,7 +6264,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6288,12 +6274,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>En vinterståndare</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6320,45 +6301,59 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129599511</v>
+        <v>129599772</v>
       </c>
       <c r="B55" t="n">
-        <v>91587</v>
+        <v>98769</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>638406</v>
+        <v>638399</v>
       </c>
       <c r="R55" t="n">
-        <v>6634775</v>
+        <v>6634806</v>
       </c>
       <c r="S55" t="n">
         <v>4</v>
@@ -6390,7 +6385,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6400,7 +6395,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6430,7 +6430,7 @@
         <v>129602370</v>
       </c>
       <c r="B56" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6551,7 +6551,7 @@
         <v>129596091</v>
       </c>
       <c r="B57" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>129602720</v>
       </c>
       <c r="B58" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6780,48 +6780,62 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129605440</v>
+        <v>129601983</v>
       </c>
       <c r="B59" t="n">
-        <v>57732</v>
+        <v>98769</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>638309</v>
+        <v>638209</v>
       </c>
       <c r="R59" t="n">
-        <v>6634908</v>
+        <v>6635047</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6848,9 +6862,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6865,50 +6889,54 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129600817</v>
+        <v>129602223</v>
       </c>
       <c r="B60" t="n">
-        <v>57732</v>
+        <v>98769</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6917,13 +6945,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>638230</v>
+        <v>638236</v>
       </c>
       <c r="R60" t="n">
-        <v>6634962</v>
+        <v>6634982</v>
       </c>
       <c r="S60" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6952,7 +6980,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6962,7 +6990,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6977,59 +7005,50 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129601983</v>
+        <v>129600817</v>
       </c>
       <c r="B61" t="n">
-        <v>98768</v>
+        <v>57733</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7038,10 +7057,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>638209</v>
+        <v>638230</v>
       </c>
       <c r="R61" t="n">
-        <v>6635047</v>
+        <v>6634962</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
@@ -7073,7 +7092,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7083,7 +7102,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7110,57 +7129,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129602223</v>
+        <v>129605440</v>
       </c>
       <c r="B62" t="n">
-        <v>98768</v>
+        <v>57733</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>638236</v>
+        <v>638309</v>
       </c>
       <c r="R62" t="n">
-        <v>6634982</v>
+        <v>6634908</v>
       </c>
       <c r="S62" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7187,19 +7197,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>14:09</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7214,12 +7214,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7229,7 +7229,7 @@
         <v>129600091</v>
       </c>
       <c r="B63" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>129597436</v>
       </c>
       <c r="B65" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>129605452</v>
       </c>
       <c r="B66" t="n">
-        <v>92905</v>
+        <v>92906</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7664,48 +7664,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129601121</v>
+        <v>129605437</v>
       </c>
       <c r="B67" t="n">
-        <v>91811</v>
+        <v>92306</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1106</v>
+        <v>3298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>638329</v>
+        <v>638356</v>
       </c>
       <c r="R67" t="n">
-        <v>6634973</v>
+        <v>6634677</v>
       </c>
       <c r="S67" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7732,19 +7732,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7759,60 +7749,60 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129605437</v>
+        <v>129601121</v>
       </c>
       <c r="B68" t="n">
-        <v>92305</v>
+        <v>91812</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3298</v>
+        <v>1106</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>638356</v>
+        <v>638329</v>
       </c>
       <c r="R68" t="n">
-        <v>6634677</v>
+        <v>6634973</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7839,9 +7829,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7856,44 +7856,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129600760</v>
+        <v>129598997</v>
       </c>
       <c r="B69" t="n">
-        <v>57732</v>
+        <v>92238</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7903,13 +7903,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>638304</v>
+        <v>638351</v>
       </c>
       <c r="R69" t="n">
-        <v>6634890</v>
+        <v>6634790</v>
       </c>
       <c r="S69" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7948,12 +7948,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:04</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Hack av spillkråka</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7968,12 +7963,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -8088,32 +8083,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129598997</v>
+        <v>129600760</v>
       </c>
       <c r="B71" t="n">
-        <v>92237</v>
+        <v>57733</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8123,13 +8118,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>638351</v>
+        <v>638304</v>
       </c>
       <c r="R71" t="n">
-        <v>6634790</v>
+        <v>6634890</v>
       </c>
       <c r="S71" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8158,7 +8153,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8168,7 +8163,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Hack av spillkråka</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8183,12 +8183,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -8198,7 +8198,7 @@
         <v>129602574</v>
       </c>
       <c r="B72" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -2256,32 +2256,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129529699</v>
+        <v>129529689</v>
       </c>
       <c r="B18" t="n">
-        <v>4779</v>
+        <v>92862</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102306</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2291,10 +2291,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>638353</v>
+        <v>638468</v>
       </c>
       <c r="R18" t="n">
-        <v>6634591</v>
+        <v>6634921</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2327,11 +2327,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2358,32 +2353,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129529689</v>
+        <v>129529699</v>
       </c>
       <c r="B19" t="n">
-        <v>92862</v>
+        <v>4779</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4361</v>
+        <v>102306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2393,10 +2388,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>638468</v>
+        <v>638353</v>
       </c>
       <c r="R19" t="n">
-        <v>6634921</v>
+        <v>6634591</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2429,6 +2424,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -978,7 +978,7 @@
         <v>129529667</v>
       </c>
       <c r="B5" t="n">
-        <v>97015</v>
+        <v>97020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>129529690</v>
       </c>
       <c r="B6" t="n">
-        <v>92908</v>
+        <v>92913</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>129529684</v>
       </c>
       <c r="B8" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>129529697</v>
       </c>
       <c r="B9" t="n">
-        <v>90970</v>
+        <v>90975</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>129529691</v>
       </c>
       <c r="B10" t="n">
-        <v>92908</v>
+        <v>92913</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>129529669</v>
       </c>
       <c r="B14" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>129529664</v>
       </c>
       <c r="B15" t="n">
-        <v>91812</v>
+        <v>91817</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>129529682</v>
       </c>
       <c r="B16" t="n">
-        <v>91361</v>
+        <v>91366</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>129529668</v>
       </c>
       <c r="B17" t="n">
-        <v>97015</v>
+        <v>97020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>129529689</v>
       </c>
       <c r="B18" t="n">
-        <v>92862</v>
+        <v>92867</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>129587678</v>
       </c>
       <c r="B21" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>129587673</v>
       </c>
       <c r="B22" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>129587679</v>
       </c>
       <c r="B23" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>129587676</v>
       </c>
       <c r="B24" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>129587685</v>
       </c>
       <c r="B26" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3144,10 +3144,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129587681</v>
+        <v>129587677</v>
       </c>
       <c r="B27" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>638468</v>
+        <v>638447</v>
       </c>
       <c r="R27" t="n">
-        <v>6634929</v>
+        <v>6634803</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3215,6 +3215,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3241,10 +3246,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129587677</v>
+        <v>129587681</v>
       </c>
       <c r="B28" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3276,10 +3281,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>638447</v>
+        <v>638468</v>
       </c>
       <c r="R28" t="n">
-        <v>6634803</v>
+        <v>6634929</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3312,11 +3317,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3346,7 +3346,7 @@
         <v>129587667</v>
       </c>
       <c r="B29" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3440,62 +3440,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129598790</v>
+        <v>129597548</v>
       </c>
       <c r="B30" t="n">
-        <v>98769</v>
+        <v>97020</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>638333</v>
+        <v>638336</v>
       </c>
       <c r="R30" t="n">
-        <v>6634812</v>
+        <v>6634702</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3524,7 +3510,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3534,7 +3520,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3561,48 +3547,62 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129597548</v>
+        <v>129598790</v>
       </c>
       <c r="B31" t="n">
-        <v>97015</v>
+        <v>98774</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>638336</v>
+        <v>638333</v>
       </c>
       <c r="R31" t="n">
-        <v>6634702</v>
+        <v>6634812</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3668,48 +3668,62 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129605451</v>
+        <v>129599980</v>
       </c>
       <c r="B32" t="n">
-        <v>92906</v>
+        <v>98774</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>638325</v>
+        <v>638416</v>
       </c>
       <c r="R32" t="n">
-        <v>6634691</v>
+        <v>6634840</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3736,9 +3750,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>2 vinterståndare</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3753,74 +3782,60 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129599980</v>
+        <v>129605451</v>
       </c>
       <c r="B33" t="n">
-        <v>98769</v>
+        <v>92911</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>638416</v>
+        <v>638325</v>
       </c>
       <c r="R33" t="n">
-        <v>6634840</v>
+        <v>6634691</v>
       </c>
       <c r="S33" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3847,24 +3862,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>2 vinterståndare</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3879,12 +3879,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -3894,7 +3894,7 @@
         <v>129598714</v>
       </c>
       <c r="B34" t="n">
-        <v>91608</v>
+        <v>91613</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>129598966</v>
       </c>
       <c r="B35" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>129599353</v>
       </c>
       <c r="B36" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4246,53 +4246,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129599884</v>
+        <v>129599503</v>
       </c>
       <c r="B37" t="n">
-        <v>57733</v>
+        <v>98774</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>638397</v>
+        <v>638325</v>
       </c>
       <c r="R37" t="n">
-        <v>6634819</v>
+        <v>6634846</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4321,7 +4316,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4331,7 +4326,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4346,60 +4341,65 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Broms</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Broms</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129599503</v>
+        <v>129599884</v>
       </c>
       <c r="B38" t="n">
-        <v>98769</v>
+        <v>57733</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>638325</v>
+        <v>638397</v>
       </c>
       <c r="R38" t="n">
-        <v>6634846</v>
+        <v>6634819</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4453,12 +4453,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anders Broms</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anders Broms</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4468,7 +4468,7 @@
         <v>129605441</v>
       </c>
       <c r="B39" t="n">
-        <v>91361</v>
+        <v>91366</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
         <v>129605436</v>
       </c>
       <c r="B40" t="n">
-        <v>97015</v>
+        <v>97020</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>129599775</v>
       </c>
       <c r="B41" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>129599955</v>
       </c>
       <c r="B42" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>129597954</v>
       </c>
       <c r="B43" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5017,10 +5017,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129601221</v>
+        <v>129598225</v>
       </c>
       <c r="B44" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5047,7 +5047,17 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5056,13 +5066,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>638294</v>
+        <v>638330</v>
       </c>
       <c r="R44" t="n">
-        <v>6634962</v>
+        <v>6634715</v>
       </c>
       <c r="S44" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5091,7 +5101,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5101,7 +5111,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>2 vinterståndare</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5116,22 +5131,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129598225</v>
+        <v>129599067</v>
       </c>
       <c r="B45" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5158,7 +5173,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5177,13 +5192,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>638330</v>
+        <v>638355</v>
       </c>
       <c r="R45" t="n">
-        <v>6634715</v>
+        <v>6634788</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5212,7 +5227,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5222,12 +5237,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>2 vinterståndare</t>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5254,62 +5269,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129599067</v>
+        <v>129602955</v>
       </c>
       <c r="B46" t="n">
-        <v>98769</v>
+        <v>57733</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>638355</v>
+        <v>638310</v>
       </c>
       <c r="R46" t="n">
-        <v>6634788</v>
+        <v>6634749</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5338,7 +5339,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5348,12 +5349,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>En vinterståndare</t>
+          <t>Hack av spillkråka</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5368,60 +5369,64 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129602955</v>
+        <v>129601221</v>
       </c>
       <c r="B47" t="n">
-        <v>57733</v>
+        <v>98774</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>638310</v>
+        <v>638294</v>
       </c>
       <c r="R47" t="n">
-        <v>6634749</v>
+        <v>6634962</v>
       </c>
       <c r="S47" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5450,7 +5455,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5460,12 +5465,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Hack av spillkråka</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5495,7 +5495,7 @@
         <v>129600150</v>
       </c>
       <c r="B48" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>129602684</v>
       </c>
       <c r="B49" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>129602225</v>
       </c>
       <c r="B50" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         <v>129599511</v>
       </c>
       <c r="B51" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5967,48 +5967,57 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129605439</v>
+        <v>129599969</v>
       </c>
       <c r="B52" t="n">
-        <v>57733</v>
+        <v>98774</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>638277</v>
+        <v>638428</v>
       </c>
       <c r="R52" t="n">
-        <v>6634933</v>
+        <v>6634835</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6035,9 +6044,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6052,22 +6071,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129599969</v>
+        <v>129599963</v>
       </c>
       <c r="B53" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6099,7 +6118,12 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6108,13 +6132,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>638428</v>
+        <v>638420</v>
       </c>
       <c r="R53" t="n">
-        <v>6634835</v>
+        <v>6634840</v>
       </c>
       <c r="S53" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6168,22 +6192,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129599963</v>
+        <v>129599772</v>
       </c>
       <c r="B54" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6210,7 +6234,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6220,7 +6244,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6229,13 +6253,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>638420</v>
+        <v>638399</v>
       </c>
       <c r="R54" t="n">
-        <v>6634840</v>
+        <v>6634806</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6264,7 +6288,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6274,7 +6298,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6301,62 +6330,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129599772</v>
+        <v>129605439</v>
       </c>
       <c r="B55" t="n">
-        <v>98769</v>
+        <v>57733</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>638399</v>
+        <v>638277</v>
       </c>
       <c r="R55" t="n">
-        <v>6634806</v>
+        <v>6634933</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6383,24 +6398,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6415,12 +6415,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6430,7 +6430,7 @@
         <v>129602370</v>
       </c>
       <c r="B56" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>129602720</v>
       </c>
       <c r="B58" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>129601983</v>
       </c>
       <c r="B59" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>129602223</v>
       </c>
       <c r="B60" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         <v>129600091</v>
       </c>
       <c r="B63" t="n">
-        <v>92908</v>
+        <v>92913</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>129605452</v>
       </c>
       <c r="B66" t="n">
-        <v>92906</v>
+        <v>92911</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7664,48 +7664,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129605437</v>
+        <v>129601121</v>
       </c>
       <c r="B67" t="n">
-        <v>92306</v>
+        <v>91817</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3298</v>
+        <v>1106</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>638356</v>
+        <v>638329</v>
       </c>
       <c r="R67" t="n">
-        <v>6634677</v>
+        <v>6634973</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7732,9 +7732,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7749,60 +7759,60 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129601121</v>
+        <v>129605437</v>
       </c>
       <c r="B68" t="n">
-        <v>91812</v>
+        <v>92311</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1106</v>
+        <v>3298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>638329</v>
+        <v>638356</v>
       </c>
       <c r="R68" t="n">
-        <v>6634973</v>
+        <v>6634677</v>
       </c>
       <c r="S68" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7829,19 +7839,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7856,44 +7856,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129598997</v>
+        <v>129600760</v>
       </c>
       <c r="B69" t="n">
-        <v>92238</v>
+        <v>57733</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7903,13 +7903,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>638351</v>
+        <v>638304</v>
       </c>
       <c r="R69" t="n">
-        <v>6634790</v>
+        <v>6634890</v>
       </c>
       <c r="S69" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7948,7 +7948,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Hack av spillkråka</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7963,12 +7968,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -8083,48 +8088,57 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129600760</v>
+        <v>129602574</v>
       </c>
       <c r="B71" t="n">
-        <v>57733</v>
+        <v>98774</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>638304</v>
+        <v>638309</v>
       </c>
       <c r="R71" t="n">
-        <v>6634890</v>
+        <v>6634813</v>
       </c>
       <c r="S71" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8153,7 +8167,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8163,12 +8177,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:04</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Hack av spillkråka</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8195,57 +8204,48 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129602574</v>
+        <v>129598997</v>
       </c>
       <c r="B72" t="n">
-        <v>98769</v>
+        <v>92243</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>638309</v>
+        <v>638351</v>
       </c>
       <c r="R72" t="n">
-        <v>6634813</v>
+        <v>6634790</v>
       </c>
       <c r="S72" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8284,7 +8284,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8299,12 +8299,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -1863,32 +1863,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129529669</v>
+        <v>129529664</v>
       </c>
       <c r="B14" t="n">
-        <v>91557</v>
+        <v>91817</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>1106</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1898,10 +1898,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>638445</v>
+        <v>638322</v>
       </c>
       <c r="R14" t="n">
-        <v>6634890</v>
+        <v>6634962</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1960,32 +1960,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129529664</v>
+        <v>129529669</v>
       </c>
       <c r="B15" t="n">
-        <v>91817</v>
+        <v>91557</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1106</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>638322</v>
+        <v>638445</v>
       </c>
       <c r="R15" t="n">
-        <v>6634962</v>
+        <v>6634890</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -3440,48 +3440,62 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129597548</v>
+        <v>129598790</v>
       </c>
       <c r="B30" t="n">
-        <v>97020</v>
+        <v>98774</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>638336</v>
+        <v>638333</v>
       </c>
       <c r="R30" t="n">
-        <v>6634702</v>
+        <v>6634812</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3510,7 +3524,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3520,7 +3534,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3547,62 +3561,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129598790</v>
+        <v>129597548</v>
       </c>
       <c r="B31" t="n">
-        <v>98774</v>
+        <v>97020</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>638333</v>
+        <v>638336</v>
       </c>
       <c r="R31" t="n">
-        <v>6634812</v>
+        <v>6634702</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3668,62 +3668,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129599980</v>
+        <v>129605451</v>
       </c>
       <c r="B32" t="n">
-        <v>98774</v>
+        <v>92911</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>638416</v>
+        <v>638325</v>
       </c>
       <c r="R32" t="n">
-        <v>6634840</v>
+        <v>6634691</v>
       </c>
       <c r="S32" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3750,24 +3736,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>2 vinterståndare</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3782,60 +3753,74 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129605451</v>
+        <v>129599980</v>
       </c>
       <c r="B33" t="n">
-        <v>92911</v>
+        <v>98774</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>638325</v>
+        <v>638416</v>
       </c>
       <c r="R33" t="n">
-        <v>6634691</v>
+        <v>6634840</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3862,9 +3847,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>2 vinterståndare</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3879,12 +3879,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4246,48 +4246,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129599503</v>
+        <v>129599884</v>
       </c>
       <c r="B37" t="n">
-        <v>98774</v>
+        <v>57733</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>638325</v>
+        <v>638397</v>
       </c>
       <c r="R37" t="n">
-        <v>6634846</v>
+        <v>6634819</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4316,7 +4321,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4326,7 +4331,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4341,65 +4346,60 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anders Broms</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anders Broms</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129599884</v>
+        <v>129599503</v>
       </c>
       <c r="B38" t="n">
-        <v>57733</v>
+        <v>98774</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>638397</v>
+        <v>638325</v>
       </c>
       <c r="R38" t="n">
-        <v>6634819</v>
+        <v>6634846</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4453,12 +4453,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Broms</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Broms</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5017,62 +5017,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129598225</v>
+        <v>129602955</v>
       </c>
       <c r="B44" t="n">
-        <v>98774</v>
+        <v>57733</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>638330</v>
+        <v>638310</v>
       </c>
       <c r="R44" t="n">
-        <v>6634715</v>
+        <v>6634749</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5101,7 +5087,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5111,12 +5097,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>2 vinterståndare</t>
+          <t>Hack av spillkråka</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5131,19 +5117,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129599067</v>
+        <v>129598225</v>
       </c>
       <c r="B45" t="n">
         <v>98774</v>
@@ -5173,7 +5159,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5192,13 +5178,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>638355</v>
+        <v>638330</v>
       </c>
       <c r="R45" t="n">
-        <v>6634788</v>
+        <v>6634715</v>
       </c>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5227,7 +5213,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5237,12 +5223,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>En vinterståndare</t>
+          <t>2 vinterståndare</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5269,48 +5255,62 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129602955</v>
+        <v>129599067</v>
       </c>
       <c r="B46" t="n">
-        <v>57733</v>
+        <v>98774</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>638310</v>
+        <v>638355</v>
       </c>
       <c r="R46" t="n">
-        <v>6634749</v>
+        <v>6634788</v>
       </c>
       <c r="S46" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Hack av spillkråka</t>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5369,12 +5369,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5860,10 +5860,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129599511</v>
+        <v>129605439</v>
       </c>
       <c r="B51" t="n">
-        <v>91593</v>
+        <v>57733</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5871,37 +5871,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>638406</v>
+        <v>638277</v>
       </c>
       <c r="R51" t="n">
-        <v>6634775</v>
+        <v>6634933</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5928,19 +5928,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>12:05</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5955,12 +5945,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6330,10 +6320,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129605439</v>
+        <v>129599511</v>
       </c>
       <c r="B55" t="n">
-        <v>57733</v>
+        <v>91593</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6341,37 +6331,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>638277</v>
+        <v>638406</v>
       </c>
       <c r="R55" t="n">
-        <v>6634933</v>
+        <v>6634775</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6398,9 +6388,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6415,12 +6415,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6548,57 +6548,57 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129596091</v>
+        <v>129602720</v>
       </c>
       <c r="B57" t="n">
-        <v>57733</v>
+        <v>98774</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Orreboda, Orreboda, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>638323</v>
+        <v>638301</v>
       </c>
       <c r="R57" t="n">
-        <v>6634555</v>
+        <v>6634767</v>
       </c>
       <c r="S57" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6652,69 +6652,69 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129602720</v>
+        <v>129596091</v>
       </c>
       <c r="B58" t="n">
-        <v>98774</v>
+        <v>57733</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Orreboda, Orreboda, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>638301</v>
+        <v>638323</v>
       </c>
       <c r="R58" t="n">
-        <v>6634767</v>
+        <v>6634555</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6753,7 +6753,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6768,59 +6768,50 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129601983</v>
+        <v>129600817</v>
       </c>
       <c r="B59" t="n">
-        <v>98774</v>
+        <v>57733</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6829,10 +6820,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>638209</v>
+        <v>638230</v>
       </c>
       <c r="R59" t="n">
-        <v>6635047</v>
+        <v>6634962</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -6864,7 +6855,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6874,7 +6865,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6901,57 +6892,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129602223</v>
+        <v>129605440</v>
       </c>
       <c r="B60" t="n">
-        <v>98774</v>
+        <v>57733</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>638236</v>
+        <v>638309</v>
       </c>
       <c r="R60" t="n">
-        <v>6634982</v>
+        <v>6634908</v>
       </c>
       <c r="S60" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6978,19 +6960,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>14:09</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7005,50 +6977,59 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129600817</v>
+        <v>129601983</v>
       </c>
       <c r="B61" t="n">
-        <v>57733</v>
+        <v>98774</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7057,10 +7038,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>638230</v>
+        <v>638209</v>
       </c>
       <c r="R61" t="n">
-        <v>6634962</v>
+        <v>6635047</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
@@ -7092,7 +7073,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7102,7 +7083,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7129,48 +7110,57 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129605440</v>
+        <v>129602223</v>
       </c>
       <c r="B62" t="n">
-        <v>57733</v>
+        <v>98774</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>638309</v>
+        <v>638236</v>
       </c>
       <c r="R62" t="n">
-        <v>6634908</v>
+        <v>6634982</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7197,9 +7187,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7214,12 +7214,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7868,48 +7868,57 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129600760</v>
+        <v>129602574</v>
       </c>
       <c r="B69" t="n">
-        <v>57733</v>
+        <v>98774</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>638304</v>
+        <v>638309</v>
       </c>
       <c r="R69" t="n">
-        <v>6634890</v>
+        <v>6634813</v>
       </c>
       <c r="S69" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7938,7 +7947,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7948,12 +7957,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:04</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Hack av spillkråka</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7980,10 +7984,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129605449</v>
+        <v>129598997</v>
       </c>
       <c r="B70" t="n">
-        <v>4779</v>
+        <v>92243</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7991,42 +7995,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>102306</v>
+        <v>1339</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>638301</v>
+        <v>638351</v>
       </c>
       <c r="R70" t="n">
-        <v>6634752</v>
+        <v>6634790</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8053,14 +8052,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8069,76 +8073,66 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129602574</v>
+        <v>129600760</v>
       </c>
       <c r="B71" t="n">
-        <v>98774</v>
+        <v>57733</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>638309</v>
+        <v>638304</v>
       </c>
       <c r="R71" t="n">
-        <v>6634813</v>
+        <v>6634890</v>
       </c>
       <c r="S71" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8167,7 +8161,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8177,7 +8171,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Hack av spillkråka</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8204,10 +8203,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129598997</v>
+        <v>129605449</v>
       </c>
       <c r="B72" t="n">
-        <v>92243</v>
+        <v>4779</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8215,37 +8214,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1339</v>
+        <v>102306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>638351</v>
+        <v>638301</v>
       </c>
       <c r="R72" t="n">
-        <v>6634790</v>
+        <v>6634752</v>
       </c>
       <c r="S72" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8272,19 +8276,14 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>11:45</t>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8293,18 +8292,19 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -1460,32 +1460,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129529691</v>
+        <v>129529700</v>
       </c>
       <c r="B10" t="n">
-        <v>92913</v>
+        <v>4779</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>102306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>638522</v>
+        <v>638165</v>
       </c>
       <c r="R10" t="n">
-        <v>6634845</v>
+        <v>6634993</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1531,6 +1531,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1557,32 +1562,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129529700</v>
+        <v>129529691</v>
       </c>
       <c r="B11" t="n">
-        <v>4779</v>
+        <v>92913</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102306</v>
+        <v>5966</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1592,10 +1597,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>638165</v>
+        <v>638522</v>
       </c>
       <c r="R11" t="n">
-        <v>6634993</v>
+        <v>6634845</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1628,11 +1633,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -3891,44 +3891,62 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129598714</v>
+        <v>129598966</v>
       </c>
       <c r="B34" t="n">
-        <v>91613</v>
+        <v>98774</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>638323</v>
+        <v>638348</v>
       </c>
       <c r="R34" t="n">
-        <v>6634794</v>
+        <v>6634797</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3957,7 +3975,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -3967,12 +3985,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Rikligt på undersidan av döda grenar på levande äldre gran.</t>
+          <t>3 vinterståndare</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3999,7 +4017,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129598966</v>
+        <v>129599353</v>
       </c>
       <c r="B35" t="n">
         <v>98774</v>
@@ -4029,7 +4047,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4039,7 +4057,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4048,13 +4066,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>638348</v>
+        <v>638395</v>
       </c>
       <c r="R35" t="n">
-        <v>6634797</v>
+        <v>6634786</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4083,7 +4101,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4093,12 +4111,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>3 vinterståndare</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4125,62 +4138,44 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129599353</v>
+        <v>129598714</v>
       </c>
       <c r="B36" t="n">
-        <v>98774</v>
+        <v>91613</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>638395</v>
+        <v>638323</v>
       </c>
       <c r="R36" t="n">
-        <v>6634786</v>
+        <v>6634794</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4209,7 +4204,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4219,7 +4214,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Rikligt på undersidan av döda grenar på levande äldre gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4659,7 +4659,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129599775</v>
+        <v>129599955</v>
       </c>
       <c r="B41" t="n">
         <v>98774</v>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4703,13 +4703,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>638435</v>
+        <v>638428</v>
       </c>
       <c r="R41" t="n">
         <v>6634839</v>
       </c>
       <c r="S41" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4775,7 +4775,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129599955</v>
+        <v>129597954</v>
       </c>
       <c r="B42" t="n">
         <v>98774</v>
@@ -4805,12 +4805,17 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4819,13 +4824,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>638428</v>
+        <v>638325</v>
       </c>
       <c r="R42" t="n">
-        <v>6634839</v>
+        <v>6634719</v>
       </c>
       <c r="S42" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4854,7 +4859,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4864,7 +4869,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>3 vinterståndare</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4879,19 +4889,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129597954</v>
+        <v>129599775</v>
       </c>
       <c r="B43" t="n">
         <v>98774</v>
@@ -4921,17 +4931,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4940,13 +4945,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>638325</v>
+        <v>638435</v>
       </c>
       <c r="R43" t="n">
-        <v>6634719</v>
+        <v>6634839</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4975,7 +4980,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -4985,12 +4990,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>3 vinterståndare</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5005,12 +5005,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5860,48 +5860,57 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129605439</v>
+        <v>129599969</v>
       </c>
       <c r="B51" t="n">
-        <v>57733</v>
+        <v>98774</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>638277</v>
+        <v>638428</v>
       </c>
       <c r="R51" t="n">
-        <v>6634933</v>
+        <v>6634835</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5928,9 +5937,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5945,19 +5964,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129599969</v>
+        <v>129599963</v>
       </c>
       <c r="B52" t="n">
         <v>98774</v>
@@ -5992,7 +6011,12 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6001,13 +6025,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>638428</v>
+        <v>638420</v>
       </c>
       <c r="R52" t="n">
-        <v>6634835</v>
+        <v>6634840</v>
       </c>
       <c r="S52" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6061,19 +6085,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129599963</v>
+        <v>129599772</v>
       </c>
       <c r="B53" t="n">
         <v>98774</v>
@@ -6103,7 +6127,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6113,7 +6137,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6122,13 +6146,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>638420</v>
+        <v>638399</v>
       </c>
       <c r="R53" t="n">
-        <v>6634840</v>
+        <v>6634806</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6157,7 +6181,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6167,7 +6191,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6194,59 +6223,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129599772</v>
+        <v>129599511</v>
       </c>
       <c r="B54" t="n">
-        <v>98774</v>
+        <v>91593</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>638399</v>
+        <v>638406</v>
       </c>
       <c r="R54" t="n">
-        <v>6634806</v>
+        <v>6634775</v>
       </c>
       <c r="S54" t="n">
         <v>4</v>
@@ -6278,7 +6293,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6288,12 +6303,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>En vinterståndare</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6320,10 +6330,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129599511</v>
+        <v>129605439</v>
       </c>
       <c r="B55" t="n">
-        <v>91593</v>
+        <v>57733</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6331,37 +6341,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>638406</v>
+        <v>638277</v>
       </c>
       <c r="R55" t="n">
-        <v>6634775</v>
+        <v>6634933</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6388,19 +6398,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>12:05</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6415,12 +6415,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6548,57 +6548,57 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129602720</v>
+        <v>129596091</v>
       </c>
       <c r="B57" t="n">
-        <v>98774</v>
+        <v>57733</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Orreboda, Orreboda, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>638301</v>
+        <v>638323</v>
       </c>
       <c r="R57" t="n">
-        <v>6634767</v>
+        <v>6634555</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6652,69 +6652,69 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129596091</v>
+        <v>129602720</v>
       </c>
       <c r="B58" t="n">
-        <v>57733</v>
+        <v>98774</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Orreboda, Orreboda, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>638323</v>
+        <v>638301</v>
       </c>
       <c r="R58" t="n">
-        <v>6634555</v>
+        <v>6634767</v>
       </c>
       <c r="S58" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6753,7 +6753,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6768,19 +6768,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129600817</v>
+        <v>129605440</v>
       </c>
       <c r="B59" t="n">
         <v>57733</v>
@@ -6809,24 +6809,19 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>638230</v>
+        <v>638309</v>
       </c>
       <c r="R59" t="n">
-        <v>6634962</v>
+        <v>6634908</v>
       </c>
       <c r="S59" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6853,19 +6848,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6880,19 +6865,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129605440</v>
+        <v>129600817</v>
       </c>
       <c r="B60" t="n">
         <v>57733</v>
@@ -6921,19 +6906,24 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>638309</v>
+        <v>638230</v>
       </c>
       <c r="R60" t="n">
-        <v>6634908</v>
+        <v>6634962</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6960,9 +6950,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6977,12 +6977,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7455,53 +7455,48 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129597436</v>
+        <v>129605452</v>
       </c>
       <c r="B65" t="n">
-        <v>57733</v>
+        <v>92911</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>638292</v>
+        <v>638324</v>
       </c>
       <c r="R65" t="n">
-        <v>6634699</v>
+        <v>6634750</v>
       </c>
       <c r="S65" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7528,19 +7523,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>10:38</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7555,60 +7540,65 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129605452</v>
+        <v>129597436</v>
       </c>
       <c r="B66" t="n">
-        <v>92911</v>
+        <v>57733</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>638324</v>
+        <v>638292</v>
       </c>
       <c r="R66" t="n">
-        <v>6634750</v>
+        <v>6634699</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7635,9 +7625,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7652,12 +7652,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7868,57 +7868,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129602574</v>
+        <v>129598997</v>
       </c>
       <c r="B69" t="n">
-        <v>98774</v>
+        <v>92243</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>638309</v>
+        <v>638351</v>
       </c>
       <c r="R69" t="n">
-        <v>6634813</v>
+        <v>6634790</v>
       </c>
       <c r="S69" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7947,7 +7938,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7957,7 +7948,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7972,22 +7963,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129598997</v>
+        <v>129605449</v>
       </c>
       <c r="B70" t="n">
-        <v>92243</v>
+        <v>4779</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7995,37 +7986,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1339</v>
+        <v>102306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>638351</v>
+        <v>638301</v>
       </c>
       <c r="R70" t="n">
-        <v>6634790</v>
+        <v>6634752</v>
       </c>
       <c r="S70" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8052,19 +8048,14 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>11:45</t>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8073,18 +8064,19 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8203,53 +8195,57 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129605449</v>
+        <v>129602574</v>
       </c>
       <c r="B72" t="n">
-        <v>4779</v>
+        <v>98774</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>638301</v>
+        <v>638309</v>
       </c>
       <c r="R72" t="n">
-        <v>6634752</v>
+        <v>6634813</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8276,14 +8272,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8292,19 +8293,18 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -1863,32 +1863,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129529664</v>
+        <v>129529669</v>
       </c>
       <c r="B14" t="n">
-        <v>91817</v>
+        <v>91557</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1106</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1898,10 +1898,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>638322</v>
+        <v>638445</v>
       </c>
       <c r="R14" t="n">
-        <v>6634962</v>
+        <v>6634890</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1960,32 +1960,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129529669</v>
+        <v>129529664</v>
       </c>
       <c r="B15" t="n">
-        <v>91557</v>
+        <v>91817</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>1106</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>638445</v>
+        <v>638322</v>
       </c>
       <c r="R15" t="n">
-        <v>6634890</v>
+        <v>6634962</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2256,32 +2256,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129529689</v>
+        <v>129529699</v>
       </c>
       <c r="B18" t="n">
-        <v>92867</v>
+        <v>4779</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4361</v>
+        <v>102306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2291,10 +2291,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>638468</v>
+        <v>638353</v>
       </c>
       <c r="R18" t="n">
-        <v>6634921</v>
+        <v>6634591</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2327,6 +2327,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2353,32 +2358,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129529699</v>
+        <v>129529689</v>
       </c>
       <c r="B19" t="n">
-        <v>4779</v>
+        <v>92867</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102306</v>
+        <v>4361</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2388,10 +2393,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>638353</v>
+        <v>638468</v>
       </c>
       <c r="R19" t="n">
-        <v>6634591</v>
+        <v>6634921</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2424,11 +2429,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2950,32 +2950,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129587670</v>
+        <v>129587685</v>
       </c>
       <c r="B25" t="n">
-        <v>57733</v>
+        <v>100963</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>638333</v>
+        <v>638463</v>
       </c>
       <c r="R25" t="n">
-        <v>6634980</v>
+        <v>6634889</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3047,32 +3047,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129587685</v>
+        <v>129587670</v>
       </c>
       <c r="B26" t="n">
-        <v>100963</v>
+        <v>57733</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3082,10 +3082,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>638463</v>
+        <v>638333</v>
       </c>
       <c r="R26" t="n">
-        <v>6634889</v>
+        <v>6634980</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -4465,32 +4465,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129605441</v>
+        <v>129605436</v>
       </c>
       <c r="B39" t="n">
-        <v>91366</v>
+        <v>97020</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3215</v>
+        <v>53</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4500,10 +4500,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>638444</v>
+        <v>638281</v>
       </c>
       <c r="R39" t="n">
-        <v>6634897</v>
+        <v>6634960</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4562,32 +4562,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129605436</v>
+        <v>129605441</v>
       </c>
       <c r="B40" t="n">
-        <v>97020</v>
+        <v>91366</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>53</v>
+        <v>3215</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4597,10 +4597,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>638281</v>
+        <v>638444</v>
       </c>
       <c r="R40" t="n">
-        <v>6634960</v>
+        <v>6634897</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4659,7 +4659,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129599955</v>
+        <v>129599775</v>
       </c>
       <c r="B41" t="n">
         <v>98774</v>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4703,13 +4703,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>638428</v>
+        <v>638435</v>
       </c>
       <c r="R41" t="n">
         <v>6634839</v>
       </c>
       <c r="S41" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4901,7 +4901,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129599775</v>
+        <v>129599955</v>
       </c>
       <c r="B43" t="n">
         <v>98774</v>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4945,13 +4945,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>638435</v>
+        <v>638428</v>
       </c>
       <c r="R43" t="n">
         <v>6634839</v>
       </c>
       <c r="S43" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5860,57 +5860,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129599969</v>
+        <v>129605439</v>
       </c>
       <c r="B51" t="n">
-        <v>98774</v>
+        <v>57733</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>638428</v>
+        <v>638277</v>
       </c>
       <c r="R51" t="n">
-        <v>6634835</v>
+        <v>6634933</v>
       </c>
       <c r="S51" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5937,19 +5928,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>12:24</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5964,74 +5945,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129599963</v>
+        <v>129599511</v>
       </c>
       <c r="B52" t="n">
-        <v>98774</v>
+        <v>91593</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>638420</v>
+        <v>638406</v>
       </c>
       <c r="R52" t="n">
-        <v>6634840</v>
+        <v>6634775</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6060,7 +6027,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6070,7 +6037,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6097,7 +6064,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129599772</v>
+        <v>129599969</v>
       </c>
       <c r="B53" t="n">
         <v>98774</v>
@@ -6127,17 +6094,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6146,13 +6108,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>638399</v>
+        <v>638428</v>
       </c>
       <c r="R53" t="n">
-        <v>6634806</v>
+        <v>6634835</v>
       </c>
       <c r="S53" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6181,7 +6143,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6191,12 +6153,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>En vinterståndare</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6211,60 +6168,74 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129599511</v>
+        <v>129599963</v>
       </c>
       <c r="B54" t="n">
-        <v>91593</v>
+        <v>98774</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>638406</v>
+        <v>638420</v>
       </c>
       <c r="R54" t="n">
-        <v>6634775</v>
+        <v>6634840</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6293,7 +6264,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6303,7 +6274,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6330,48 +6301,62 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129605439</v>
+        <v>129599772</v>
       </c>
       <c r="B55" t="n">
-        <v>57733</v>
+        <v>98774</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>638277</v>
+        <v>638399</v>
       </c>
       <c r="R55" t="n">
-        <v>6634933</v>
+        <v>6634806</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6398,9 +6383,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6415,12 +6415,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6548,57 +6548,57 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129596091</v>
+        <v>129602720</v>
       </c>
       <c r="B57" t="n">
-        <v>57733</v>
+        <v>98774</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Orreboda, Orreboda, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>638323</v>
+        <v>638301</v>
       </c>
       <c r="R57" t="n">
-        <v>6634555</v>
+        <v>6634767</v>
       </c>
       <c r="S57" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6652,69 +6652,69 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129602720</v>
+        <v>129596091</v>
       </c>
       <c r="B58" t="n">
-        <v>98774</v>
+        <v>57733</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Orreboda, Orreboda, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>638301</v>
+        <v>638323</v>
       </c>
       <c r="R58" t="n">
-        <v>6634767</v>
+        <v>6634555</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6753,7 +6753,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6768,19 +6768,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129605440</v>
+        <v>129600817</v>
       </c>
       <c r="B59" t="n">
         <v>57733</v>
@@ -6809,19 +6809,24 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>638309</v>
+        <v>638230</v>
       </c>
       <c r="R59" t="n">
-        <v>6634908</v>
+        <v>6634962</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6848,9 +6853,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6865,19 +6880,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129600817</v>
+        <v>129605440</v>
       </c>
       <c r="B60" t="n">
         <v>57733</v>
@@ -6906,24 +6921,19 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>638230</v>
+        <v>638309</v>
       </c>
       <c r="R60" t="n">
-        <v>6634962</v>
+        <v>6634908</v>
       </c>
       <c r="S60" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6950,19 +6960,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6977,12 +6977,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7868,32 +7868,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129598997</v>
+        <v>129600760</v>
       </c>
       <c r="B69" t="n">
-        <v>92243</v>
+        <v>57733</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7903,13 +7903,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>638351</v>
+        <v>638304</v>
       </c>
       <c r="R69" t="n">
-        <v>6634790</v>
+        <v>6634890</v>
       </c>
       <c r="S69" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7948,7 +7948,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Hack av spillkråka</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7963,22 +7968,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129605449</v>
+        <v>129598997</v>
       </c>
       <c r="B70" t="n">
-        <v>4779</v>
+        <v>92243</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7986,42 +7991,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>102306</v>
+        <v>1339</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>638301</v>
+        <v>638351</v>
       </c>
       <c r="R70" t="n">
-        <v>6634752</v>
+        <v>6634790</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8048,14 +8048,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8064,67 +8069,71 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129600760</v>
+        <v>129605449</v>
       </c>
       <c r="B71" t="n">
-        <v>57733</v>
+        <v>4779</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>638304</v>
+        <v>638301</v>
       </c>
       <c r="R71" t="n">
-        <v>6634890</v>
+        <v>6634752</v>
       </c>
       <c r="S71" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8151,24 +8160,14 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Hack av spillkråka</t>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8177,18 +8176,19 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -978,7 +978,7 @@
         <v>129529667</v>
       </c>
       <c r="B5" t="n">
-        <v>97020</v>
+        <v>97024</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>129529690</v>
       </c>
       <c r="B6" t="n">
-        <v>92913</v>
+        <v>92917</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>129529684</v>
       </c>
       <c r="B8" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>129529697</v>
       </c>
       <c r="B9" t="n">
-        <v>90975</v>
+        <v>90979</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1460,32 +1460,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129529700</v>
+        <v>129529691</v>
       </c>
       <c r="B10" t="n">
-        <v>4779</v>
+        <v>92917</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102306</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>638165</v>
+        <v>638522</v>
       </c>
       <c r="R10" t="n">
-        <v>6634993</v>
+        <v>6634845</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1531,11 +1531,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1562,32 +1557,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129529691</v>
+        <v>129529700</v>
       </c>
       <c r="B11" t="n">
-        <v>92913</v>
+        <v>4779</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>102306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1597,10 +1592,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>638522</v>
+        <v>638165</v>
       </c>
       <c r="R11" t="n">
-        <v>6634845</v>
+        <v>6634993</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1633,6 +1628,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1866,7 +1866,7 @@
         <v>129529669</v>
       </c>
       <c r="B14" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>129529664</v>
       </c>
       <c r="B15" t="n">
-        <v>91817</v>
+        <v>91821</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>129529682</v>
       </c>
       <c r="B16" t="n">
-        <v>91366</v>
+        <v>91370</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>129529668</v>
       </c>
       <c r="B17" t="n">
-        <v>97020</v>
+        <v>97024</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2256,32 +2256,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129529699</v>
+        <v>129529689</v>
       </c>
       <c r="B18" t="n">
-        <v>4779</v>
+        <v>92871</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102306</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2291,10 +2291,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>638353</v>
+        <v>638468</v>
       </c>
       <c r="R18" t="n">
-        <v>6634591</v>
+        <v>6634921</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2327,11 +2327,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2358,32 +2353,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129529689</v>
+        <v>129529699</v>
       </c>
       <c r="B19" t="n">
-        <v>92867</v>
+        <v>4779</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4361</v>
+        <v>102306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2393,10 +2388,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>638468</v>
+        <v>638353</v>
       </c>
       <c r="R19" t="n">
-        <v>6634921</v>
+        <v>6634591</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2429,6 +2424,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2555,7 +2555,7 @@
         <v>129587678</v>
       </c>
       <c r="B21" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>129587673</v>
       </c>
       <c r="B22" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>129587679</v>
       </c>
       <c r="B23" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>129587676</v>
       </c>
       <c r="B24" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>129587685</v>
       </c>
       <c r="B25" t="n">
-        <v>100963</v>
+        <v>100967</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>129587677</v>
       </c>
       <c r="B27" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>129587681</v>
       </c>
       <c r="B28" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>129587667</v>
       </c>
       <c r="B29" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>129598790</v>
       </c>
       <c r="B30" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
         <v>129597548</v>
       </c>
       <c r="B31" t="n">
-        <v>97020</v>
+        <v>97024</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>129605451</v>
       </c>
       <c r="B32" t="n">
-        <v>92911</v>
+        <v>92915</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>129599980</v>
       </c>
       <c r="B33" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3891,10 +3891,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129598966</v>
+        <v>129599353</v>
       </c>
       <c r="B34" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3940,13 +3940,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>638348</v>
+        <v>638395</v>
       </c>
       <c r="R34" t="n">
-        <v>6634797</v>
+        <v>6634786</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -3985,12 +3985,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>3 vinterståndare</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4017,62 +4012,44 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129599353</v>
+        <v>129598714</v>
       </c>
       <c r="B35" t="n">
-        <v>98774</v>
+        <v>91617</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>638395</v>
+        <v>638323</v>
       </c>
       <c r="R35" t="n">
-        <v>6634786</v>
+        <v>6634794</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4101,7 +4078,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4111,7 +4088,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Rikligt på undersidan av döda grenar på levande äldre gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4138,44 +4120,62 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129598714</v>
+        <v>129598966</v>
       </c>
       <c r="B36" t="n">
-        <v>91613</v>
+        <v>98778</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>638323</v>
+        <v>638348</v>
       </c>
       <c r="R36" t="n">
-        <v>6634794</v>
+        <v>6634797</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Rikligt på undersidan av döda grenar på levande äldre gran.</t>
+          <t>3 vinterståndare</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4246,53 +4246,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129599884</v>
+        <v>129599503</v>
       </c>
       <c r="B37" t="n">
-        <v>57733</v>
+        <v>98778</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>638397</v>
+        <v>638325</v>
       </c>
       <c r="R37" t="n">
-        <v>6634819</v>
+        <v>6634846</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4321,7 +4316,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4331,7 +4326,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4346,60 +4341,65 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Broms</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Broms</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129599503</v>
+        <v>129599884</v>
       </c>
       <c r="B38" t="n">
-        <v>98774</v>
+        <v>57733</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>638325</v>
+        <v>638397</v>
       </c>
       <c r="R38" t="n">
-        <v>6634846</v>
+        <v>6634819</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4453,12 +4453,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anders Broms</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anders Broms</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4468,7 +4468,7 @@
         <v>129605436</v>
       </c>
       <c r="B39" t="n">
-        <v>97020</v>
+        <v>97024</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
         <v>129605441</v>
       </c>
       <c r="B40" t="n">
-        <v>91366</v>
+        <v>91370</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4659,10 +4659,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129599775</v>
+        <v>129599955</v>
       </c>
       <c r="B41" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4703,13 +4703,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>638435</v>
+        <v>638428</v>
       </c>
       <c r="R41" t="n">
         <v>6634839</v>
       </c>
       <c r="S41" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4778,7 +4778,7 @@
         <v>129597954</v>
       </c>
       <c r="B42" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4901,10 +4901,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129599955</v>
+        <v>129599775</v>
       </c>
       <c r="B43" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4945,13 +4945,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>638428</v>
+        <v>638435</v>
       </c>
       <c r="R43" t="n">
         <v>6634839</v>
       </c>
       <c r="S43" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5017,48 +5017,52 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129602955</v>
+        <v>129601221</v>
       </c>
       <c r="B44" t="n">
-        <v>57733</v>
+        <v>98778</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>638310</v>
+        <v>638294</v>
       </c>
       <c r="R44" t="n">
-        <v>6634749</v>
+        <v>6634962</v>
       </c>
       <c r="S44" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5087,7 +5091,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5097,12 +5101,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Hack av spillkråka</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5132,7 +5131,7 @@
         <v>129598225</v>
       </c>
       <c r="B45" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5258,7 +5257,7 @@
         <v>129599067</v>
       </c>
       <c r="B46" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5381,52 +5380,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129601221</v>
+        <v>129602955</v>
       </c>
       <c r="B47" t="n">
-        <v>98774</v>
+        <v>57733</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>638294</v>
+        <v>638310</v>
       </c>
       <c r="R47" t="n">
-        <v>6634962</v>
+        <v>6634749</v>
       </c>
       <c r="S47" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5455,7 +5450,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5465,7 +5460,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Hack av spillkråka</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5495,7 +5495,7 @@
         <v>129600150</v>
       </c>
       <c r="B48" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5613,10 +5613,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129602684</v>
+        <v>129602225</v>
       </c>
       <c r="B49" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5662,13 +5662,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>638332</v>
+        <v>638237</v>
       </c>
       <c r="R49" t="n">
-        <v>6634693</v>
+        <v>6635004</v>
       </c>
       <c r="S49" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5707,7 +5707,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5734,10 +5739,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129602225</v>
+        <v>129602684</v>
       </c>
       <c r="B50" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5764,7 +5769,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5774,7 +5779,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5783,13 +5788,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>638237</v>
+        <v>638332</v>
       </c>
       <c r="R50" t="n">
-        <v>6635004</v>
+        <v>6634693</v>
       </c>
       <c r="S50" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5818,7 +5823,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5828,12 +5833,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>En vinterståndare</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5960,7 +5960,7 @@
         <v>129599511</v>
       </c>
       <c r="B52" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>129599969</v>
       </c>
       <c r="B53" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>129599963</v>
       </c>
       <c r="B54" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>129599772</v>
       </c>
       <c r="B55" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         <v>129602370</v>
       </c>
       <c r="B56" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6548,57 +6548,57 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129602720</v>
+        <v>129596091</v>
       </c>
       <c r="B57" t="n">
-        <v>98774</v>
+        <v>57733</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Orreboda, Orreboda, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>638301</v>
+        <v>638323</v>
       </c>
       <c r="R57" t="n">
-        <v>6634767</v>
+        <v>6634555</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6652,69 +6652,69 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129596091</v>
+        <v>129602720</v>
       </c>
       <c r="B58" t="n">
-        <v>57733</v>
+        <v>98778</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Orreboda, Orreboda, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>638323</v>
+        <v>638301</v>
       </c>
       <c r="R58" t="n">
-        <v>6634555</v>
+        <v>6634767</v>
       </c>
       <c r="S58" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6753,7 +6753,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6768,50 +6768,59 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129600817</v>
+        <v>129601983</v>
       </c>
       <c r="B59" t="n">
-        <v>57733</v>
+        <v>98778</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6820,10 +6829,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>638230</v>
+        <v>638209</v>
       </c>
       <c r="R59" t="n">
-        <v>6634962</v>
+        <v>6635047</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -6855,7 +6864,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6865,7 +6874,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6892,48 +6901,57 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129605440</v>
+        <v>129602223</v>
       </c>
       <c r="B60" t="n">
-        <v>57733</v>
+        <v>98778</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>638309</v>
+        <v>638236</v>
       </c>
       <c r="R60" t="n">
-        <v>6634908</v>
+        <v>6634982</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6960,9 +6978,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6977,59 +7005,50 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129601983</v>
+        <v>129600817</v>
       </c>
       <c r="B61" t="n">
-        <v>98774</v>
+        <v>57733</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7038,10 +7057,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>638209</v>
+        <v>638230</v>
       </c>
       <c r="R61" t="n">
-        <v>6635047</v>
+        <v>6634962</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
@@ -7073,7 +7092,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7083,7 +7102,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7110,57 +7129,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129602223</v>
+        <v>129605440</v>
       </c>
       <c r="B62" t="n">
-        <v>98774</v>
+        <v>57733</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>638236</v>
+        <v>638309</v>
       </c>
       <c r="R62" t="n">
-        <v>6634982</v>
+        <v>6634908</v>
       </c>
       <c r="S62" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7187,19 +7197,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>14:09</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7214,12 +7214,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7229,7 +7229,7 @@
         <v>129600091</v>
       </c>
       <c r="B63" t="n">
-        <v>92913</v>
+        <v>92917</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>129605452</v>
       </c>
       <c r="B65" t="n">
-        <v>92911</v>
+        <v>92915</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7664,48 +7664,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129601121</v>
+        <v>129605437</v>
       </c>
       <c r="B67" t="n">
-        <v>91817</v>
+        <v>92315</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1106</v>
+        <v>3298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>638329</v>
+        <v>638356</v>
       </c>
       <c r="R67" t="n">
-        <v>6634973</v>
+        <v>6634677</v>
       </c>
       <c r="S67" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7732,19 +7732,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7759,60 +7749,60 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129605437</v>
+        <v>129601121</v>
       </c>
       <c r="B68" t="n">
-        <v>92311</v>
+        <v>91821</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3298</v>
+        <v>1106</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>638356</v>
+        <v>638329</v>
       </c>
       <c r="R68" t="n">
-        <v>6634677</v>
+        <v>6634973</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7839,9 +7829,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7856,60 +7856,65 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129600760</v>
+        <v>129605449</v>
       </c>
       <c r="B69" t="n">
-        <v>57733</v>
+        <v>4779</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>638304</v>
+        <v>638301</v>
       </c>
       <c r="R69" t="n">
-        <v>6634890</v>
+        <v>6634752</v>
       </c>
       <c r="S69" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7936,24 +7941,14 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Hack av spillkråka</t>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7962,66 +7957,76 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129598997</v>
+        <v>129602574</v>
       </c>
       <c r="B70" t="n">
-        <v>92243</v>
+        <v>98778</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>638351</v>
+        <v>638309</v>
       </c>
       <c r="R70" t="n">
-        <v>6634790</v>
+        <v>6634813</v>
       </c>
       <c r="S70" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8050,7 +8055,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8060,7 +8065,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8075,65 +8080,60 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129605449</v>
+        <v>129600760</v>
       </c>
       <c r="B71" t="n">
-        <v>4779</v>
+        <v>57733</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>638301</v>
+        <v>638304</v>
       </c>
       <c r="R71" t="n">
-        <v>6634752</v>
+        <v>6634890</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8160,14 +8160,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På äldre levande gran</t>
+          <t>Hack av spillkråka</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8176,76 +8186,66 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129602574</v>
+        <v>129598997</v>
       </c>
       <c r="B72" t="n">
-        <v>98774</v>
+        <v>92247</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>638309</v>
+        <v>638351</v>
       </c>
       <c r="R72" t="n">
-        <v>6634813</v>
+        <v>6634790</v>
       </c>
       <c r="S72" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8284,7 +8284,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8299,12 +8299,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -978,7 +978,7 @@
         <v>129529667</v>
       </c>
       <c r="B5" t="n">
-        <v>97024</v>
+        <v>97026</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>129529690</v>
       </c>
       <c r="B6" t="n">
-        <v>92917</v>
+        <v>92919</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>129529684</v>
       </c>
       <c r="B8" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>129529697</v>
       </c>
       <c r="B9" t="n">
-        <v>90979</v>
+        <v>90981</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>129529691</v>
       </c>
       <c r="B10" t="n">
-        <v>92917</v>
+        <v>92919</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>129529669</v>
       </c>
       <c r="B14" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>129529664</v>
       </c>
       <c r="B15" t="n">
-        <v>91821</v>
+        <v>91823</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>129529682</v>
       </c>
       <c r="B16" t="n">
-        <v>91370</v>
+        <v>91372</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>129529668</v>
       </c>
       <c r="B17" t="n">
-        <v>97024</v>
+        <v>97026</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>129529689</v>
       </c>
       <c r="B18" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>129587678</v>
       </c>
       <c r="B21" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>129587673</v>
       </c>
       <c r="B22" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>129587679</v>
       </c>
       <c r="B23" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>129587676</v>
       </c>
       <c r="B24" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2950,32 +2950,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129587685</v>
+        <v>129587670</v>
       </c>
       <c r="B25" t="n">
-        <v>100967</v>
+        <v>57733</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>638463</v>
+        <v>638333</v>
       </c>
       <c r="R25" t="n">
-        <v>6634889</v>
+        <v>6634980</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3047,32 +3047,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129587670</v>
+        <v>129587685</v>
       </c>
       <c r="B26" t="n">
-        <v>57733</v>
+        <v>100969</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3082,10 +3082,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>638333</v>
+        <v>638463</v>
       </c>
       <c r="R26" t="n">
-        <v>6634980</v>
+        <v>6634889</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3147,7 +3147,7 @@
         <v>129587677</v>
       </c>
       <c r="B27" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>129587681</v>
       </c>
       <c r="B28" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>129587667</v>
       </c>
       <c r="B29" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3440,62 +3440,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129598790</v>
+        <v>129597548</v>
       </c>
       <c r="B30" t="n">
-        <v>98778</v>
+        <v>97026</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>638333</v>
+        <v>638336</v>
       </c>
       <c r="R30" t="n">
-        <v>6634812</v>
+        <v>6634702</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3524,7 +3510,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3534,7 +3520,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3561,48 +3547,62 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129597548</v>
+        <v>129598790</v>
       </c>
       <c r="B31" t="n">
-        <v>97024</v>
+        <v>98780</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>638336</v>
+        <v>638333</v>
       </c>
       <c r="R31" t="n">
-        <v>6634702</v>
+        <v>6634812</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3671,7 +3671,7 @@
         <v>129605451</v>
       </c>
       <c r="B32" t="n">
-        <v>92915</v>
+        <v>92917</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>129599980</v>
       </c>
       <c r="B33" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3891,62 +3891,44 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129599353</v>
+        <v>129598714</v>
       </c>
       <c r="B34" t="n">
-        <v>98778</v>
+        <v>91619</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>638395</v>
+        <v>638323</v>
       </c>
       <c r="R34" t="n">
-        <v>6634786</v>
+        <v>6634794</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3975,7 +3957,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -3985,7 +3967,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Rikligt på undersidan av döda grenar på levande äldre gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4012,44 +3999,62 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129598714</v>
+        <v>129598966</v>
       </c>
       <c r="B35" t="n">
-        <v>91617</v>
+        <v>98780</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>638323</v>
+        <v>638348</v>
       </c>
       <c r="R35" t="n">
-        <v>6634794</v>
+        <v>6634797</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4078,7 +4083,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4088,12 +4093,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Rikligt på undersidan av döda grenar på levande äldre gran.</t>
+          <t>3 vinterståndare</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4120,10 +4125,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129598966</v>
+        <v>129599353</v>
       </c>
       <c r="B36" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4150,7 +4155,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4160,7 +4165,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4169,13 +4174,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>638348</v>
+        <v>638395</v>
       </c>
       <c r="R36" t="n">
-        <v>6634797</v>
+        <v>6634786</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4204,7 +4209,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4214,12 +4219,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>3 vinterståndare</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4249,7 +4249,7 @@
         <v>129599503</v>
       </c>
       <c r="B37" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>129605436</v>
       </c>
       <c r="B39" t="n">
-        <v>97024</v>
+        <v>97026</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
         <v>129605441</v>
       </c>
       <c r="B40" t="n">
-        <v>91370</v>
+        <v>91372</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4659,10 +4659,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129599955</v>
+        <v>129599775</v>
       </c>
       <c r="B41" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4703,13 +4703,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>638428</v>
+        <v>638435</v>
       </c>
       <c r="R41" t="n">
         <v>6634839</v>
       </c>
       <c r="S41" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4775,10 +4775,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129597954</v>
+        <v>129599955</v>
       </c>
       <c r="B42" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4805,17 +4805,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4824,13 +4819,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>638325</v>
+        <v>638428</v>
       </c>
       <c r="R42" t="n">
-        <v>6634719</v>
+        <v>6634839</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4859,7 +4854,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4869,12 +4864,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>3 vinterståndare</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4889,22 +4879,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129599775</v>
+        <v>129597954</v>
       </c>
       <c r="B43" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4931,12 +4921,17 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4945,13 +4940,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>638435</v>
+        <v>638325</v>
       </c>
       <c r="R43" t="n">
-        <v>6634839</v>
+        <v>6634719</v>
       </c>
       <c r="S43" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4980,7 +4975,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -4990,7 +4985,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>3 vinterståndare</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5005,64 +5005,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129601221</v>
+        <v>129602955</v>
       </c>
       <c r="B44" t="n">
-        <v>98778</v>
+        <v>57733</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>638294</v>
+        <v>638310</v>
       </c>
       <c r="R44" t="n">
-        <v>6634962</v>
+        <v>6634749</v>
       </c>
       <c r="S44" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5091,7 +5087,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5101,7 +5097,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Hack av spillkråka</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5128,10 +5129,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129598225</v>
+        <v>129601221</v>
       </c>
       <c r="B45" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5158,17 +5159,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5177,13 +5168,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>638330</v>
+        <v>638294</v>
       </c>
       <c r="R45" t="n">
-        <v>6634715</v>
+        <v>6634962</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5212,7 +5203,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5222,12 +5213,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>2 vinterståndare</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5242,22 +5228,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129599067</v>
+        <v>129598225</v>
       </c>
       <c r="B46" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5284,7 +5270,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5303,13 +5289,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>638355</v>
+        <v>638330</v>
       </c>
       <c r="R46" t="n">
-        <v>6634788</v>
+        <v>6634715</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5338,7 +5324,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5348,12 +5334,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>En vinterståndare</t>
+          <t>2 vinterståndare</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5380,48 +5366,62 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129602955</v>
+        <v>129599067</v>
       </c>
       <c r="B47" t="n">
-        <v>57733</v>
+        <v>98780</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>638310</v>
+        <v>638355</v>
       </c>
       <c r="R47" t="n">
-        <v>6634749</v>
+        <v>6634788</v>
       </c>
       <c r="S47" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Hack av spillkråka</t>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5480,12 +5480,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5495,7 +5495,7 @@
         <v>129600150</v>
       </c>
       <c r="B48" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>129602225</v>
       </c>
       <c r="B49" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>129602684</v>
       </c>
       <c r="B50" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5860,10 +5860,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129605439</v>
+        <v>129599511</v>
       </c>
       <c r="B51" t="n">
-        <v>57733</v>
+        <v>91599</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5871,37 +5871,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>638277</v>
+        <v>638406</v>
       </c>
       <c r="R51" t="n">
-        <v>6634933</v>
+        <v>6634775</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5928,9 +5928,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5945,60 +5955,69 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129599511</v>
+        <v>129599969</v>
       </c>
       <c r="B52" t="n">
-        <v>91597</v>
+        <v>98780</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>638406</v>
+        <v>638428</v>
       </c>
       <c r="R52" t="n">
-        <v>6634775</v>
+        <v>6634835</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6027,7 +6046,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6037,7 +6056,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6052,22 +6071,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129599969</v>
+        <v>129599963</v>
       </c>
       <c r="B53" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6099,7 +6118,12 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6108,13 +6132,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>638428</v>
+        <v>638420</v>
       </c>
       <c r="R53" t="n">
-        <v>6634835</v>
+        <v>6634840</v>
       </c>
       <c r="S53" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6168,22 +6192,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129599963</v>
+        <v>129599772</v>
       </c>
       <c r="B54" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6210,7 +6234,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6220,7 +6244,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6229,13 +6253,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>638420</v>
+        <v>638399</v>
       </c>
       <c r="R54" t="n">
-        <v>6634840</v>
+        <v>6634806</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6264,7 +6288,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6274,7 +6298,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6301,62 +6330,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129599772</v>
+        <v>129605439</v>
       </c>
       <c r="B55" t="n">
-        <v>98778</v>
+        <v>57733</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>638399</v>
+        <v>638277</v>
       </c>
       <c r="R55" t="n">
-        <v>6634806</v>
+        <v>6634933</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6383,24 +6398,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6415,12 +6415,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6430,7 +6430,7 @@
         <v>129602370</v>
       </c>
       <c r="B56" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>129602720</v>
       </c>
       <c r="B58" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>129601983</v>
       </c>
       <c r="B59" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>129602223</v>
       </c>
       <c r="B60" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         <v>129600091</v>
       </c>
       <c r="B63" t="n">
-        <v>92917</v>
+        <v>92919</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>129605452</v>
       </c>
       <c r="B65" t="n">
-        <v>92915</v>
+        <v>92917</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7664,48 +7664,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129605437</v>
+        <v>129601121</v>
       </c>
       <c r="B67" t="n">
-        <v>92315</v>
+        <v>91823</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3298</v>
+        <v>1106</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>638356</v>
+        <v>638329</v>
       </c>
       <c r="R67" t="n">
-        <v>6634677</v>
+        <v>6634973</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7732,9 +7732,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7749,60 +7759,60 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129601121</v>
+        <v>129605437</v>
       </c>
       <c r="B68" t="n">
-        <v>91821</v>
+        <v>92317</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1106</v>
+        <v>3298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>638329</v>
+        <v>638356</v>
       </c>
       <c r="R68" t="n">
-        <v>6634973</v>
+        <v>6634677</v>
       </c>
       <c r="S68" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7829,19 +7839,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7856,65 +7856,69 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129605449</v>
+        <v>129602574</v>
       </c>
       <c r="B69" t="n">
-        <v>4779</v>
+        <v>98780</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>638301</v>
+        <v>638309</v>
       </c>
       <c r="R69" t="n">
-        <v>6634752</v>
+        <v>6634813</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7941,14 +7945,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7957,76 +7966,66 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129602574</v>
+        <v>129598997</v>
       </c>
       <c r="B70" t="n">
-        <v>98778</v>
+        <v>92249</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>638309</v>
+        <v>638351</v>
       </c>
       <c r="R70" t="n">
-        <v>6634813</v>
+        <v>6634790</v>
       </c>
       <c r="S70" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8055,7 +8054,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8065,7 +8064,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8080,12 +8079,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8204,10 +8203,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129598997</v>
+        <v>129605449</v>
       </c>
       <c r="B72" t="n">
-        <v>92247</v>
+        <v>4779</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8215,37 +8214,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1339</v>
+        <v>102306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>638351</v>
+        <v>638301</v>
       </c>
       <c r="R72" t="n">
-        <v>6634790</v>
+        <v>6634752</v>
       </c>
       <c r="S72" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8272,19 +8276,14 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>11:45</t>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8293,18 +8292,19 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -3668,48 +3668,62 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129605451</v>
+        <v>129599980</v>
       </c>
       <c r="B32" t="n">
-        <v>92917</v>
+        <v>98780</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>638325</v>
+        <v>638416</v>
       </c>
       <c r="R32" t="n">
-        <v>6634691</v>
+        <v>6634840</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3736,9 +3750,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>2 vinterståndare</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3753,74 +3782,60 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129599980</v>
+        <v>129605451</v>
       </c>
       <c r="B33" t="n">
-        <v>98780</v>
+        <v>92917</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>638416</v>
+        <v>638325</v>
       </c>
       <c r="R33" t="n">
-        <v>6634840</v>
+        <v>6634691</v>
       </c>
       <c r="S33" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3847,24 +3862,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>2 vinterståndare</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3879,56 +3879,74 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129598714</v>
+        <v>129598966</v>
       </c>
       <c r="B34" t="n">
-        <v>91619</v>
+        <v>98780</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>638323</v>
+        <v>638348</v>
       </c>
       <c r="R34" t="n">
-        <v>6634794</v>
+        <v>6634797</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3957,7 +3975,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -3967,12 +3985,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Rikligt på undersidan av döda grenar på levande äldre gran.</t>
+          <t>3 vinterståndare</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3999,7 +4017,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129598966</v>
+        <v>129599353</v>
       </c>
       <c r="B35" t="n">
         <v>98780</v>
@@ -4029,7 +4047,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4039,7 +4057,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4048,13 +4066,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>638348</v>
+        <v>638395</v>
       </c>
       <c r="R35" t="n">
-        <v>6634797</v>
+        <v>6634786</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4083,7 +4101,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4093,12 +4111,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>3 vinterståndare</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4125,62 +4138,44 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129599353</v>
+        <v>129598714</v>
       </c>
       <c r="B36" t="n">
-        <v>98780</v>
+        <v>91619</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>638395</v>
+        <v>638323</v>
       </c>
       <c r="R36" t="n">
-        <v>6634786</v>
+        <v>6634794</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4209,7 +4204,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4219,7 +4214,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Rikligt på undersidan av döda grenar på levande äldre gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5860,10 +5860,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129599511</v>
+        <v>129605439</v>
       </c>
       <c r="B51" t="n">
-        <v>91599</v>
+        <v>57733</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5871,37 +5871,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>638406</v>
+        <v>638277</v>
       </c>
       <c r="R51" t="n">
-        <v>6634775</v>
+        <v>6634933</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5928,19 +5928,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>12:05</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5955,12 +5945,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6330,10 +6320,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129605439</v>
+        <v>129599511</v>
       </c>
       <c r="B55" t="n">
-        <v>57733</v>
+        <v>91599</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6341,37 +6331,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>638277</v>
+        <v>638406</v>
       </c>
       <c r="R55" t="n">
-        <v>6634933</v>
+        <v>6634775</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6398,9 +6388,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6415,12 +6415,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6780,47 +6780,38 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129601983</v>
+        <v>129600817</v>
       </c>
       <c r="B59" t="n">
-        <v>98780</v>
+        <v>57733</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6829,10 +6820,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>638209</v>
+        <v>638230</v>
       </c>
       <c r="R59" t="n">
-        <v>6635047</v>
+        <v>6634962</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -6864,7 +6855,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6874,7 +6865,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6901,57 +6892,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129602223</v>
+        <v>129605440</v>
       </c>
       <c r="B60" t="n">
-        <v>98780</v>
+        <v>57733</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>638236</v>
+        <v>638309</v>
       </c>
       <c r="R60" t="n">
-        <v>6634982</v>
+        <v>6634908</v>
       </c>
       <c r="S60" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6978,19 +6960,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>14:09</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7005,50 +6977,59 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129600817</v>
+        <v>129601983</v>
       </c>
       <c r="B61" t="n">
-        <v>57733</v>
+        <v>98780</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7057,10 +7038,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>638230</v>
+        <v>638209</v>
       </c>
       <c r="R61" t="n">
-        <v>6634962</v>
+        <v>6635047</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
@@ -7092,7 +7073,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7102,7 +7083,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7129,48 +7110,57 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129605440</v>
+        <v>129602223</v>
       </c>
       <c r="B62" t="n">
-        <v>57733</v>
+        <v>98780</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>638309</v>
+        <v>638236</v>
       </c>
       <c r="R62" t="n">
-        <v>6634908</v>
+        <v>6634982</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7197,9 +7187,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7214,12 +7214,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7868,57 +7868,53 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129602574</v>
+        <v>129605449</v>
       </c>
       <c r="B69" t="n">
-        <v>98780</v>
+        <v>4779</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>638309</v>
+        <v>638301</v>
       </c>
       <c r="R69" t="n">
-        <v>6634813</v>
+        <v>6634752</v>
       </c>
       <c r="S69" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7945,19 +7941,14 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>14:29</t>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7966,66 +7957,76 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129598997</v>
+        <v>129602574</v>
       </c>
       <c r="B70" t="n">
-        <v>92249</v>
+        <v>98780</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>638351</v>
+        <v>638309</v>
       </c>
       <c r="R70" t="n">
-        <v>6634790</v>
+        <v>6634813</v>
       </c>
       <c r="S70" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8054,7 +8055,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8064,7 +8065,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8079,12 +8080,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8203,10 +8204,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129605449</v>
+        <v>129598997</v>
       </c>
       <c r="B72" t="n">
-        <v>4779</v>
+        <v>92249</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8214,42 +8215,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>102306</v>
+        <v>1339</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>638301</v>
+        <v>638351</v>
       </c>
       <c r="R72" t="n">
-        <v>6634752</v>
+        <v>6634790</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8276,14 +8272,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8292,19 +8293,18 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -3891,62 +3891,44 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129598966</v>
+        <v>129598714</v>
       </c>
       <c r="B34" t="n">
-        <v>98780</v>
+        <v>91619</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>638348</v>
+        <v>638323</v>
       </c>
       <c r="R34" t="n">
-        <v>6634797</v>
+        <v>6634794</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3975,7 +3957,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -3985,12 +3967,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>3 vinterståndare</t>
+          <t>Rikligt på undersidan av döda grenar på levande äldre gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4017,7 +3999,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129599353</v>
+        <v>129598966</v>
       </c>
       <c r="B35" t="n">
         <v>98780</v>
@@ -4047,7 +4029,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4057,7 +4039,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4066,13 +4048,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>638395</v>
+        <v>638348</v>
       </c>
       <c r="R35" t="n">
-        <v>6634786</v>
+        <v>6634797</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4101,7 +4083,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4111,7 +4093,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>3 vinterståndare</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4138,44 +4125,62 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129598714</v>
+        <v>129599353</v>
       </c>
       <c r="B36" t="n">
-        <v>91619</v>
+        <v>98780</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>638323</v>
+        <v>638395</v>
       </c>
       <c r="R36" t="n">
-        <v>6634794</v>
+        <v>6634786</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4204,7 +4209,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4214,12 +4219,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:29</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Rikligt på undersidan av döda grenar på levande äldre gran.</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4246,48 +4246,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129599503</v>
+        <v>129599884</v>
       </c>
       <c r="B37" t="n">
-        <v>98780</v>
+        <v>57733</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>638325</v>
+        <v>638397</v>
       </c>
       <c r="R37" t="n">
-        <v>6634846</v>
+        <v>6634819</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4316,7 +4321,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4326,7 +4331,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4341,65 +4346,60 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anders Broms</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anders Broms</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129599884</v>
+        <v>129599503</v>
       </c>
       <c r="B38" t="n">
-        <v>57733</v>
+        <v>98780</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>638397</v>
+        <v>638325</v>
       </c>
       <c r="R38" t="n">
-        <v>6634819</v>
+        <v>6634846</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4453,12 +4453,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Broms</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Broms</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5957,57 +5957,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129599969</v>
+        <v>129599511</v>
       </c>
       <c r="B52" t="n">
-        <v>98780</v>
+        <v>91599</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>638428</v>
+        <v>638406</v>
       </c>
       <c r="R52" t="n">
-        <v>6634835</v>
+        <v>6634775</v>
       </c>
       <c r="S52" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6036,7 +6027,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6046,7 +6037,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6061,19 +6052,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129599963</v>
+        <v>129599969</v>
       </c>
       <c r="B53" t="n">
         <v>98780</v>
@@ -6108,12 +6099,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6122,13 +6108,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>638420</v>
+        <v>638428</v>
       </c>
       <c r="R53" t="n">
-        <v>6634840</v>
+        <v>6634835</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6182,19 +6168,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129599772</v>
+        <v>129599963</v>
       </c>
       <c r="B54" t="n">
         <v>98780</v>
@@ -6224,7 +6210,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6234,7 +6220,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6243,13 +6229,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>638399</v>
+        <v>638420</v>
       </c>
       <c r="R54" t="n">
-        <v>6634806</v>
+        <v>6634840</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6278,7 +6264,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6288,12 +6274,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>En vinterståndare</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6320,45 +6301,59 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129599511</v>
+        <v>129599772</v>
       </c>
       <c r="B55" t="n">
-        <v>91599</v>
+        <v>98780</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>638406</v>
+        <v>638399</v>
       </c>
       <c r="R55" t="n">
-        <v>6634775</v>
+        <v>6634806</v>
       </c>
       <c r="S55" t="n">
         <v>4</v>
@@ -6390,7 +6385,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6400,7 +6395,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -978,7 +978,7 @@
         <v>129529667</v>
       </c>
       <c r="B5" t="n">
-        <v>97026</v>
+        <v>97036</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>129529668</v>
       </c>
       <c r="B17" t="n">
-        <v>97026</v>
+        <v>97036</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>129587678</v>
       </c>
       <c r="B21" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>129587673</v>
       </c>
       <c r="B22" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>129587679</v>
       </c>
       <c r="B23" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>129587676</v>
       </c>
       <c r="B24" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2950,32 +2950,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129587670</v>
+        <v>129587685</v>
       </c>
       <c r="B25" t="n">
-        <v>57733</v>
+        <v>100979</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>638333</v>
+        <v>638463</v>
       </c>
       <c r="R25" t="n">
-        <v>6634980</v>
+        <v>6634889</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3047,32 +3047,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129587685</v>
+        <v>129587670</v>
       </c>
       <c r="B26" t="n">
-        <v>100969</v>
+        <v>57733</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3082,10 +3082,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>638463</v>
+        <v>638333</v>
       </c>
       <c r="R26" t="n">
-        <v>6634889</v>
+        <v>6634980</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3147,7 +3147,7 @@
         <v>129587677</v>
       </c>
       <c r="B27" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>129587681</v>
       </c>
       <c r="B28" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>129597548</v>
       </c>
       <c r="B30" t="n">
-        <v>97026</v>
+        <v>97036</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>129598790</v>
       </c>
       <c r="B31" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>129599980</v>
       </c>
       <c r="B32" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3891,44 +3891,62 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129598714</v>
+        <v>129599353</v>
       </c>
       <c r="B34" t="n">
-        <v>91619</v>
+        <v>98790</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>638323</v>
+        <v>638395</v>
       </c>
       <c r="R34" t="n">
-        <v>6634794</v>
+        <v>6634786</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3957,7 +3975,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -3967,12 +3985,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:29</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Rikligt på undersidan av döda grenar på levande äldre gran.</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4002,7 +4015,7 @@
         <v>129598966</v>
       </c>
       <c r="B35" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4125,62 +4138,44 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129599353</v>
+        <v>129598714</v>
       </c>
       <c r="B36" t="n">
-        <v>98780</v>
+        <v>91619</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>638395</v>
+        <v>638323</v>
       </c>
       <c r="R36" t="n">
-        <v>6634786</v>
+        <v>6634794</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4209,7 +4204,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4219,7 +4214,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Rikligt på undersidan av döda grenar på levande äldre gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4246,53 +4246,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129599884</v>
+        <v>129599503</v>
       </c>
       <c r="B37" t="n">
-        <v>57733</v>
+        <v>98790</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>638397</v>
+        <v>638325</v>
       </c>
       <c r="R37" t="n">
-        <v>6634819</v>
+        <v>6634846</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4321,7 +4316,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4331,7 +4326,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4346,60 +4341,65 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Broms</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Broms</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129599503</v>
+        <v>129599884</v>
       </c>
       <c r="B38" t="n">
-        <v>98780</v>
+        <v>57733</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>638325</v>
+        <v>638397</v>
       </c>
       <c r="R38" t="n">
-        <v>6634846</v>
+        <v>6634819</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4453,12 +4453,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anders Broms</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anders Broms</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4468,7 +4468,7 @@
         <v>129605436</v>
       </c>
       <c r="B39" t="n">
-        <v>97026</v>
+        <v>97036</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4659,10 +4659,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129599775</v>
+        <v>129597954</v>
       </c>
       <c r="B41" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4689,12 +4689,17 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4703,13 +4708,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>638435</v>
+        <v>638325</v>
       </c>
       <c r="R41" t="n">
-        <v>6634839</v>
+        <v>6634719</v>
       </c>
       <c r="S41" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4738,7 +4743,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4748,7 +4753,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>3 vinterståndare</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4763,12 +4773,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -4778,7 +4788,7 @@
         <v>129599955</v>
       </c>
       <c r="B42" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4891,10 +4901,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129597954</v>
+        <v>129599775</v>
       </c>
       <c r="B43" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4921,17 +4931,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4940,13 +4945,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>638325</v>
+        <v>638435</v>
       </c>
       <c r="R43" t="n">
-        <v>6634719</v>
+        <v>6634839</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4975,7 +4980,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -4985,12 +4990,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>3 vinterståndare</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5005,12 +5005,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5132,7 +5132,7 @@
         <v>129601221</v>
       </c>
       <c r="B45" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>129598225</v>
       </c>
       <c r="B46" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>129599067</v>
       </c>
       <c r="B47" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         <v>129600150</v>
       </c>
       <c r="B48" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5613,10 +5613,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129602225</v>
+        <v>129602684</v>
       </c>
       <c r="B49" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5662,13 +5662,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>638237</v>
+        <v>638332</v>
       </c>
       <c r="R49" t="n">
-        <v>6635004</v>
+        <v>6634693</v>
       </c>
       <c r="S49" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5707,12 +5707,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>En vinterståndare</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5739,10 +5734,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129602684</v>
+        <v>129602225</v>
       </c>
       <c r="B50" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5769,7 +5764,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5779,7 +5774,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5788,13 +5783,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>638332</v>
+        <v>638237</v>
       </c>
       <c r="R50" t="n">
-        <v>6634693</v>
+        <v>6635004</v>
       </c>
       <c r="S50" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5823,7 +5818,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5833,7 +5828,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5860,48 +5860,57 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129605439</v>
+        <v>129599969</v>
       </c>
       <c r="B51" t="n">
-        <v>57733</v>
+        <v>98790</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>638277</v>
+        <v>638428</v>
       </c>
       <c r="R51" t="n">
-        <v>6634933</v>
+        <v>6634835</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5928,9 +5937,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5945,57 +5964,71 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129599511</v>
+        <v>129599772</v>
       </c>
       <c r="B52" t="n">
-        <v>91599</v>
+        <v>98790</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>638406</v>
+        <v>638399</v>
       </c>
       <c r="R52" t="n">
-        <v>6634775</v>
+        <v>6634806</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6027,7 +6060,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6037,7 +6070,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6064,10 +6102,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129599969</v>
+        <v>129599963</v>
       </c>
       <c r="B53" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6099,7 +6137,12 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6108,13 +6151,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>638428</v>
+        <v>638420</v>
       </c>
       <c r="R53" t="n">
-        <v>6634835</v>
+        <v>6634840</v>
       </c>
       <c r="S53" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6168,74 +6211,60 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129599963</v>
+        <v>129605439</v>
       </c>
       <c r="B54" t="n">
-        <v>98780</v>
+        <v>57733</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>638420</v>
+        <v>638277</v>
       </c>
       <c r="R54" t="n">
-        <v>6634840</v>
+        <v>6634933</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6262,19 +6291,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>12:24</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6289,71 +6308,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129599772</v>
+        <v>129599511</v>
       </c>
       <c r="B55" t="n">
-        <v>98780</v>
+        <v>91599</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>638399</v>
+        <v>638406</v>
       </c>
       <c r="R55" t="n">
-        <v>6634806</v>
+        <v>6634775</v>
       </c>
       <c r="S55" t="n">
         <v>4</v>
@@ -6385,7 +6390,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6395,12 +6400,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>En vinterståndare</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6430,7 +6430,7 @@
         <v>129602370</v>
       </c>
       <c r="B56" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6548,57 +6548,57 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129596091</v>
+        <v>129602720</v>
       </c>
       <c r="B57" t="n">
-        <v>57733</v>
+        <v>98790</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Orreboda, Orreboda, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>638323</v>
+        <v>638301</v>
       </c>
       <c r="R57" t="n">
-        <v>6634555</v>
+        <v>6634767</v>
       </c>
       <c r="S57" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6652,69 +6652,69 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129602720</v>
+        <v>129596091</v>
       </c>
       <c r="B58" t="n">
-        <v>98780</v>
+        <v>57733</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Orreboda, Orreboda, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>638301</v>
+        <v>638323</v>
       </c>
       <c r="R58" t="n">
-        <v>6634767</v>
+        <v>6634555</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6753,7 +6753,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6768,19 +6768,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129600817</v>
+        <v>129605440</v>
       </c>
       <c r="B59" t="n">
         <v>57733</v>
@@ -6809,24 +6809,19 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>638230</v>
+        <v>638309</v>
       </c>
       <c r="R59" t="n">
-        <v>6634962</v>
+        <v>6634908</v>
       </c>
       <c r="S59" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6853,19 +6848,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6880,19 +6865,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129605440</v>
+        <v>129600817</v>
       </c>
       <c r="B60" t="n">
         <v>57733</v>
@@ -6921,19 +6906,24 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>638309</v>
+        <v>638230</v>
       </c>
       <c r="R60" t="n">
-        <v>6634908</v>
+        <v>6634962</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6960,9 +6950,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6977,12 +6977,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6992,7 +6992,7 @@
         <v>129601983</v>
       </c>
       <c r="B61" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>129602223</v>
       </c>
       <c r="B62" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7868,53 +7868,57 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129605449</v>
+        <v>129602574</v>
       </c>
       <c r="B69" t="n">
-        <v>4779</v>
+        <v>98790</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>638301</v>
+        <v>638309</v>
       </c>
       <c r="R69" t="n">
-        <v>6634752</v>
+        <v>6634813</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7941,14 +7945,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7957,76 +7966,66 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129602574</v>
+        <v>129600760</v>
       </c>
       <c r="B70" t="n">
-        <v>98780</v>
+        <v>57733</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>638309</v>
+        <v>638304</v>
       </c>
       <c r="R70" t="n">
-        <v>6634813</v>
+        <v>6634890</v>
       </c>
       <c r="S70" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8055,7 +8054,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8065,7 +8064,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Hack av spillkråka</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8092,48 +8096,53 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129600760</v>
+        <v>129605449</v>
       </c>
       <c r="B71" t="n">
-        <v>57733</v>
+        <v>4779</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>638304</v>
+        <v>638301</v>
       </c>
       <c r="R71" t="n">
-        <v>6634890</v>
+        <v>6634752</v>
       </c>
       <c r="S71" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8160,24 +8169,14 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Hack av spillkråka</t>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8186,18 +8185,19 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -1863,32 +1863,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129529669</v>
+        <v>129529664</v>
       </c>
       <c r="B14" t="n">
-        <v>91563</v>
+        <v>91823</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>1106</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1898,10 +1898,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>638445</v>
+        <v>638322</v>
       </c>
       <c r="R14" t="n">
-        <v>6634890</v>
+        <v>6634962</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1960,32 +1960,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129529664</v>
+        <v>129529669</v>
       </c>
       <c r="B15" t="n">
-        <v>91823</v>
+        <v>91563</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1106</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>638322</v>
+        <v>638445</v>
       </c>
       <c r="R15" t="n">
-        <v>6634962</v>
+        <v>6634890</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -3668,62 +3668,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129599980</v>
+        <v>129605451</v>
       </c>
       <c r="B32" t="n">
-        <v>98790</v>
+        <v>92917</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>638416</v>
+        <v>638325</v>
       </c>
       <c r="R32" t="n">
-        <v>6634840</v>
+        <v>6634691</v>
       </c>
       <c r="S32" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3750,24 +3736,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>2 vinterståndare</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3782,60 +3753,74 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129605451</v>
+        <v>129599980</v>
       </c>
       <c r="B33" t="n">
-        <v>92917</v>
+        <v>98790</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>638325</v>
+        <v>638416</v>
       </c>
       <c r="R33" t="n">
-        <v>6634691</v>
+        <v>6634840</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3862,9 +3847,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>2 vinterståndare</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3879,12 +3879,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -5017,48 +5017,52 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129602955</v>
+        <v>129601221</v>
       </c>
       <c r="B44" t="n">
-        <v>57733</v>
+        <v>98790</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>638310</v>
+        <v>638294</v>
       </c>
       <c r="R44" t="n">
-        <v>6634749</v>
+        <v>6634962</v>
       </c>
       <c r="S44" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5087,7 +5091,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5097,12 +5101,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Hack av spillkråka</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5129,7 +5128,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129601221</v>
+        <v>129598225</v>
       </c>
       <c r="B45" t="n">
         <v>98790</v>
@@ -5159,7 +5158,17 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5168,13 +5177,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>638294</v>
+        <v>638330</v>
       </c>
       <c r="R45" t="n">
-        <v>6634962</v>
+        <v>6634715</v>
       </c>
       <c r="S45" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5203,7 +5212,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5213,7 +5222,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>2 vinterståndare</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5228,19 +5242,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129598225</v>
+        <v>129599067</v>
       </c>
       <c r="B46" t="n">
         <v>98790</v>
@@ -5270,7 +5284,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5289,13 +5303,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>638330</v>
+        <v>638355</v>
       </c>
       <c r="R46" t="n">
-        <v>6634715</v>
+        <v>6634788</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5324,7 +5338,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5334,12 +5348,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>2 vinterståndare</t>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5366,62 +5380,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129599067</v>
+        <v>129602955</v>
       </c>
       <c r="B47" t="n">
-        <v>98790</v>
+        <v>57733</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>638355</v>
+        <v>638310</v>
       </c>
       <c r="R47" t="n">
-        <v>6634788</v>
+        <v>6634749</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>En vinterståndare</t>
+          <t>Hack av spillkråka</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5480,12 +5480,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5860,57 +5860,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129599969</v>
+        <v>129605439</v>
       </c>
       <c r="B51" t="n">
-        <v>98790</v>
+        <v>57733</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>638428</v>
+        <v>638277</v>
       </c>
       <c r="R51" t="n">
-        <v>6634835</v>
+        <v>6634933</v>
       </c>
       <c r="S51" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5937,19 +5928,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>12:24</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5964,71 +5945,57 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129599772</v>
+        <v>129599511</v>
       </c>
       <c r="B52" t="n">
-        <v>98790</v>
+        <v>91599</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>638399</v>
+        <v>638406</v>
       </c>
       <c r="R52" t="n">
-        <v>6634806</v>
+        <v>6634775</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6060,7 +6027,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6070,12 +6037,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>En vinterståndare</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6102,7 +6064,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129599963</v>
+        <v>129599969</v>
       </c>
       <c r="B53" t="n">
         <v>98790</v>
@@ -6137,12 +6099,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6151,13 +6108,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>638420</v>
+        <v>638428</v>
       </c>
       <c r="R53" t="n">
-        <v>6634840</v>
+        <v>6634835</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6211,60 +6168,74 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129605439</v>
+        <v>129599772</v>
       </c>
       <c r="B54" t="n">
-        <v>57733</v>
+        <v>98790</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>638277</v>
+        <v>638399</v>
       </c>
       <c r="R54" t="n">
-        <v>6634933</v>
+        <v>6634806</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6291,9 +6262,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6308,60 +6294,74 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129599511</v>
+        <v>129599963</v>
       </c>
       <c r="B55" t="n">
-        <v>91599</v>
+        <v>98790</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>638406</v>
+        <v>638420</v>
       </c>
       <c r="R55" t="n">
-        <v>6634775</v>
+        <v>6634840</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7664,48 +7664,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129601121</v>
+        <v>129605437</v>
       </c>
       <c r="B67" t="n">
-        <v>91823</v>
+        <v>92317</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1106</v>
+        <v>3298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>638329</v>
+        <v>638356</v>
       </c>
       <c r="R67" t="n">
-        <v>6634973</v>
+        <v>6634677</v>
       </c>
       <c r="S67" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7732,19 +7732,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7759,60 +7749,60 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129605437</v>
+        <v>129601121</v>
       </c>
       <c r="B68" t="n">
-        <v>92317</v>
+        <v>91823</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3298</v>
+        <v>1106</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>638356</v>
+        <v>638329</v>
       </c>
       <c r="R68" t="n">
-        <v>6634677</v>
+        <v>6634973</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7839,9 +7829,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7856,12 +7856,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -5017,52 +5017,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129601221</v>
+        <v>129602955</v>
       </c>
       <c r="B44" t="n">
-        <v>98790</v>
+        <v>57733</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>638294</v>
+        <v>638310</v>
       </c>
       <c r="R44" t="n">
-        <v>6634962</v>
+        <v>6634749</v>
       </c>
       <c r="S44" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5091,7 +5087,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5101,7 +5097,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Hack av spillkråka</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5380,48 +5381,52 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129602955</v>
+        <v>129601221</v>
       </c>
       <c r="B47" t="n">
-        <v>57733</v>
+        <v>98790</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>638310</v>
+        <v>638294</v>
       </c>
       <c r="R47" t="n">
-        <v>6634749</v>
+        <v>6634962</v>
       </c>
       <c r="S47" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5450,7 +5455,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5460,12 +5465,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Hack av spillkråka</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5860,48 +5860,57 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129605439</v>
+        <v>129599969</v>
       </c>
       <c r="B51" t="n">
-        <v>57733</v>
+        <v>98790</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>638277</v>
+        <v>638428</v>
       </c>
       <c r="R51" t="n">
-        <v>6634933</v>
+        <v>6634835</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5928,9 +5937,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5945,57 +5964,71 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129599511</v>
+        <v>129599772</v>
       </c>
       <c r="B52" t="n">
-        <v>91599</v>
+        <v>98790</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>638406</v>
+        <v>638399</v>
       </c>
       <c r="R52" t="n">
-        <v>6634775</v>
+        <v>6634806</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6027,7 +6060,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6037,7 +6070,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6064,7 +6102,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129599969</v>
+        <v>129599963</v>
       </c>
       <c r="B53" t="n">
         <v>98790</v>
@@ -6099,7 +6137,12 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6108,13 +6151,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>638428</v>
+        <v>638420</v>
       </c>
       <c r="R53" t="n">
-        <v>6634835</v>
+        <v>6634840</v>
       </c>
       <c r="S53" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6168,74 +6211,60 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129599772</v>
+        <v>129605439</v>
       </c>
       <c r="B54" t="n">
-        <v>98790</v>
+        <v>57733</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>638399</v>
+        <v>638277</v>
       </c>
       <c r="R54" t="n">
-        <v>6634806</v>
+        <v>6634933</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6262,24 +6291,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6294,74 +6308,60 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129599963</v>
+        <v>129599511</v>
       </c>
       <c r="B55" t="n">
-        <v>98790</v>
+        <v>91599</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>638420</v>
+        <v>638406</v>
       </c>
       <c r="R55" t="n">
-        <v>6634840</v>
+        <v>6634775</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -2555,7 +2555,7 @@
         <v>129587678</v>
       </c>
       <c r="B21" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>129587673</v>
       </c>
       <c r="B22" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>129587679</v>
       </c>
       <c r="B23" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>129587676</v>
       </c>
       <c r="B24" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>129587685</v>
       </c>
       <c r="B25" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>129587670</v>
       </c>
       <c r="B26" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>129587677</v>
       </c>
       <c r="B27" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>129587681</v>
       </c>
       <c r="B28" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>129587667</v>
       </c>
       <c r="B29" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>129597548</v>
       </c>
       <c r="B30" t="n">
-        <v>97036</v>
+        <v>97040</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>129598790</v>
       </c>
       <c r="B31" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3668,48 +3668,62 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129605451</v>
+        <v>129599980</v>
       </c>
       <c r="B32" t="n">
-        <v>92917</v>
+        <v>98794</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>638325</v>
+        <v>638416</v>
       </c>
       <c r="R32" t="n">
-        <v>6634691</v>
+        <v>6634840</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3736,9 +3750,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>2 vinterståndare</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3753,74 +3782,60 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129599980</v>
+        <v>129605451</v>
       </c>
       <c r="B33" t="n">
-        <v>98790</v>
+        <v>92920</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>638416</v>
+        <v>638325</v>
       </c>
       <c r="R33" t="n">
-        <v>6634840</v>
+        <v>6634691</v>
       </c>
       <c r="S33" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3847,24 +3862,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>2 vinterståndare</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3879,22 +3879,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129599353</v>
+        <v>129598966</v>
       </c>
       <c r="B34" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3940,13 +3940,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>638395</v>
+        <v>638348</v>
       </c>
       <c r="R34" t="n">
-        <v>6634786</v>
+        <v>6634797</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -3985,7 +3985,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>3 vinterståndare</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4012,10 +4017,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129598966</v>
+        <v>129599353</v>
       </c>
       <c r="B35" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4042,7 +4047,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4052,7 +4057,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4061,13 +4066,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>638348</v>
+        <v>638395</v>
       </c>
       <c r="R35" t="n">
-        <v>6634797</v>
+        <v>6634786</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4096,7 +4101,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4106,12 +4111,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>3 vinterståndare</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4141,7 +4141,7 @@
         <v>129598714</v>
       </c>
       <c r="B36" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4246,48 +4246,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129599503</v>
+        <v>129599884</v>
       </c>
       <c r="B37" t="n">
-        <v>98790</v>
+        <v>57734</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>638325</v>
+        <v>638397</v>
       </c>
       <c r="R37" t="n">
-        <v>6634846</v>
+        <v>6634819</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4316,7 +4321,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4326,7 +4331,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4341,65 +4346,60 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anders Broms</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anders Broms</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129599884</v>
+        <v>129599503</v>
       </c>
       <c r="B38" t="n">
-        <v>57733</v>
+        <v>98794</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>638397</v>
+        <v>638325</v>
       </c>
       <c r="R38" t="n">
-        <v>6634819</v>
+        <v>6634846</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4453,12 +4453,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Broms</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Broms</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4468,7 +4468,7 @@
         <v>129605436</v>
       </c>
       <c r="B39" t="n">
-        <v>97036</v>
+        <v>97040</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
         <v>129605441</v>
       </c>
       <c r="B40" t="n">
-        <v>91372</v>
+        <v>91375</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4659,10 +4659,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129597954</v>
+        <v>129599775</v>
       </c>
       <c r="B41" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4689,17 +4689,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4708,13 +4703,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>638325</v>
+        <v>638435</v>
       </c>
       <c r="R41" t="n">
-        <v>6634719</v>
+        <v>6634839</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4743,7 +4738,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4753,12 +4748,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>3 vinterståndare</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4773,12 +4763,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -4788,7 +4778,7 @@
         <v>129599955</v>
       </c>
       <c r="B42" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4901,10 +4891,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129599775</v>
+        <v>129597954</v>
       </c>
       <c r="B43" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4931,12 +4921,17 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4945,13 +4940,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>638435</v>
+        <v>638325</v>
       </c>
       <c r="R43" t="n">
-        <v>6634839</v>
+        <v>6634719</v>
       </c>
       <c r="S43" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4980,7 +4975,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -4990,7 +4985,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>3 vinterståndare</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5005,60 +5005,74 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129602955</v>
+        <v>129598225</v>
       </c>
       <c r="B44" t="n">
-        <v>57733</v>
+        <v>98794</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>638310</v>
+        <v>638330</v>
       </c>
       <c r="R44" t="n">
-        <v>6634749</v>
+        <v>6634715</v>
       </c>
       <c r="S44" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5087,7 +5101,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5097,12 +5111,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Hack av spillkråka</t>
+          <t>2 vinterståndare</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5117,22 +5131,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129598225</v>
+        <v>129599067</v>
       </c>
       <c r="B45" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5159,7 +5173,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5178,13 +5192,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>638330</v>
+        <v>638355</v>
       </c>
       <c r="R45" t="n">
-        <v>6634715</v>
+        <v>6634788</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5213,7 +5227,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5223,12 +5237,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>2 vinterståndare</t>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5255,62 +5269,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129599067</v>
+        <v>129602955</v>
       </c>
       <c r="B46" t="n">
-        <v>98790</v>
+        <v>57734</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>638355</v>
+        <v>638310</v>
       </c>
       <c r="R46" t="n">
-        <v>6634788</v>
+        <v>6634749</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>En vinterståndare</t>
+          <t>Hack av spillkråka</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5369,12 +5369,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5384,7 +5384,7 @@
         <v>129601221</v>
       </c>
       <c r="B47" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         <v>129600150</v>
       </c>
       <c r="B48" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>129602684</v>
       </c>
       <c r="B49" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>129602225</v>
       </c>
       <c r="B50" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5860,57 +5860,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129599969</v>
+        <v>129599511</v>
       </c>
       <c r="B51" t="n">
-        <v>98790</v>
+        <v>91602</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>638428</v>
+        <v>638406</v>
       </c>
       <c r="R51" t="n">
-        <v>6634835</v>
+        <v>6634775</v>
       </c>
       <c r="S51" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5939,7 +5930,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5949,7 +5940,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5964,22 +5955,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129599772</v>
+        <v>129599969</v>
       </c>
       <c r="B52" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6006,17 +5997,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6025,13 +6011,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>638399</v>
+        <v>638428</v>
       </c>
       <c r="R52" t="n">
-        <v>6634806</v>
+        <v>6634835</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6060,7 +6046,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6070,12 +6056,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>En vinterståndare</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6090,12 +6071,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6105,7 +6086,7 @@
         <v>129599963</v>
       </c>
       <c r="B53" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6223,48 +6204,62 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129605439</v>
+        <v>129599772</v>
       </c>
       <c r="B54" t="n">
-        <v>57733</v>
+        <v>98794</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>638277</v>
+        <v>638399</v>
       </c>
       <c r="R54" t="n">
-        <v>6634933</v>
+        <v>6634806</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6291,9 +6286,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6308,22 +6318,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129599511</v>
+        <v>129605439</v>
       </c>
       <c r="B55" t="n">
-        <v>91599</v>
+        <v>57734</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6331,37 +6341,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>638406</v>
+        <v>638277</v>
       </c>
       <c r="R55" t="n">
-        <v>6634775</v>
+        <v>6634933</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6388,19 +6398,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>12:05</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6415,12 +6415,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6430,7 +6430,7 @@
         <v>129602370</v>
       </c>
       <c r="B56" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6548,57 +6548,57 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129602720</v>
+        <v>129596091</v>
       </c>
       <c r="B57" t="n">
-        <v>98790</v>
+        <v>57734</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Orreboda, Orreboda, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>638301</v>
+        <v>638323</v>
       </c>
       <c r="R57" t="n">
-        <v>6634767</v>
+        <v>6634555</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6652,69 +6652,69 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129596091</v>
+        <v>129602720</v>
       </c>
       <c r="B58" t="n">
-        <v>57733</v>
+        <v>98794</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Orreboda, Orreboda, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>638323</v>
+        <v>638301</v>
       </c>
       <c r="R58" t="n">
-        <v>6634555</v>
+        <v>6634767</v>
       </c>
       <c r="S58" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6753,7 +6753,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6768,22 +6768,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129605440</v>
+        <v>129600817</v>
       </c>
       <c r="B59" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6809,19 +6809,24 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>638309</v>
+        <v>638230</v>
       </c>
       <c r="R59" t="n">
-        <v>6634908</v>
+        <v>6634962</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6848,9 +6853,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6865,22 +6880,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129600817</v>
+        <v>129605440</v>
       </c>
       <c r="B60" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6906,24 +6921,19 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>638230</v>
+        <v>638309</v>
       </c>
       <c r="R60" t="n">
-        <v>6634962</v>
+        <v>6634908</v>
       </c>
       <c r="S60" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6950,19 +6960,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6977,12 +6977,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6992,7 +6992,7 @@
         <v>129601983</v>
       </c>
       <c r="B61" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>129602223</v>
       </c>
       <c r="B62" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         <v>129600091</v>
       </c>
       <c r="B63" t="n">
-        <v>92919</v>
+        <v>92922</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7455,48 +7455,53 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129605452</v>
+        <v>129597436</v>
       </c>
       <c r="B65" t="n">
-        <v>92917</v>
+        <v>57734</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>638324</v>
+        <v>638292</v>
       </c>
       <c r="R65" t="n">
-        <v>6634750</v>
+        <v>6634699</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7523,9 +7528,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7540,65 +7555,60 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129597436</v>
+        <v>129605452</v>
       </c>
       <c r="B66" t="n">
-        <v>57733</v>
+        <v>92920</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>638292</v>
+        <v>638324</v>
       </c>
       <c r="R66" t="n">
-        <v>6634699</v>
+        <v>6634750</v>
       </c>
       <c r="S66" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7625,19 +7635,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>10:38</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7652,12 +7652,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7667,7 +7667,7 @@
         <v>129605437</v>
       </c>
       <c r="B67" t="n">
-        <v>92317</v>
+        <v>92320</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>129601121</v>
       </c>
       <c r="B68" t="n">
-        <v>91823</v>
+        <v>91826</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7868,57 +7868,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129602574</v>
+        <v>129600760</v>
       </c>
       <c r="B69" t="n">
-        <v>98790</v>
+        <v>57734</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>638309</v>
+        <v>638304</v>
       </c>
       <c r="R69" t="n">
-        <v>6634813</v>
+        <v>6634890</v>
       </c>
       <c r="S69" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7947,7 +7938,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7957,7 +7948,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Hack av spillkråka</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7984,32 +7980,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129600760</v>
+        <v>129598997</v>
       </c>
       <c r="B70" t="n">
-        <v>57733</v>
+        <v>92252</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8019,13 +8015,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>638304</v>
+        <v>638351</v>
       </c>
       <c r="R70" t="n">
-        <v>6634890</v>
+        <v>6634790</v>
       </c>
       <c r="S70" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8054,7 +8050,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8064,12 +8060,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:04</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Hack av spillkråka</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8084,12 +8075,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8204,48 +8195,57 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129598997</v>
+        <v>129602574</v>
       </c>
       <c r="B72" t="n">
-        <v>92249</v>
+        <v>98794</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>638351</v>
+        <v>638309</v>
       </c>
       <c r="R72" t="n">
-        <v>6634790</v>
+        <v>6634813</v>
       </c>
       <c r="S72" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8284,7 +8284,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8299,12 +8299,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -2950,32 +2950,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129587685</v>
+        <v>129587670</v>
       </c>
       <c r="B25" t="n">
-        <v>100983</v>
+        <v>57734</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>638463</v>
+        <v>638333</v>
       </c>
       <c r="R25" t="n">
-        <v>6634889</v>
+        <v>6634980</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3047,32 +3047,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129587670</v>
+        <v>129587685</v>
       </c>
       <c r="B26" t="n">
-        <v>57734</v>
+        <v>100983</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3082,10 +3082,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>638333</v>
+        <v>638463</v>
       </c>
       <c r="R26" t="n">
-        <v>6634980</v>
+        <v>6634889</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -4465,32 +4465,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129605436</v>
+        <v>129605441</v>
       </c>
       <c r="B39" t="n">
-        <v>97040</v>
+        <v>91375</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>53</v>
+        <v>3215</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4500,10 +4500,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>638281</v>
+        <v>638444</v>
       </c>
       <c r="R39" t="n">
-        <v>6634960</v>
+        <v>6634897</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4562,32 +4562,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129605441</v>
+        <v>129605436</v>
       </c>
       <c r="B40" t="n">
-        <v>91375</v>
+        <v>97040</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3215</v>
+        <v>53</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4597,10 +4597,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>638444</v>
+        <v>638281</v>
       </c>
       <c r="R40" t="n">
-        <v>6634897</v>
+        <v>6634960</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5860,10 +5860,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129599511</v>
+        <v>129605439</v>
       </c>
       <c r="B51" t="n">
-        <v>91602</v>
+        <v>57734</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5871,37 +5871,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>638406</v>
+        <v>638277</v>
       </c>
       <c r="R51" t="n">
-        <v>6634775</v>
+        <v>6634933</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5928,19 +5928,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>12:05</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5955,69 +5945,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129599969</v>
+        <v>129599511</v>
       </c>
       <c r="B52" t="n">
-        <v>98794</v>
+        <v>91602</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>638428</v>
+        <v>638406</v>
       </c>
       <c r="R52" t="n">
-        <v>6634835</v>
+        <v>6634775</v>
       </c>
       <c r="S52" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6046,7 +6027,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6056,7 +6037,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6071,19 +6052,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129599963</v>
+        <v>129599969</v>
       </c>
       <c r="B53" t="n">
         <v>98794</v>
@@ -6118,12 +6099,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6132,13 +6108,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>638420</v>
+        <v>638428</v>
       </c>
       <c r="R53" t="n">
-        <v>6634840</v>
+        <v>6634835</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6192,19 +6168,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129599772</v>
+        <v>129599963</v>
       </c>
       <c r="B54" t="n">
         <v>98794</v>
@@ -6234,7 +6210,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6244,7 +6220,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6253,13 +6229,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>638399</v>
+        <v>638420</v>
       </c>
       <c r="R54" t="n">
-        <v>6634806</v>
+        <v>6634840</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6288,7 +6264,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6298,12 +6274,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>En vinterståndare</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6330,48 +6301,62 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129605439</v>
+        <v>129599772</v>
       </c>
       <c r="B55" t="n">
-        <v>57734</v>
+        <v>98794</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>638277</v>
+        <v>638399</v>
       </c>
       <c r="R55" t="n">
-        <v>6634933</v>
+        <v>6634806</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6398,9 +6383,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6415,12 +6415,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -7664,48 +7664,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129605437</v>
+        <v>129601121</v>
       </c>
       <c r="B67" t="n">
-        <v>92320</v>
+        <v>91826</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3298</v>
+        <v>1106</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>638356</v>
+        <v>638329</v>
       </c>
       <c r="R67" t="n">
-        <v>6634677</v>
+        <v>6634973</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7732,9 +7732,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7749,60 +7759,60 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129601121</v>
+        <v>129605437</v>
       </c>
       <c r="B68" t="n">
-        <v>91826</v>
+        <v>92320</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1106</v>
+        <v>3298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>638329</v>
+        <v>638356</v>
       </c>
       <c r="R68" t="n">
-        <v>6634973</v>
+        <v>6634677</v>
       </c>
       <c r="S68" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7829,19 +7839,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7856,12 +7856,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -2555,7 +2555,7 @@
         <v>129587678</v>
       </c>
       <c r="B21" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>129587673</v>
       </c>
       <c r="B22" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>129587679</v>
       </c>
       <c r="B23" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>129587676</v>
       </c>
       <c r="B24" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2950,32 +2950,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129587670</v>
+        <v>129587685</v>
       </c>
       <c r="B25" t="n">
-        <v>57734</v>
+        <v>100986</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>638333</v>
+        <v>638463</v>
       </c>
       <c r="R25" t="n">
-        <v>6634980</v>
+        <v>6634889</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3047,32 +3047,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129587685</v>
+        <v>129587670</v>
       </c>
       <c r="B26" t="n">
-        <v>100983</v>
+        <v>57737</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3082,10 +3082,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>638463</v>
+        <v>638333</v>
       </c>
       <c r="R26" t="n">
-        <v>6634889</v>
+        <v>6634980</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3147,7 +3147,7 @@
         <v>129587677</v>
       </c>
       <c r="B27" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>129587681</v>
       </c>
       <c r="B28" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>129587667</v>
       </c>
       <c r="B29" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>129597548</v>
       </c>
       <c r="B30" t="n">
-        <v>97040</v>
+        <v>97043</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>129598790</v>
       </c>
       <c r="B31" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3668,62 +3668,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129599980</v>
+        <v>129605451</v>
       </c>
       <c r="B32" t="n">
-        <v>98794</v>
+        <v>92923</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>638416</v>
+        <v>638325</v>
       </c>
       <c r="R32" t="n">
-        <v>6634840</v>
+        <v>6634691</v>
       </c>
       <c r="S32" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3750,24 +3736,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>2 vinterståndare</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3782,60 +3753,74 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129605451</v>
+        <v>129599980</v>
       </c>
       <c r="B33" t="n">
-        <v>92920</v>
+        <v>98797</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>638325</v>
+        <v>638416</v>
       </c>
       <c r="R33" t="n">
-        <v>6634691</v>
+        <v>6634840</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3862,9 +3847,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>2 vinterståndare</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3879,74 +3879,56 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129598966</v>
+        <v>129598714</v>
       </c>
       <c r="B34" t="n">
-        <v>98794</v>
+        <v>91625</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>638348</v>
+        <v>638323</v>
       </c>
       <c r="R34" t="n">
-        <v>6634797</v>
+        <v>6634794</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3975,7 +3957,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -3985,12 +3967,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>3 vinterståndare</t>
+          <t>Rikligt på undersidan av döda grenar på levande äldre gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4017,10 +3999,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129599353</v>
+        <v>129598966</v>
       </c>
       <c r="B35" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4047,7 +4029,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4057,7 +4039,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4066,13 +4048,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>638395</v>
+        <v>638348</v>
       </c>
       <c r="R35" t="n">
-        <v>6634786</v>
+        <v>6634797</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4101,7 +4083,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4111,7 +4093,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>3 vinterståndare</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4138,44 +4125,62 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129598714</v>
+        <v>129599353</v>
       </c>
       <c r="B36" t="n">
-        <v>91622</v>
+        <v>98797</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>638323</v>
+        <v>638395</v>
       </c>
       <c r="R36" t="n">
-        <v>6634794</v>
+        <v>6634786</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4204,7 +4209,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4214,12 +4219,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:29</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Rikligt på undersidan av döda grenar på levande äldre gran.</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4249,7 +4249,7 @@
         <v>129599884</v>
       </c>
       <c r="B37" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
         <v>129599503</v>
       </c>
       <c r="B38" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>129605441</v>
       </c>
       <c r="B39" t="n">
-        <v>91375</v>
+        <v>91378</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
         <v>129605436</v>
       </c>
       <c r="B40" t="n">
-        <v>97040</v>
+        <v>97043</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4659,10 +4659,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129599775</v>
+        <v>129597954</v>
       </c>
       <c r="B41" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4689,12 +4689,17 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4703,13 +4708,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>638435</v>
+        <v>638325</v>
       </c>
       <c r="R41" t="n">
-        <v>6634839</v>
+        <v>6634719</v>
       </c>
       <c r="S41" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4738,7 +4743,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4748,7 +4753,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>3 vinterståndare</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4763,22 +4773,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129599955</v>
+        <v>129599775</v>
       </c>
       <c r="B42" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4805,7 +4815,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4819,13 +4829,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>638428</v>
+        <v>638435</v>
       </c>
       <c r="R42" t="n">
         <v>6634839</v>
       </c>
       <c r="S42" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4854,7 +4864,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4864,7 +4874,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4891,10 +4901,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129597954</v>
+        <v>129599955</v>
       </c>
       <c r="B43" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4921,17 +4931,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4940,13 +4945,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>638325</v>
+        <v>638428</v>
       </c>
       <c r="R43" t="n">
-        <v>6634719</v>
+        <v>6634839</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4975,7 +4980,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -4985,12 +4990,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>3 vinterståndare</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5005,74 +5005,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129598225</v>
+        <v>129602955</v>
       </c>
       <c r="B44" t="n">
-        <v>98794</v>
+        <v>57737</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>638330</v>
+        <v>638310</v>
       </c>
       <c r="R44" t="n">
-        <v>6634715</v>
+        <v>6634749</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5101,7 +5087,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5111,12 +5097,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>2 vinterståndare</t>
+          <t>Hack av spillkråka</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5131,22 +5117,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129599067</v>
+        <v>129601221</v>
       </c>
       <c r="B45" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5173,17 +5159,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5192,13 +5168,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>638355</v>
+        <v>638294</v>
       </c>
       <c r="R45" t="n">
-        <v>6634788</v>
+        <v>6634962</v>
       </c>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5227,7 +5203,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5237,12 +5213,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>En vinterståndare</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5257,60 +5228,74 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129602955</v>
+        <v>129598225</v>
       </c>
       <c r="B46" t="n">
-        <v>57734</v>
+        <v>98797</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>638310</v>
+        <v>638330</v>
       </c>
       <c r="R46" t="n">
-        <v>6634749</v>
+        <v>6634715</v>
       </c>
       <c r="S46" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5339,7 +5324,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5349,12 +5334,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Hack av spillkråka</t>
+          <t>2 vinterståndare</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5369,22 +5354,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129601221</v>
+        <v>129599067</v>
       </c>
       <c r="B47" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5411,7 +5396,17 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5420,13 +5415,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>638294</v>
+        <v>638355</v>
       </c>
       <c r="R47" t="n">
-        <v>6634962</v>
+        <v>6634788</v>
       </c>
       <c r="S47" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5455,7 +5450,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5465,7 +5460,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5480,22 +5480,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129600150</v>
+        <v>129602225</v>
       </c>
       <c r="B48" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5541,13 +5541,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>638354</v>
+        <v>638237</v>
       </c>
       <c r="R48" t="n">
-        <v>6634767</v>
+        <v>6635004</v>
       </c>
       <c r="S48" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5586,7 +5586,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5613,10 +5618,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129602684</v>
+        <v>129600150</v>
       </c>
       <c r="B49" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5643,7 +5648,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5653,7 +5658,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5662,10 +5667,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>638332</v>
+        <v>638354</v>
       </c>
       <c r="R49" t="n">
-        <v>6634693</v>
+        <v>6634767</v>
       </c>
       <c r="S49" t="n">
         <v>4</v>
@@ -5697,7 +5702,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5707,7 +5712,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5734,10 +5739,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129602225</v>
+        <v>129602684</v>
       </c>
       <c r="B50" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5764,7 +5769,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5774,7 +5779,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5783,13 +5788,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>638237</v>
+        <v>638332</v>
       </c>
       <c r="R50" t="n">
-        <v>6635004</v>
+        <v>6634693</v>
       </c>
       <c r="S50" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5818,7 +5823,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5828,12 +5833,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>En vinterståndare</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5863,7 +5863,7 @@
         <v>129605439</v>
       </c>
       <c r="B51" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>129599511</v>
       </c>
       <c r="B52" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>129599969</v>
       </c>
       <c r="B53" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>129599963</v>
       </c>
       <c r="B54" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>129599772</v>
       </c>
       <c r="B55" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         <v>129602370</v>
       </c>
       <c r="B56" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6551,7 +6551,7 @@
         <v>129596091</v>
       </c>
       <c r="B57" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>129602720</v>
       </c>
       <c r="B58" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6780,38 +6780,47 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129600817</v>
+        <v>129601983</v>
       </c>
       <c r="B59" t="n">
-        <v>57734</v>
+        <v>98797</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6820,10 +6829,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>638230</v>
+        <v>638209</v>
       </c>
       <c r="R59" t="n">
-        <v>6634962</v>
+        <v>6635047</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -6855,7 +6864,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6865,7 +6874,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6892,48 +6901,57 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129605440</v>
+        <v>129602223</v>
       </c>
       <c r="B60" t="n">
-        <v>57734</v>
+        <v>98797</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>638309</v>
+        <v>638236</v>
       </c>
       <c r="R60" t="n">
-        <v>6634908</v>
+        <v>6634982</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6960,9 +6978,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6977,59 +7005,50 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129601983</v>
+        <v>129600817</v>
       </c>
       <c r="B61" t="n">
-        <v>98794</v>
+        <v>57737</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7038,10 +7057,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>638209</v>
+        <v>638230</v>
       </c>
       <c r="R61" t="n">
-        <v>6635047</v>
+        <v>6634962</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
@@ -7073,7 +7092,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7083,7 +7102,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7110,57 +7129,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129602223</v>
+        <v>129605440</v>
       </c>
       <c r="B62" t="n">
-        <v>98794</v>
+        <v>57737</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>638236</v>
+        <v>638309</v>
       </c>
       <c r="R62" t="n">
-        <v>6634982</v>
+        <v>6634908</v>
       </c>
       <c r="S62" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7187,19 +7197,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>14:09</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7214,12 +7214,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7229,7 +7229,7 @@
         <v>129600091</v>
       </c>
       <c r="B63" t="n">
-        <v>92922</v>
+        <v>92925</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7455,53 +7455,48 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129597436</v>
+        <v>129605452</v>
       </c>
       <c r="B65" t="n">
-        <v>57734</v>
+        <v>92923</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>638292</v>
+        <v>638324</v>
       </c>
       <c r="R65" t="n">
-        <v>6634699</v>
+        <v>6634750</v>
       </c>
       <c r="S65" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7528,19 +7523,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>10:38</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7555,60 +7540,65 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129605452</v>
+        <v>129597436</v>
       </c>
       <c r="B66" t="n">
-        <v>92920</v>
+        <v>57737</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>638324</v>
+        <v>638292</v>
       </c>
       <c r="R66" t="n">
-        <v>6634750</v>
+        <v>6634699</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7635,9 +7625,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7652,60 +7652,60 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129601121</v>
+        <v>129605437</v>
       </c>
       <c r="B67" t="n">
-        <v>91826</v>
+        <v>92323</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1106</v>
+        <v>3298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>638329</v>
+        <v>638356</v>
       </c>
       <c r="R67" t="n">
-        <v>6634973</v>
+        <v>6634677</v>
       </c>
       <c r="S67" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7732,19 +7732,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7759,60 +7749,60 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129605437</v>
+        <v>129601121</v>
       </c>
       <c r="B68" t="n">
-        <v>92320</v>
+        <v>91829</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3298</v>
+        <v>1106</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>638356</v>
+        <v>638329</v>
       </c>
       <c r="R68" t="n">
-        <v>6634677</v>
+        <v>6634973</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7839,9 +7829,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7856,60 +7856,69 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129600760</v>
+        <v>129602574</v>
       </c>
       <c r="B69" t="n">
-        <v>57734</v>
+        <v>98797</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>638304</v>
+        <v>638309</v>
       </c>
       <c r="R69" t="n">
-        <v>6634890</v>
+        <v>6634813</v>
       </c>
       <c r="S69" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7938,7 +7947,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7948,12 +7957,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:04</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Hack av spillkråka</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7980,32 +7984,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129598997</v>
+        <v>129600760</v>
       </c>
       <c r="B70" t="n">
-        <v>92252</v>
+        <v>57737</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8015,13 +8019,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>638351</v>
+        <v>638304</v>
       </c>
       <c r="R70" t="n">
-        <v>6634790</v>
+        <v>6634890</v>
       </c>
       <c r="S70" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8050,7 +8054,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8060,7 +8064,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Hack av spillkråka</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8075,12 +8084,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8195,57 +8204,48 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129602574</v>
+        <v>129598997</v>
       </c>
       <c r="B72" t="n">
-        <v>98794</v>
+        <v>92255</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>638309</v>
+        <v>638351</v>
       </c>
       <c r="R72" t="n">
-        <v>6634813</v>
+        <v>6634790</v>
       </c>
       <c r="S72" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8284,7 +8284,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8299,12 +8299,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -4659,7 +4659,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129597954</v>
+        <v>129599775</v>
       </c>
       <c r="B41" t="n">
         <v>98797</v>
@@ -4689,17 +4689,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4708,13 +4703,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>638325</v>
+        <v>638435</v>
       </c>
       <c r="R41" t="n">
-        <v>6634719</v>
+        <v>6634839</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4743,7 +4738,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4753,12 +4748,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>3 vinterståndare</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4773,19 +4763,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129599775</v>
+        <v>129599955</v>
       </c>
       <c r="B42" t="n">
         <v>98797</v>
@@ -4815,7 +4805,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4829,13 +4819,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>638435</v>
+        <v>638428</v>
       </c>
       <c r="R42" t="n">
         <v>6634839</v>
       </c>
       <c r="S42" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4864,7 +4854,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4874,7 +4864,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4901,7 +4891,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129599955</v>
+        <v>129597954</v>
       </c>
       <c r="B43" t="n">
         <v>98797</v>
@@ -4931,12 +4921,17 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4945,13 +4940,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>638428</v>
+        <v>638325</v>
       </c>
       <c r="R43" t="n">
-        <v>6634839</v>
+        <v>6634719</v>
       </c>
       <c r="S43" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4980,7 +4975,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -4990,7 +4985,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>3 vinterståndare</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5005,12 +5005,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -6548,57 +6548,57 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129596091</v>
+        <v>129602720</v>
       </c>
       <c r="B57" t="n">
-        <v>57737</v>
+        <v>98797</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Orreboda, Orreboda, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>638323</v>
+        <v>638301</v>
       </c>
       <c r="R57" t="n">
-        <v>6634555</v>
+        <v>6634767</v>
       </c>
       <c r="S57" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6652,69 +6652,69 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129602720</v>
+        <v>129596091</v>
       </c>
       <c r="B58" t="n">
-        <v>98797</v>
+        <v>57737</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Orreboda, Orreboda, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>638301</v>
+        <v>638323</v>
       </c>
       <c r="R58" t="n">
-        <v>6634767</v>
+        <v>6634555</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6753,7 +6753,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6768,12 +6768,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7868,57 +7868,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129602574</v>
+        <v>129600760</v>
       </c>
       <c r="B69" t="n">
-        <v>98797</v>
+        <v>57737</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>638309</v>
+        <v>638304</v>
       </c>
       <c r="R69" t="n">
-        <v>6634813</v>
+        <v>6634890</v>
       </c>
       <c r="S69" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7947,7 +7938,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7957,7 +7948,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Hack av spillkråka</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7984,48 +7980,53 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129600760</v>
+        <v>129605449</v>
       </c>
       <c r="B70" t="n">
-        <v>57737</v>
+        <v>4779</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>638304</v>
+        <v>638301</v>
       </c>
       <c r="R70" t="n">
-        <v>6634890</v>
+        <v>6634752</v>
       </c>
       <c r="S70" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8052,24 +8053,14 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Hack av spillkråka</t>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8078,71 +8069,76 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129605449</v>
+        <v>129602574</v>
       </c>
       <c r="B71" t="n">
-        <v>4779</v>
+        <v>98797</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>638301</v>
+        <v>638309</v>
       </c>
       <c r="R71" t="n">
-        <v>6634752</v>
+        <v>6634813</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8169,14 +8165,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8185,19 +8186,18 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -8314,7 +8314,7 @@
         <v>132099004</v>
       </c>
       <c r="B73" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -8314,7 +8314,7 @@
         <v>132099004</v>
       </c>
       <c r="B73" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -8314,7 +8314,7 @@
         <v>132099004</v>
       </c>
       <c r="B73" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -8314,7 +8314,7 @@
         <v>132099004</v>
       </c>
       <c r="B73" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -8314,7 +8314,7 @@
         <v>132099004</v>
       </c>
       <c r="B73" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -8314,7 +8314,7 @@
         <v>132099004</v>
       </c>
       <c r="B73" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -8314,7 +8314,7 @@
         <v>132099004</v>
       </c>
       <c r="B73" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY74"/>
+  <dimension ref="A1:AY86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128759905</v>
+        <v>129529667</v>
       </c>
       <c r="B2" t="n">
-        <v>98678</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>638438</v>
+        <v>638289</v>
       </c>
       <c r="R2" t="n">
-        <v>6634804</v>
+        <v>6634966</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,64 +760,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128959115</v>
+        <v>129529668</v>
       </c>
       <c r="B3" t="n">
-        <v>98724</v>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Orreboda, Orreboda, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>638451</v>
+        <v>638445</v>
       </c>
       <c r="R3" t="n">
-        <v>6634705</v>
+        <v>6634888</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -841,12 +837,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>1 kvm, längs hela stocken</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -861,60 +862,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129529701</v>
+        <v>129597548</v>
       </c>
       <c r="B4" t="n">
-        <v>4779</v>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>638164</v>
+        <v>638336</v>
       </c>
       <c r="R4" t="n">
-        <v>6635000</v>
+        <v>6634702</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -938,17 +939,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På levande äldre gran</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -963,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129529667</v>
+        <v>129605436</v>
       </c>
       <c r="B5" t="n">
-        <v>97036</v>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1010,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>638289</v>
+        <v>638281</v>
       </c>
       <c r="R5" t="n">
-        <v>6634966</v>
+        <v>6634960</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1040,12 +1046,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1072,32 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129529690</v>
+        <v>129529685</v>
       </c>
       <c r="B6" t="n">
-        <v>92919</v>
+        <v>92145</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>1100</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rosetticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Postia floriformis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Quél.) Jülich</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1107,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>638521</v>
+        <v>638472</v>
       </c>
       <c r="R6" t="n">
-        <v>6634838</v>
+        <v>6634942</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1169,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129529673</v>
+        <v>129529664</v>
       </c>
       <c r="B7" t="n">
-        <v>57896</v>
+        <v>92134</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1180,21 +1186,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>1106</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1204,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>638516</v>
+        <v>638322</v>
       </c>
       <c r="R7" t="n">
-        <v>6634868</v>
+        <v>6634962</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1266,48 +1272,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129529684</v>
+        <v>129601121</v>
       </c>
       <c r="B8" t="n">
-        <v>92052</v>
+        <v>92134</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>1106</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>638462</v>
+        <v>638329</v>
       </c>
       <c r="R8" t="n">
-        <v>6634855</v>
+        <v>6634973</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1331,12 +1337,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1351,44 +1367,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129529697</v>
+        <v>129587667</v>
       </c>
       <c r="B9" t="n">
-        <v>90981</v>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5685</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1398,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>638402</v>
+        <v>638466</v>
       </c>
       <c r="R9" t="n">
-        <v>6634635</v>
+        <v>6634835</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1428,12 +1444,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1460,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129529691</v>
+        <v>129599511</v>
       </c>
       <c r="B10" t="n">
-        <v>92919</v>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1471,37 +1487,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>638522</v>
+        <v>638406</v>
       </c>
       <c r="R10" t="n">
-        <v>6634845</v>
+        <v>6634775</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1525,12 +1541,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1545,44 +1571,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129529700</v>
+        <v>129529683</v>
       </c>
       <c r="B11" t="n">
-        <v>4779</v>
+        <v>92369</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102306</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1592,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>638165</v>
+        <v>638471</v>
       </c>
       <c r="R11" t="n">
-        <v>6634993</v>
+        <v>6634943</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1628,11 +1654,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1659,32 +1680,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129529688</v>
+        <v>129529684</v>
       </c>
       <c r="B12" t="n">
-        <v>4779</v>
+        <v>92369</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102306</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1694,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>638173</v>
+        <v>638462</v>
       </c>
       <c r="R12" t="n">
-        <v>6634959</v>
+        <v>6634855</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1730,11 +1751,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1761,10 +1777,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129529698</v>
+        <v>129598997</v>
       </c>
       <c r="B13" t="n">
-        <v>4779</v>
+        <v>92564</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1772,37 +1788,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102306</v>
+        <v>1339</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>638291</v>
+        <v>638351</v>
       </c>
       <c r="R13" t="n">
-        <v>6634662</v>
+        <v>6634790</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1826,17 +1842,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På levande äldre gran</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1851,44 +1872,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129529664</v>
+        <v>129529680</v>
       </c>
       <c r="B14" t="n">
-        <v>91823</v>
+        <v>91680</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1106</v>
+        <v>3215</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1898,10 +1919,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>638322</v>
+        <v>638472</v>
       </c>
       <c r="R14" t="n">
-        <v>6634962</v>
+        <v>6634952</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1960,10 +1981,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129529669</v>
+        <v>129529681</v>
       </c>
       <c r="B15" t="n">
-        <v>91563</v>
+        <v>91680</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1971,21 +1992,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>3215</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1995,10 +2016,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>638445</v>
+        <v>638480</v>
       </c>
       <c r="R15" t="n">
-        <v>6634890</v>
+        <v>6634921</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2060,7 +2081,7 @@
         <v>129529682</v>
       </c>
       <c r="B16" t="n">
-        <v>91372</v>
+        <v>91680</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2154,32 +2175,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129529668</v>
+        <v>129605441</v>
       </c>
       <c r="B17" t="n">
-        <v>97036</v>
+        <v>91680</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>3215</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2189,10 +2210,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>638445</v>
+        <v>638444</v>
       </c>
       <c r="R17" t="n">
-        <v>6634888</v>
+        <v>6634897</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2219,17 +2240,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>1 kvm, längs hela stocken</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2256,32 +2272,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129529689</v>
+        <v>129605437</v>
       </c>
       <c r="B18" t="n">
-        <v>92873</v>
+        <v>92632</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4361</v>
+        <v>3298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2291,10 +2307,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>638468</v>
+        <v>638356</v>
       </c>
       <c r="R18" t="n">
-        <v>6634921</v>
+        <v>6634677</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2321,12 +2337,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2353,32 +2369,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129529699</v>
+        <v>129529689</v>
       </c>
       <c r="B19" t="n">
-        <v>4779</v>
+        <v>93189</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102306</v>
+        <v>4361</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2388,10 +2404,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>638353</v>
+        <v>638468</v>
       </c>
       <c r="R19" t="n">
-        <v>6634591</v>
+        <v>6634921</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2424,11 +2440,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2455,32 +2466,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129529679</v>
+        <v>129529669</v>
       </c>
       <c r="B20" t="n">
-        <v>57733</v>
+        <v>91872</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2490,10 +2501,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>638353</v>
+        <v>638445</v>
       </c>
       <c r="R20" t="n">
-        <v>6634546</v>
+        <v>6634890</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2552,32 +2563,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129587678</v>
+        <v>129529670</v>
       </c>
       <c r="B21" t="n">
-        <v>98797</v>
+        <v>91872</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2587,10 +2598,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>638458</v>
+        <v>638473</v>
       </c>
       <c r="R21" t="n">
-        <v>6634826</v>
+        <v>6634944</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2617,12 +2628,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2649,32 +2660,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129587673</v>
+        <v>129529671</v>
       </c>
       <c r="B22" t="n">
-        <v>98797</v>
+        <v>91872</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2684,10 +2695,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>638448</v>
+        <v>638471</v>
       </c>
       <c r="R22" t="n">
-        <v>6634809</v>
+        <v>6634943</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2714,17 +2725,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Blommande</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2751,32 +2757,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129587679</v>
+        <v>129587666</v>
       </c>
       <c r="B23" t="n">
-        <v>98797</v>
+        <v>91872</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2786,10 +2792,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>638451</v>
+        <v>638444</v>
       </c>
       <c r="R23" t="n">
-        <v>6634848</v>
+        <v>6634931</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2848,32 +2854,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129587676</v>
+        <v>129529697</v>
       </c>
       <c r="B24" t="n">
-        <v>98797</v>
+        <v>91282</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>5685</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2883,10 +2889,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>638438</v>
+        <v>638402</v>
       </c>
       <c r="R24" t="n">
-        <v>6634803</v>
+        <v>6634635</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -2913,17 +2919,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>10 buketter</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2950,32 +2951,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129587685</v>
+        <v>129605451</v>
       </c>
       <c r="B25" t="n">
-        <v>100986</v>
+        <v>93233</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2985,10 +2986,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>638463</v>
+        <v>638325</v>
       </c>
       <c r="R25" t="n">
-        <v>6634889</v>
+        <v>6634691</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3015,12 +3016,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3047,10 +3048,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129587670</v>
+        <v>129605452</v>
       </c>
       <c r="B26" t="n">
-        <v>57737</v>
+        <v>93233</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3058,21 +3059,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3082,10 +3083,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>638333</v>
+        <v>638324</v>
       </c>
       <c r="R26" t="n">
-        <v>6634980</v>
+        <v>6634750</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3112,12 +3113,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3144,32 +3145,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129587677</v>
+        <v>129529690</v>
       </c>
       <c r="B27" t="n">
-        <v>98797</v>
+        <v>93235</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3179,10 +3180,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>638447</v>
+        <v>638521</v>
       </c>
       <c r="R27" t="n">
-        <v>6634803</v>
+        <v>6634838</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3209,17 +3210,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>10 buketter</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3246,32 +3242,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129587681</v>
+        <v>129529691</v>
       </c>
       <c r="B28" t="n">
-        <v>98797</v>
+        <v>93235</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3281,10 +3277,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>638468</v>
+        <v>638522</v>
       </c>
       <c r="R28" t="n">
-        <v>6634929</v>
+        <v>6634845</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3311,12 +3307,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3343,10 +3339,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129587667</v>
+        <v>129600091</v>
       </c>
       <c r="B29" t="n">
-        <v>91605</v>
+        <v>93235</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3354,37 +3350,51 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>5966</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>638466</v>
+        <v>638367</v>
       </c>
       <c r="R29" t="n">
-        <v>6634835</v>
+        <v>6634820</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3408,12 +3418,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3428,60 +3448,60 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129597548</v>
+        <v>129529679</v>
       </c>
       <c r="B30" t="n">
-        <v>97043</v>
+        <v>57950</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>638336</v>
+        <v>638353</v>
       </c>
       <c r="R30" t="n">
-        <v>6634702</v>
+        <v>6634546</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3505,22 +3525,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>10:44</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>10:44</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3535,74 +3545,60 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129598790</v>
+        <v>129587670</v>
       </c>
       <c r="B31" t="n">
-        <v>98797</v>
+        <v>57950</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
         <v>638333</v>
       </c>
       <c r="R31" t="n">
-        <v>6634812</v>
+        <v>6634980</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3626,22 +3622,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>11:31</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>11:31</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3656,22 +3642,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129605451</v>
+        <v>129596091</v>
       </c>
       <c r="B32" t="n">
-        <v>92923</v>
+        <v>57950</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3679,37 +3665,46 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Orreboda, Orreboda, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>638325</v>
+        <v>638323</v>
       </c>
       <c r="R32" t="n">
-        <v>6634691</v>
+        <v>6634555</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3736,9 +3731,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3753,59 +3758,50 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129599980</v>
+        <v>129597436</v>
       </c>
       <c r="B33" t="n">
-        <v>98797</v>
+        <v>57950</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3814,13 +3810,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>638416</v>
+        <v>638292</v>
       </c>
       <c r="R33" t="n">
-        <v>6634840</v>
+        <v>6634699</v>
       </c>
       <c r="S33" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3849,7 +3845,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -3859,12 +3855,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>2 vinterståndare</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3891,41 +3882,50 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129598714</v>
+        <v>129599884</v>
       </c>
       <c r="B34" t="n">
-        <v>91625</v>
+        <v>57950</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>638323</v>
+        <v>638397</v>
       </c>
       <c r="R34" t="n">
-        <v>6634794</v>
+        <v>6634819</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -3957,7 +3957,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -3967,12 +3967,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:29</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Rikligt på undersidan av döda grenar på levande äldre gran.</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3999,62 +3994,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129598966</v>
+        <v>129600760</v>
       </c>
       <c r="B35" t="n">
-        <v>98797</v>
+        <v>57950</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>638348</v>
+        <v>638304</v>
       </c>
       <c r="R35" t="n">
-        <v>6634797</v>
+        <v>6634890</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4083,7 +4064,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4093,12 +4074,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>3 vinterståndare</t>
+          <t>Hack av spillkråka</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4113,59 +4094,50 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129599353</v>
+        <v>129600817</v>
       </c>
       <c r="B36" t="n">
-        <v>98797</v>
+        <v>57950</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4174,13 +4146,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>638395</v>
+        <v>638230</v>
       </c>
       <c r="R36" t="n">
-        <v>6634786</v>
+        <v>6634962</v>
       </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4209,7 +4181,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4219,7 +4191,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4246,14 +4218,14 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129599884</v>
+        <v>129602955</v>
       </c>
       <c r="B37" t="n">
-        <v>57737</v>
+        <v>57950</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4275,24 +4247,19 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>638397</v>
+        <v>638310</v>
       </c>
       <c r="R37" t="n">
-        <v>6634819</v>
+        <v>6634749</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4321,7 +4288,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4331,7 +4298,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Hack av spillkråka</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4346,60 +4318,60 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129599503</v>
+        <v>129605439</v>
       </c>
       <c r="B38" t="n">
-        <v>98797</v>
+        <v>57950</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>638325</v>
+        <v>638277</v>
       </c>
       <c r="R38" t="n">
-        <v>6634846</v>
+        <v>6634933</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4426,19 +4398,9 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>12:03</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>12:03</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4453,22 +4415,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anders Broms</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anders Broms</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129605441</v>
+        <v>129605440</v>
       </c>
       <c r="B39" t="n">
-        <v>91378</v>
+        <v>57950</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4476,21 +4438,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3215</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4500,10 +4462,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>638444</v>
+        <v>638309</v>
       </c>
       <c r="R39" t="n">
-        <v>6634897</v>
+        <v>6634908</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4562,32 +4524,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129605436</v>
+        <v>129529688</v>
       </c>
       <c r="B40" t="n">
-        <v>97043</v>
+        <v>4781</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4597,10 +4559,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>638281</v>
+        <v>638173</v>
       </c>
       <c r="R40" t="n">
-        <v>6634960</v>
+        <v>6634959</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4627,12 +4589,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4659,57 +4626,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129599775</v>
+        <v>129529698</v>
       </c>
       <c r="B41" t="n">
-        <v>98797</v>
+        <v>4781</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>638435</v>
+        <v>638291</v>
       </c>
       <c r="R41" t="n">
-        <v>6634839</v>
+        <v>6634662</v>
       </c>
       <c r="S41" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4733,22 +4691,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>12:14</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>12:14</t>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4763,69 +4716,60 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129599955</v>
+        <v>129529699</v>
       </c>
       <c r="B42" t="n">
-        <v>98797</v>
+        <v>4781</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>638428</v>
+        <v>638353</v>
       </c>
       <c r="R42" t="n">
-        <v>6634839</v>
+        <v>6634591</v>
       </c>
       <c r="S42" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4849,22 +4793,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4879,74 +4818,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129597954</v>
+        <v>129529700</v>
       </c>
       <c r="B43" t="n">
-        <v>98797</v>
+        <v>4781</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>638325</v>
+        <v>638165</v>
       </c>
       <c r="R43" t="n">
-        <v>6634719</v>
+        <v>6634993</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4970,27 +4895,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>10:55</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>10:55</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>3 vinterståndare</t>
+          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5005,60 +4920,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129602955</v>
+        <v>129529701</v>
       </c>
       <c r="B44" t="n">
-        <v>57737</v>
+        <v>4781</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>638310</v>
+        <v>638164</v>
       </c>
       <c r="R44" t="n">
-        <v>6634749</v>
+        <v>6635000</v>
       </c>
       <c r="S44" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5082,27 +4997,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Hack av spillkråka</t>
+          <t>På levande äldre gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5117,64 +5022,65 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129601221</v>
+        <v>129605449</v>
       </c>
       <c r="B45" t="n">
-        <v>98797</v>
+        <v>4781</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>638294</v>
+        <v>638301</v>
       </c>
       <c r="R45" t="n">
-        <v>6634962</v>
+        <v>6634752</v>
       </c>
       <c r="S45" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5201,19 +5107,14 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:23</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:23</t>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5222,80 +5123,72 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129598225</v>
+        <v>129605450</v>
       </c>
       <c r="B46" t="n">
-        <v>98797</v>
+        <v>4781</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>638330</v>
+        <v>638178</v>
       </c>
       <c r="R46" t="n">
-        <v>6634715</v>
+        <v>6635025</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5322,24 +5215,14 @@
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>2 vinterståndare</t>
+          <t>På äldre levande gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5348,80 +5231,67 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129599067</v>
+        <v>132099005</v>
       </c>
       <c r="B47" t="n">
-        <v>98797</v>
+        <v>4782</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>638355</v>
+        <v>638473</v>
       </c>
       <c r="R47" t="n">
-        <v>6634788</v>
+        <v>6634917</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5445,27 +5315,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>En vinterståndare</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5480,74 +5345,60 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129602225</v>
+        <v>129529672</v>
       </c>
       <c r="B48" t="n">
-        <v>98797</v>
+        <v>58114</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>638237</v>
+        <v>638452</v>
       </c>
       <c r="R48" t="n">
-        <v>6635004</v>
+        <v>6634930</v>
       </c>
       <c r="S48" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5571,27 +5422,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>14:09</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>En vinterståndare</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5606,74 +5442,60 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129600150</v>
+        <v>129529673</v>
       </c>
       <c r="B49" t="n">
-        <v>98797</v>
+        <v>58114</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>638354</v>
+        <v>638516</v>
       </c>
       <c r="R49" t="n">
-        <v>6634767</v>
+        <v>6634868</v>
       </c>
       <c r="S49" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5697,22 +5519,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>12:36</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>12:36</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5727,59 +5539,54 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129602684</v>
+        <v>129601877</v>
       </c>
       <c r="B50" t="n">
-        <v>98797</v>
+        <v>58114</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5788,13 +5595,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>638332</v>
+        <v>638218</v>
       </c>
       <c r="R50" t="n">
-        <v>6634693</v>
+        <v>6635080</v>
       </c>
       <c r="S50" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5823,7 +5630,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5833,7 +5640,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5860,48 +5667,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129605439</v>
+        <v>128759905</v>
       </c>
       <c r="B51" t="n">
-        <v>57737</v>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>638277</v>
+        <v>638438</v>
       </c>
       <c r="R51" t="n">
-        <v>6634933</v>
+        <v>6634804</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5925,12 +5732,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5945,60 +5752,69 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129599511</v>
+        <v>128958726</v>
       </c>
       <c r="B52" t="n">
-        <v>91605</v>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Orreboda, Orreboda, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>638406</v>
+        <v>638523</v>
       </c>
       <c r="R52" t="n">
-        <v>6634775</v>
+        <v>6634716</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6022,22 +5838,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>12:05</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>12:05</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6052,22 +5858,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129599969</v>
+        <v>128959115</v>
       </c>
       <c r="B53" t="n">
-        <v>98797</v>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6094,27 +5900,22 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Orreboda, Orreboda, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>638428</v>
+        <v>638451</v>
       </c>
       <c r="R53" t="n">
-        <v>6634835</v>
+        <v>6634705</v>
       </c>
       <c r="S53" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6138,22 +5939,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>12:24</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>12:24</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6168,22 +5959,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129599963</v>
+        <v>129587673</v>
       </c>
       <c r="B54" t="n">
-        <v>98797</v>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6208,34 +5999,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>638420</v>
+        <v>638448</v>
       </c>
       <c r="R54" t="n">
-        <v>6634840</v>
+        <v>6634809</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6259,22 +6036,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>12:24</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>12:24</t>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Blommande</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6289,22 +6061,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129599772</v>
+        <v>129587675</v>
       </c>
       <c r="B55" t="n">
-        <v>98797</v>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6329,34 +6101,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>638399</v>
+        <v>638480</v>
       </c>
       <c r="R55" t="n">
-        <v>6634806</v>
+        <v>6634941</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6380,27 +6138,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>En vinterståndare</t>
+          <t>15 buketter</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6415,22 +6163,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129602370</v>
+        <v>129587676</v>
       </c>
       <c r="B56" t="n">
-        <v>98797</v>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6455,34 +6203,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>638275</v>
+        <v>638438</v>
       </c>
       <c r="R56" t="n">
-        <v>6634839</v>
+        <v>6634803</v>
       </c>
       <c r="S56" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6506,22 +6240,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>14:22</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>14:22</t>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6536,22 +6265,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129602720</v>
+        <v>129587677</v>
       </c>
       <c r="B57" t="n">
-        <v>98797</v>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6576,29 +6305,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>638301</v>
+        <v>638447</v>
       </c>
       <c r="R57" t="n">
-        <v>6634767</v>
+        <v>6634803</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6622,22 +6342,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>10 buketter</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6652,69 +6367,60 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129596091</v>
+        <v>129587678</v>
       </c>
       <c r="B58" t="n">
-        <v>57737</v>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Orreboda, Orreboda, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>638323</v>
+        <v>638458</v>
       </c>
       <c r="R58" t="n">
-        <v>6634555</v>
+        <v>6634826</v>
       </c>
       <c r="S58" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6738,22 +6444,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6768,22 +6464,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129601983</v>
+        <v>129587679</v>
       </c>
       <c r="B59" t="n">
-        <v>98797</v>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6808,34 +6504,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>638209</v>
+        <v>638451</v>
       </c>
       <c r="R59" t="n">
-        <v>6635047</v>
+        <v>6634848</v>
       </c>
       <c r="S59" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6859,22 +6541,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>13:56</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>13:56</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6889,22 +6561,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129602223</v>
+        <v>129587680</v>
       </c>
       <c r="B60" t="n">
-        <v>98797</v>
+        <v>99118</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6929,29 +6601,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>638236</v>
+        <v>638463</v>
       </c>
       <c r="R60" t="n">
-        <v>6634982</v>
+        <v>6634930</v>
       </c>
       <c r="S60" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6975,22 +6638,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>14:09</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>14:09</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7005,65 +6658,60 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129600817</v>
+        <v>129587681</v>
       </c>
       <c r="B61" t="n">
-        <v>57737</v>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kolarskogen, Kolarskogen, Upl</t>
+          <t>Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>638230</v>
+        <v>638468</v>
       </c>
       <c r="R61" t="n">
-        <v>6634962</v>
+        <v>6634929</v>
       </c>
       <c r="S61" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7087,22 +6735,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>13:08</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>13:08</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7117,60 +6755,74 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129605440</v>
+        <v>129597954</v>
       </c>
       <c r="B62" t="n">
-        <v>57737</v>
+        <v>99118</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>638309</v>
+        <v>638325</v>
       </c>
       <c r="R62" t="n">
-        <v>6634908</v>
+        <v>6634719</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7197,9 +6849,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>3 vinterståndare</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7214,59 +6881,59 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129600091</v>
+        <v>129598225</v>
       </c>
       <c r="B63" t="n">
-        <v>92925</v>
+        <v>99118</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7275,13 +6942,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>638367</v>
+        <v>638330</v>
       </c>
       <c r="R63" t="n">
-        <v>6634820</v>
+        <v>6634715</v>
       </c>
       <c r="S63" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7310,7 +6977,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7320,7 +6987,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>2 vinterståndare</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7347,53 +7019,62 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129605450</v>
+        <v>129598790</v>
       </c>
       <c r="B64" t="n">
-        <v>4779</v>
+        <v>99118</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>638178</v>
+        <v>638333</v>
       </c>
       <c r="R64" t="n">
-        <v>6635025</v>
+        <v>6634812</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7420,14 +7101,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7436,67 +7122,80 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129605452</v>
+        <v>129598966</v>
       </c>
       <c r="B65" t="n">
-        <v>92923</v>
+        <v>99118</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>638324</v>
+        <v>638348</v>
       </c>
       <c r="R65" t="n">
-        <v>6634750</v>
+        <v>6634797</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7523,9 +7222,24 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>3 vinterståndare</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7540,50 +7254,59 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129597436</v>
+        <v>129599067</v>
       </c>
       <c r="B66" t="n">
-        <v>57737</v>
+        <v>99118</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7592,13 +7315,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>638292</v>
+        <v>638355</v>
       </c>
       <c r="R66" t="n">
-        <v>6634699</v>
+        <v>6634788</v>
       </c>
       <c r="S66" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7627,7 +7350,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7637,7 +7360,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7664,48 +7392,62 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129605437</v>
+        <v>129599353</v>
       </c>
       <c r="B67" t="n">
-        <v>92323</v>
+        <v>99118</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>638356</v>
+        <v>638395</v>
       </c>
       <c r="R67" t="n">
-        <v>6634677</v>
+        <v>6634786</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7732,9 +7474,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7749,22 +7501,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129601121</v>
+        <v>129599503</v>
       </c>
       <c r="B68" t="n">
-        <v>91829</v>
+        <v>99118</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7772,21 +7524,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1106</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7796,13 +7548,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>638329</v>
+        <v>638325</v>
       </c>
       <c r="R68" t="n">
-        <v>6634973</v>
+        <v>6634846</v>
       </c>
       <c r="S68" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7831,7 +7583,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7841,7 +7593,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7856,60 +7608,74 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Broms</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Anders Broms</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129600760</v>
+        <v>129599772</v>
       </c>
       <c r="B69" t="n">
-        <v>57737</v>
+        <v>99118</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>638304</v>
+        <v>638399</v>
       </c>
       <c r="R69" t="n">
-        <v>6634890</v>
+        <v>6634806</v>
       </c>
       <c r="S69" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7938,7 +7704,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7948,12 +7714,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Hack av spillkråka</t>
+          <t>En vinterståndare</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7968,65 +7734,69 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Hannes Theelen</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129605449</v>
+        <v>129599775</v>
       </c>
       <c r="B70" t="n">
-        <v>4779</v>
+        <v>99118</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>638301</v>
+        <v>638435</v>
       </c>
       <c r="R70" t="n">
-        <v>6634752</v>
+        <v>6634839</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8053,14 +7823,19 @@
           <t>2025-11-08</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-11-08</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>På äldre levande gran</t>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8069,29 +7844,28 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129602574</v>
+        <v>129599955</v>
       </c>
       <c r="B71" t="n">
-        <v>98797</v>
+        <v>99118</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8118,7 +7892,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -8132,13 +7906,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>638309</v>
+        <v>638428</v>
       </c>
       <c r="R71" t="n">
-        <v>6634813</v>
+        <v>6634839</v>
       </c>
       <c r="S71" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8167,7 +7941,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8177,7 +7951,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8204,48 +7978,62 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129598997</v>
+        <v>129599963</v>
       </c>
       <c r="B72" t="n">
-        <v>92255</v>
+        <v>99118</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>638351</v>
+        <v>638420</v>
       </c>
       <c r="R72" t="n">
-        <v>6634790</v>
+        <v>6634840</v>
       </c>
       <c r="S72" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8274,7 +8062,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8284,7 +8072,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8311,10 +8099,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132099004</v>
+        <v>129599969</v>
       </c>
       <c r="B73" t="n">
-        <v>99122</v>
+        <v>99118</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8339,7 +8127,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="J73" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -8347,17 +8139,17 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>638412</v>
+        <v>638428</v>
       </c>
       <c r="R73" t="n">
-        <v>6634843</v>
+        <v>6634835</v>
       </c>
       <c r="S73" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8381,22 +8173,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8411,60 +8203,74 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Hannes Theelen</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132099005</v>
+        <v>129599980</v>
       </c>
       <c r="B74" t="n">
-        <v>4781</v>
+        <v>99118</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Kolarskogen, Upl</t>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>638473</v>
+        <v>638416</v>
       </c>
       <c r="R74" t="n">
-        <v>6634917</v>
+        <v>6634840</v>
       </c>
       <c r="S74" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8488,22 +8294,27 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>2 vinterståndare</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8518,15 +8329,1390 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>129600150</v>
+      </c>
+      <c r="B75" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>638354</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6634767</v>
+      </c>
+      <c r="S75" t="n">
+        <v>4</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>129601221</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>638294</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6634962</v>
+      </c>
+      <c r="S76" t="n">
+        <v>12</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Hannes Theelen</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Hannes Theelen</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>129601983</v>
+      </c>
+      <c r="B77" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>638209</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6635047</v>
+      </c>
+      <c r="S77" t="n">
+        <v>4</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>129602223</v>
+      </c>
+      <c r="B78" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>638236</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6634982</v>
+      </c>
+      <c r="S78" t="n">
+        <v>9</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Hannes Theelen</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Hannes Theelen</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>129602225</v>
+      </c>
+      <c r="B79" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>638237</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6635004</v>
+      </c>
+      <c r="S79" t="n">
+        <v>7</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>En vinterståndare</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>129602370</v>
+      </c>
+      <c r="B80" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>638275</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6634839</v>
+      </c>
+      <c r="S80" t="n">
+        <v>8</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>129602574</v>
+      </c>
+      <c r="B81" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>638309</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6634813</v>
+      </c>
+      <c r="S81" t="n">
+        <v>17</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Hannes Theelen</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Hannes Theelen</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>129602684</v>
+      </c>
+      <c r="B82" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>638332</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6634693</v>
+      </c>
+      <c r="S82" t="n">
+        <v>4</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>129602720</v>
+      </c>
+      <c r="B83" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>638301</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6634767</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Hannes Theelen</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Hannes Theelen</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>129605448</v>
+      </c>
+      <c r="B84" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>638393</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6634876</v>
+      </c>
+      <c r="S84" t="n">
+        <v>15</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
           <t>Tomas Falk</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
+      <c r="AX84" t="inlineStr">
         <is>
           <t>Tomas Falk</t>
         </is>
       </c>
-      <c r="AY74" t="inlineStr"/>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>132099004</v>
+      </c>
+      <c r="B85" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>638412</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6634843</v>
+      </c>
+      <c r="S85" t="n">
+        <v>3</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>129587685</v>
+      </c>
+      <c r="B86" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Kolarskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>638463</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6634889</v>
+      </c>
+      <c r="S86" t="n">
+        <v>15</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Vänge</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -2064,7 +2064,7 @@
         <v>135003552</v>
       </c>
       <c r="B15" t="n">
-        <v>91528</v>
+        <v>91531</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -1952,7 +1952,7 @@
         <v>134843687</v>
       </c>
       <c r="B14" t="n">
-        <v>91459</v>
+        <v>91533</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>135003552</v>
       </c>
       <c r="B15" t="n">
-        <v>91531</v>
+        <v>91533</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -1952,7 +1952,7 @@
         <v>134843687</v>
       </c>
       <c r="B14" t="n">
-        <v>91533</v>
+        <v>91535</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>135003552</v>
       </c>
       <c r="B15" t="n">
-        <v>91533</v>
+        <v>91535</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -1952,7 +1952,7 @@
         <v>134843687</v>
       </c>
       <c r="B14" t="n">
-        <v>91535</v>
+        <v>91536</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>135003552</v>
       </c>
       <c r="B15" t="n">
-        <v>91535</v>
+        <v>91536</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -1952,7 +1952,7 @@
         <v>134843687</v>
       </c>
       <c r="B14" t="n">
-        <v>91536</v>
+        <v>91537</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>135003552</v>
       </c>
       <c r="B15" t="n">
-        <v>91536</v>
+        <v>91537</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -1952,7 +1952,7 @@
         <v>134843687</v>
       </c>
       <c r="B14" t="n">
-        <v>91537</v>
+        <v>91538</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>135003552</v>
       </c>
       <c r="B15" t="n">
-        <v>91537</v>
+        <v>91538</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -1952,7 +1952,7 @@
         <v>134843687</v>
       </c>
       <c r="B14" t="n">
-        <v>91538</v>
+        <v>91544</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>135003552</v>
       </c>
       <c r="B15" t="n">
-        <v>91538</v>
+        <v>91544</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -1952,7 +1952,7 @@
         <v>134843687</v>
       </c>
       <c r="B14" t="n">
-        <v>91544</v>
+        <v>91545</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>135003552</v>
       </c>
       <c r="B15" t="n">
-        <v>91544</v>
+        <v>91545</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -1952,7 +1952,7 @@
         <v>134843687</v>
       </c>
       <c r="B14" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>135003552</v>
       </c>
       <c r="B15" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -1952,7 +1952,7 @@
         <v>134843687</v>
       </c>
       <c r="B14" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>135003552</v>
       </c>
       <c r="B15" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -1952,7 +1952,7 @@
         <v>134843687</v>
       </c>
       <c r="B14" t="n">
-        <v>91558</v>
+        <v>91559</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>135003552</v>
       </c>
       <c r="B15" t="n">
-        <v>91558</v>
+        <v>91559</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -1952,7 +1952,7 @@
         <v>134843687</v>
       </c>
       <c r="B14" t="n">
-        <v>91559</v>
+        <v>91572</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>135003552</v>
       </c>
       <c r="B15" t="n">
-        <v>91559</v>
+        <v>91572</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 53593-2025 artfynd.xlsx
+++ b/artfynd/A 53593-2025 artfynd.xlsx
@@ -1952,7 +1952,7 @@
         <v>134843687</v>
       </c>
       <c r="B14" t="n">
-        <v>91572</v>
+        <v>91573</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>135003552</v>
       </c>
       <c r="B15" t="n">
-        <v>91572</v>
+        <v>91573</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
